--- a/news_today.xlsx
+++ b/news_today.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="1182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1681" uniqueCount="1186">
   <si>
     <t>Title</t>
   </si>
@@ -118,6 +118,15 @@
     <t>https://www.bbc.com/news/articles/c0q3nwdk315o?at_medium=RSS&amp;at_campaign=rss</t>
   </si>
   <si>
+    <t>'For Dad, who didn't get to see this' - Shiffrin wins slalom gold</t>
+  </si>
+  <si>
+    <t>American star Mikaela Shiffrin cements her status as the greatest alpine skier of all time as she wins Olympic slalom gold in emphatic fashion.</t>
+  </si>
+  <si>
+    <t>https://www.bbc.com/sport/articles/ce8n4yp20zyo?at_medium=RSS&amp;at_campaign=rss</t>
+  </si>
+  <si>
     <t>'How on earth have they done that?' - see Morrison's miracle shot that stole win for GB</t>
   </si>
   <si>
@@ -136,166 +145,160 @@
     <t>https://www.bbc.com/news/videos/cgk2gj3zm8do?at_medium=RSS&amp;at_campaign=rss</t>
   </si>
   <si>
+    <t>How a fatal crash happened on a smart motorway</t>
+  </si>
+  <si>
+    <t>Pulvinder Dhillon, 68, from London, died after the crash on the M4 in Berkshire in March 2022.</t>
+  </si>
+  <si>
+    <t>https://www.bbc.com/news/articles/c4g2d4l1x15o?at_medium=RSS&amp;at_campaign=rss</t>
+  </si>
+  <si>
+    <t>'I would sell a lung for a Hannah Montana tour': Fans react to 20th anniversary special announcement</t>
+  </si>
+  <si>
+    <t>Fans are gearing up for the "Hannahversary" - a special to mark the show's 20th anniversary.</t>
+  </si>
+  <si>
+    <t>https://www.bbc.com/news/articles/c0k1xjm7463o?at_medium=RSS&amp;at_campaign=rss</t>
+  </si>
+  <si>
+    <t>'Just push us into the sea': The frustration of a coastal community failed by political promises</t>
+  </si>
+  <si>
+    <t>In Horden, County Durham, Westminster slogans have long been left unmet as the population has plummeted.</t>
+  </si>
+  <si>
+    <t>https://www.bbc.com/news/articles/cm2136jnjx1o?at_medium=RSS&amp;at_campaign=rss</t>
+  </si>
+  <si>
+    <t>William says it has taken 'long time to understand my emotions'</t>
+  </si>
+  <si>
+    <t>Prince William has offered his advice to those struggling with their mental health, in a special Radio 1 panel discussion.</t>
+  </si>
+  <si>
+    <t>https://www.bbc.com/news/articles/cm21d4j26pdo?at_medium=RSS&amp;at_campaign=rss</t>
+  </si>
+  <si>
+    <t>I invested £12,000 in Brewdog  - I think I've lost it all</t>
+  </si>
+  <si>
+    <t>More than 200,000 people bought Equity for Punks shares in the craft brewer but many now believe they are worthless.</t>
+  </si>
+  <si>
+    <t>https://www.bbc.com/news/articles/c795879x08go?at_medium=RSS&amp;at_campaign=rss</t>
+  </si>
+  <si>
+    <t>Cynthia Erivo ignores online criticism as Dracula gets mixed reviews</t>
+  </si>
+  <si>
+    <t>The Wicked star appears in a one-woman version of the classic horror story in London's West End.</t>
+  </si>
+  <si>
+    <t>https://www.bbc.com/news/articles/cqxd4r4xzx1o?at_medium=RSS&amp;at_campaign=rss</t>
+  </si>
+  <si>
+    <t>I hated my appearance. Here's how I learned to accept it</t>
+  </si>
+  <si>
+    <t>Tilly and Charlotte share their experiences of body dysmorphic disorder and how they recovered from it.</t>
+  </si>
+  <si>
+    <t>https://www.bbc.com/news/articles/cre2pelrpwzo?at_medium=RSS&amp;at_campaign=rss</t>
+  </si>
+  <si>
+    <t>Letter by young Queen Elizabeth II to be auctioned</t>
+  </si>
+  <si>
+    <t>The letter from Queen Elizabeth II asks if "the birds are well, and the goldfish haven't died".</t>
+  </si>
+  <si>
+    <t>https://www.bbc.com/news/articles/cp85v315zvjo?at_medium=RSS&amp;at_campaign=rss</t>
+  </si>
+  <si>
+    <t>Zuckerberg arrives to testify in social media addiction trial</t>
+  </si>
+  <si>
+    <t>The billionaire Meta chief executive faces questioning over whether use of Instagram harms children.</t>
+  </si>
+  <si>
+    <t>https://www.bbc.com/news/articles/c5y42znjnjvo?at_medium=RSS&amp;at_campaign=rss</t>
+  </si>
+  <si>
+    <t>Plan to increase youth minimum wage could be delayed</t>
+  </si>
+  <si>
+    <t>Government sources tell BBC News they could slow down plans to make minimum wage equal across age groups.</t>
+  </si>
+  <si>
+    <t>https://www.bbc.com/news/articles/c5y6g57j3meo?at_medium=RSS&amp;at_campaign=rss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Climber on trial for leaving girlfriend to die on Austria's highest mountain </t>
+  </si>
+  <si>
+    <t>Kerstin G's boyfriend is accused of leaving her unprotected and exhausted close to the summit during a blizzard.</t>
+  </si>
+  <si>
+    <t>https://www.bbc.com/news/articles/c5yv9plyjgpo?at_medium=RSS&amp;at_campaign=rss</t>
+  </si>
+  <si>
+    <t>Man who threw corrosive liquid on guest at spiritual retreat and fled country is jailed</t>
+  </si>
+  <si>
+    <t>A wellness retreat owner went on the run in several countries after throwing liquid into a guest's face.</t>
+  </si>
+  <si>
+    <t>https://www.bbc.com/news/articles/c4g82znj294o?at_medium=RSS&amp;at_campaign=rss</t>
+  </si>
+  <si>
+    <t>Otter cubs rescued after sheltering in car engine</t>
+  </si>
+  <si>
+    <t>The tired and cold cubs were taken in for the night by Karen Watson, who kept them in a cardboard box in her bathtub.</t>
+  </si>
+  <si>
+    <t>https://www.bbc.com/news/articles/cpw0zrn919po?at_medium=RSS&amp;at_campaign=rss</t>
+  </si>
+  <si>
+    <t>Wave of arrests over killing of French nationalist piles pressure on far left</t>
+  </si>
+  <si>
+    <t>Eleven people are in detention in connection with the killing of far-right student activist Quentin Deranque.</t>
+  </si>
+  <si>
+    <t>https://www.bbc.com/news/articles/c62dzgy0q37o?at_medium=RSS&amp;at_campaign=rss</t>
+  </si>
+  <si>
+    <t>GB's curling medal hopes still alive after double win over US</t>
+  </si>
+  <si>
+    <t>Team GB's slim Winter Olympics curling medal hopes are still alive after both the men's and women's rink edge out the United States in Cortina.</t>
+  </si>
+  <si>
+    <t>https://www.bbc.com/sport/articles/c0q3nejy1pjo?at_medium=RSS&amp;at_campaign=rss</t>
+  </si>
+  <si>
+    <t>Hamilton finds new F1 cars 'more fun' to drive</t>
+  </si>
+  <si>
+    <t>Lewis Hamilton says he finds the new Formula 1 cars this year "more fun" to drive - in contrast to the views of Max Verstappen and Fernando Alonso.</t>
+  </si>
+  <si>
+    <t>https://www.bbc.com/sport/formula1/articles/c20z9wlw1vpo?at_medium=RSS&amp;at_campaign=rss</t>
+  </si>
+  <si>
+    <t>'It smacks of England' - Australia fail again at T20 World Cup</t>
+  </si>
+  <si>
+    <t>Muddled selection and the lack of a plan B - how Australia's T20 World Cup campaign was derailed in Sri Lanka.</t>
+  </si>
+  <si>
+    <t>https://www.bbc.com/sport/cricket/articles/cqxd4rgr99qo?at_medium=RSS&amp;at_campaign=rss</t>
+  </si>
+  <si>
     <t>'For Dad, who didn't get to see this' - Shiffrin wins gold</t>
-  </si>
-  <si>
-    <t>American star Mikaela Shiffrin cements her status as the greatest alpine skier of all time as she wins Olympic slalom gold in emphatic fashion.</t>
-  </si>
-  <si>
-    <t>https://www.bbc.com/sport/articles/ce8n4yp20zyo?at_medium=RSS&amp;at_campaign=rss</t>
-  </si>
-  <si>
-    <t>How a fatal crash happened on a smart motorway</t>
-  </si>
-  <si>
-    <t>Pulvinder Dhillon, 68, from London, died after the crash on the M4 in Berkshire in March 2022.</t>
-  </si>
-  <si>
-    <t>https://www.bbc.com/news/articles/c4g2d4l1x15o?at_medium=RSS&amp;at_campaign=rss</t>
-  </si>
-  <si>
-    <t>'I would sell a lung for a Hannah Montana tour': Fans react to 20th anniversary special announcement</t>
-  </si>
-  <si>
-    <t>Fans are gearing up for the "Hannahversary" - a special to mark the show's 20th anniversary.</t>
-  </si>
-  <si>
-    <t>https://www.bbc.com/news/articles/c0k1xjm7463o?at_medium=RSS&amp;at_campaign=rss</t>
-  </si>
-  <si>
-    <t>'Just push us into the sea': The frustration of a coastal community failed by political promises</t>
-  </si>
-  <si>
-    <t>In Horden, County Durham, Westminster slogans have long been left unmet as the population has plummeted.</t>
-  </si>
-  <si>
-    <t>https://www.bbc.com/news/articles/cm2136jnjx1o?at_medium=RSS&amp;at_campaign=rss</t>
-  </si>
-  <si>
-    <t>William says it has taken 'long time to understand my emotions'</t>
-  </si>
-  <si>
-    <t>Prince William has offered his advice to those struggling with their mental health, in a special Radio 1 panel discussion.</t>
-  </si>
-  <si>
-    <t>https://www.bbc.com/news/articles/cm21d4j26pdo?at_medium=RSS&amp;at_campaign=rss</t>
-  </si>
-  <si>
-    <t>I invested £12,000 in Brewdog  - I think I've lost it all</t>
-  </si>
-  <si>
-    <t>More than 200,000 people bought Equity for Punks shares in the craft brewer but many now believe they are worthless.</t>
-  </si>
-  <si>
-    <t>https://www.bbc.com/news/articles/c795879x08go?at_medium=RSS&amp;at_campaign=rss</t>
-  </si>
-  <si>
-    <t>Cynthia Erivo ignores online criticism as Dracula gets mixed reviews</t>
-  </si>
-  <si>
-    <t>The Wicked star appears in a one-woman version of the classic horror story in London's West End.</t>
-  </si>
-  <si>
-    <t>https://www.bbc.com/news/articles/cqxd4r4xzx1o?at_medium=RSS&amp;at_campaign=rss</t>
-  </si>
-  <si>
-    <t>I hated my appearance. Here's how I learned to accept it</t>
-  </si>
-  <si>
-    <t>Tilly and Charlotte share their experiences of body dysmorphic disorder and how they recovered from it.</t>
-  </si>
-  <si>
-    <t>https://www.bbc.com/news/articles/cre2pelrpwzo?at_medium=RSS&amp;at_campaign=rss</t>
-  </si>
-  <si>
-    <t>Letter by young Queen Elizabeth II to be auctioned</t>
-  </si>
-  <si>
-    <t>The letter from Queen Elizabeth II asks if "the birds are well, and the goldfish haven't died".</t>
-  </si>
-  <si>
-    <t>https://www.bbc.com/news/articles/cp85v315zvjo?at_medium=RSS&amp;at_campaign=rss</t>
-  </si>
-  <si>
-    <t>Zuckerberg arrives to testify in social media addiction trial</t>
-  </si>
-  <si>
-    <t>The billionaire Meta chief executive faces questioning over whether use of Instagram harms children.</t>
-  </si>
-  <si>
-    <t>https://www.bbc.com/news/articles/c5y42znjnjvo?at_medium=RSS&amp;at_campaign=rss</t>
-  </si>
-  <si>
-    <t>Plan to increase youth minimum wage could be delayed</t>
-  </si>
-  <si>
-    <t>Government sources tell BBC News they could slow down plans to make minimum wage equal across age groups.</t>
-  </si>
-  <si>
-    <t>https://www.bbc.com/news/articles/c5y6g57j3meo?at_medium=RSS&amp;at_campaign=rss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Climber on trial for leaving girlfriend to die on Austria's highest mountain </t>
-  </si>
-  <si>
-    <t>Kerstin G's boyfriend is accused of leaving her unprotected and exhausted close to the summit during a blizzard.</t>
-  </si>
-  <si>
-    <t>https://www.bbc.com/news/articles/c5yv9plyjgpo?at_medium=RSS&amp;at_campaign=rss</t>
-  </si>
-  <si>
-    <t>Man who threw corrosive liquid on guest at spiritual retreat and fled country is jailed</t>
-  </si>
-  <si>
-    <t>A wellness retreat owner went on the run in several countries after throwing liquid into a guest's face.</t>
-  </si>
-  <si>
-    <t>https://www.bbc.com/news/articles/c4g82znj294o?at_medium=RSS&amp;at_campaign=rss</t>
-  </si>
-  <si>
-    <t>Otter cubs rescued after sheltering in car engine</t>
-  </si>
-  <si>
-    <t>The tired and cold cubs were taken in for the night by Karen Watson, who kept them in a cardboard box in her bathtub.</t>
-  </si>
-  <si>
-    <t>https://www.bbc.com/news/articles/cpw0zrn919po?at_medium=RSS&amp;at_campaign=rss</t>
-  </si>
-  <si>
-    <t>Wave of arrests over killing of French nationalist piles pressure on far left</t>
-  </si>
-  <si>
-    <t>Eleven people are in detention in connection with the killing of far-right student activist Quentin Deranque.</t>
-  </si>
-  <si>
-    <t>https://www.bbc.com/news/articles/c62dzgy0q37o?at_medium=RSS&amp;at_campaign=rss</t>
-  </si>
-  <si>
-    <t>GB's curling medal hopes still alive after double win over US</t>
-  </si>
-  <si>
-    <t>Team GB's slim Winter Olympics curling medal hopes are still alive after both the men's and women's rink edge out the United States in Cortina.</t>
-  </si>
-  <si>
-    <t>https://www.bbc.com/sport/articles/c0q3nejy1pjo?at_medium=RSS&amp;at_campaign=rss</t>
-  </si>
-  <si>
-    <t>Hamilton finds new F1 cars 'more fun' to drive</t>
-  </si>
-  <si>
-    <t>Lewis Hamilton says he finds the new Formula 1 cars this year "more fun" to drive - in contrast to the views of Max Verstappen and Fernando Alonso.</t>
-  </si>
-  <si>
-    <t>https://www.bbc.com/sport/formula1/articles/c20z9wlw1vpo?at_medium=RSS&amp;at_campaign=rss</t>
-  </si>
-  <si>
-    <t>'It smacks of England' - Australia fail again at T20 World Cup</t>
-  </si>
-  <si>
-    <t>Muddled selection and the lack of a plan B - how Australia's T20 World Cup campaign was derailed in Sri Lanka.</t>
-  </si>
-  <si>
-    <t>https://www.bbc.com/sport/cricket/articles/cqxd4rgr99qo?at_medium=RSS&amp;at_campaign=rss</t>
   </si>
   <si>
     <t>ModaLisboa regressa ao Pátio Galé para mostrar a moda enquanto forma de cuidado</t>
@@ -1715,22 +1718,247 @@
     <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPUE0yR3I5bkMzZDVvZlJIVk1ZSTBPa2YtRWswcnBPMXJrRElHRHc4VUk5b3ZWclZUcWNhcTdyaWVYcHhIUXdMWGJEZUhETFRTQUYwSjBhS1lkLUY5TGg5Y3RNU3RZWUNpRVJDX3RTdFlXZEN0MDZvNl83MGdYR3E0TVE0U0k?oc=5</t>
   </si>
   <si>
-    <t>Numb to the Numbers: How Normalized Debt is Putting Canadians at Risk - Yahoo Finance Singapore</t>
-  </si>
-  <si>
-    <t>Numb to the Numbers: How Normalized Debt is Putting Canadians at Risk  Yahoo Finance Singapore</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQdEIyYTdWVjdDRFhDaFpuU094TGttVXo2RWlNdi0zLXprUzM5U3hyZndpUW5fOFdjMjRpaTk0dGNqcHM4OE5mUGZMelpIaXkxS2RsalpocmVjRVMzMjFSckdGaDNVTmZkc0pKYTdSQ3ZJeDB4QVRYTGltcW5fR013c0R0NThuY0tBX0FiQ0oyN3Y2cDVO?oc=5</t>
-  </si>
-  <si>
     <t>Billionaires’ Low Taxes Are Becoming a Problem for the Economy - The Wall Street Journal</t>
   </si>
   <si>
     <t>Billionaires’ Low Taxes Are Becoming a Problem for the Economy  The Wall Street Journal</t>
   </si>
   <si>
-    <t>https://news.google.com/rss/articles/CBMipANBVV95cUxPYm8yYlNYbjdHOWhtZ0dQN1FGSm9oa19fSHFGQ205YllrS05CbmNjeXdmMzBBWndaTEZtaXlhQW14NFZQQmZkcFZJVWlOdnpRZHhkS0RPQmlpZk5lZnRnaG84Z2JMeXNtd0M4QmNvdXpuNHphVEhybjRqTUNlV3RuWk0tZzBwbEl6aG1ldDFRbzJ1QTduODdwbjNEb0NESkdJS1JjTm9WaVVfM3gzSGk3VTdxLUE3bTNkTXFlVWZjd2lEY2x6QWFxLXhveU13MGZMd2I0M3NWQWQtUEVXakY2UFNLUDN5bGVtVk15UWRVNTBzY2xBeUJadW04U1FFcnFZNndqazlZWk9ZN0VIWTdLcjBVNDY4UUdhMHFaMFY4NGRicVlnYlRSOXhEcWVla2VMV0xLbWUxXzdDYXY3RXJraVpwY1JlaHNLcHlRb00zbUNIQVVUcG4wdGZ6NWtJSUpjSmNRd1JPYWR3YjJoa0Y2QUVUQWl3Z3ZvWXhYa1Z1ZXY0a09BNTBJV3lBSVRlMXFCN2gxRnVWSnh3RVVaTnJVeHFVenQ?oc=5</t>
+    <t>https://news.google.com/rss/articles/CBMipANBVV95cUxNNjVTREItcVAtQk9uZksyTWQyUUx5a1Vwc2VWRllHM2FzODNVWGQ1RkQ5NnRaRTAtTzRFd1c0U01ReksyRmRrLXFHRUl3V3VlWHdTY0RJVW94Y1RPT25RSVFrSFdaWE5NZU9kMkhVMU44Sm1EMU5KTGNXTm1ZaDJzZldFV3hkakJSVzlaVm1UeldLOWtsZFRxNzBVV0hYOFFNVWZ6aE9uNzN1V0FiTlRLNk95OWFaVEdmekF3WUtCaHZJNmx6bFoxczJiVF9qVzJYZVZYSlh2dDdtWTJYQnR1ZTlwazU0ZVJTYjZZQTBZRFNjcDU1R09LR0stWHVVQnN4dENaMTMyY3ZPS2xSTWFZUkFSNDZiWHZGM25QVXBwaXE3SkhEM09xQ0QyZ2VqaXVoQUNydHNiNEFjQ1M3NmY5b2hCVnZWX1dYUmxhY3I2THhyekxXa1d4NnBIYlVYRXo1OElzd1hCamhXdkJTcklnemdSNm5pSi1FSVNJaS1rbHRqa3RvM0ZMTThNV01RLUdkWUNPVndOQ3JJdHNqakNDdmNKa1Y?oc=5</t>
+  </si>
+  <si>
+    <t>Apollo-Backed Fund Lends Wayflyer $250 Million to Finance SMEs - Bloomberg.com</t>
+  </si>
+  <si>
+    <t>Apollo-Backed Fund Lends Wayflyer $250 Million to Finance SMEs  Bloomberg.com</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPQ0FVYnZGaXlNek51bTVtd25PaWJqOFZZWmJqVF9qNUtTRjJIUEhRWTJtNG81YjVUUmZJMHpzWjJUXy1KQWJXUTBUelNxNV9tZGd5ZUtHa21CT2dGWGwzZTNwRWl4em5COWpNdjh4ZXpCWnVTNXpoME04S2R3cjdkSFluSTMzSmxJQ09VZWRsQjFvdXNnRUM0QTdCMTAzNG41YVR1Y2pjd0s5S1FCdHlXUllB?oc=5</t>
+  </si>
+  <si>
+    <t>Economic Sector Performance Dashboards - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Economic Sector Performance Dashboards  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiSkFVX3lxTE1aZHRnWXJQdlUwdmU4ZExFUzhEVXA5TXBHSFBsNS15TzJCSWtfMGRtU09HNENQMl9mTzlBenQyVmtTOFBKaFJDQ2ZB?oc=5</t>
+  </si>
+  <si>
+    <t>Coffee &amp; Donuts with the Mayor and Finance February 28 - City of West Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>Coffee &amp; Donuts with the Mayor and Finance February 28  City of West Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNR2VZNUNzbDNRYWNJMEVURm53elA3TU85SVdudUIzQ0Z5OTROdG44dXB5WlpqbkdPNHNSb044eHFvODZzQXJFTGJpM3NaajkyTTNid3ZVNjg0WldTaHA2eW5vRkdaWVBRUEttQnNqaGE4STFEZF9LQVhlRHdmTlc3ZVRscXRkMExyREE?oc=5</t>
+  </si>
+  <si>
+    <t>Governor Moore Testifies Before Senate Finance Committee in Support of Legislative Agenda to Make Maryland More Affordable and More Competitive - Office of Governor Wes Moore (.gov)</t>
+  </si>
+  <si>
+    <t>Governor Moore Testifies Before Senate Finance Committee in Support of Legislative Agenda to Make Maryland More Affordable and More Competitive  Office of Governor Wes Moore (.gov)</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxQM1pHd3I0RG5XejdpVWJEcUxramNPeU1WOUxlU0MyczlaS0pLMUw2Tm1nSVQzcGNPRWpQT1I3cXVLcXBUaUpYcGxGSkg3OHp1U3Y2eDZhV2RtRV9FR3J6QUV6Y2hyblRGeVNkdU1HT0ZEOFc4Q1RhREJCN29JVlptRzk2TWZoaHhncjhwekdHb0xTVTFMMjBDUnl2QmtqOXBpUmgyaUlTaE1XeW5WOVJDaWR0X3NPaXZieDd3MjREM3NCYU0wSzBWVGptbDhUWGIwcVFDUHdvTmhRdnBQd21HazlmTDRBUGx3VDdrZE02b01PZG1JeFpLMlJPTTd3Y21DSFNIZ2Zn?oc=5</t>
+  </si>
+  <si>
+    <t>Avalara Recognized on G2's 2026 Best Software Awards for Accounting and Finance Products - PR Newswire</t>
+  </si>
+  <si>
+    <t>Avalara Recognized on G2's 2026 Best Software Awards for Accounting and Finance Products  PR Newswire</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOOExlVW1PTkhpeVRVeVJqS1A3WVdydlhPNGx5cWhmZS1TQ3pBM3hnZGZwSFhkVWtnRnlRNm1tcnlySzVnYk5uZVRrbVNSV3BMQXEwTkhJTTZweVlZVWpxcndnZ0pxcGdhOTBJQ25MY1lKcm9WdnZWaldvMVR6cnhCNEl1aVBaVDRrTGgwMmVHMl9jQVIwc3pZeHVVTGVDb2hpZTAwa3M0MFcwRWhuaW81R0JIY2JEanRpc0c0aFB2dGs0OTZQSDhIVUhHSjByeWFuMEZ0eHBEbzVIX1k?oc=5</t>
+  </si>
+  <si>
+    <t>Program - Milken Institute</t>
+  </si>
+  <si>
+    <t>Program  Milken Institute</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE9rdkpHVDFFMmpRcTFFc0FlTnJ2bElINVdKNm1OeDVVWXVVMl8yVnpETHpKalVCc2o2T3NtSVhVWlBodzBVdFZycTQ5MksxbWFIbXh2eC1wbWNOMUt6MkxQcHdiTFdxZFBhQ2JQUFNKUQ?oc=5</t>
+  </si>
+  <si>
+    <t>Konica Minolta Wins the Bronze Prize in the Seventh ESG Finance Awards Japan of the Ministry of the Environment - Konica Minolta</t>
+  </si>
+  <si>
+    <t>Konica Minolta Wins the Bronze Prize in the Seventh ESG Finance Awards Japan of the Ministry of the Environment  Konica Minolta</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1XVnlJT3NZTlNITVVJU2JrUV9yejAtMTIxa05DXzY4ME0zWVBoRTBvOUduLWp1OTR4N21EbkdOa1VCQjBqYURmUUpVQ0p6VzZSX1BfMENPRTBScFpFSGxsRGloZzlPY1pVak9qNWNiMmVfLWNVdzhXVQ?oc=5</t>
+  </si>
+  <si>
+    <t>New Climate Finance Initiative Supports Climate Adaptation Efforts in Glacier-Dependent Regions - Columbia University in the City of New York</t>
+  </si>
+  <si>
+    <t>New Climate Finance Initiative Supports Climate Adaptation Efforts in Glacier-Dependent Regions  Columbia University in the City of New York</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOMTN2TUpQT0dqaGR5VU9SSng0YzJibE1DZGdJOUVVWm4xM0RDVkUteVBpS0lZb3k5VDhxVEsyekNWNXUzR2YtN3pOV2hNRDQ4WVI5VHpyaDNnVXNmc21CNlh4SDdJd0V3V3dyWU9hc3VObGotYmZvQzNrWVRRTUFCSUVTU2Zial9JRWU0c1ZNZWw1eFFCdmxFZ2JxdDJkLWNxa0NEM2lFUlFtdkNHSjZQeWUwNl81TEJCdkY4QnVwb2JIRmE4ZGlGUVNaQ3FFN1BIb2k2RG5FbU8?oc=5</t>
+  </si>
+  <si>
+    <t>Women in Securities Finance appoints Hill Sands - Securities Finance Times</t>
+  </si>
+  <si>
+    <t>Women in Securities Finance appoints Hill Sands  Securities Finance Times</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQMjJkLTZVcm84eTNLM3RfeFl2d21odEx4ZlJSNUtUSkpPVzVockVkRmtOY00xcGg4VFltTXNoUFJRVkVFX0habzNBMlZNN3RmODJLc0R6djdOOWkteGtPb3FfazcwbUQ2MDlUTjNTaEJuM0IycDdKSUJHak5LbFNxeEFDMGVRWXJYTTFsQlRoRWcwWlQ5X1FQUnVEend5R1B2ejUw?oc=5</t>
+  </si>
+  <si>
+    <t>The Real Bottleneck in Finance Isn’t Payments. It’s Settlement. - FinTech Weekly</t>
+  </si>
+  <si>
+    <t>The Real Bottleneck in Finance Isn’t Payments. It’s Settlement.  FinTech Weekly</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOR3RLRlRYOFVvWE9LX1c1UzRubldLcjg1eXpSbXE3YlNvb2U3ZVdQZWZFVnBYOHhWYkNSN0JKZ2t0MFdSRGVLUmRtYmFxbUEzM0hBNXFmYlJJbEZZNUMwbkpFazNVNUdTTklFVmg4N3NGX2JUWDFpRV9ScXRRWG9pa1A1Q1pxc093U2c?oc=5</t>
+  </si>
+  <si>
+    <t>Symposium on International Investment Law &amp; Contemporary Crises: Energy Finance Market Design &amp; IIA Claims - Opinio Juris</t>
+  </si>
+  <si>
+    <t>Symposium on International Investment Law &amp; Contemporary Crises: Energy Finance Market Design &amp; IIA Claims  Opinio Juris</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNdE85WEhsdkw2YTBwVW14aklibzR3X0pLUVVkZEVlM2xjNEFzRXBzMkVINmQyc1VZMExFV0R1WmRCZHlac2FzQS03djdrSk9SdU1sM1ZOS2JlSGRGS0RDU3lQaktUNlBPN0VVclhWbjdJUXdkalVPM0stRXp4S3luVUJRNkVyV2NnUVpoTHhQM2VVV3F2QzBfT2VUNDNyVENwQWJyNV82TldkZE1ITnNiWGVhRGM1TlA1Z3NPcHJ4Rjg4S1pSeXFXNjc2Wlh6X21obUE?oc=5</t>
+  </si>
+  <si>
+    <t>AI adoption already hitting Irish graduate jobs, finance department says - Reuters</t>
+  </si>
+  <si>
+    <t>AI adoption already hitting Irish graduate jobs, finance department says  Reuters</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNY0ZlYUU3ZWpFUFF0WEk1eXRkc1ZwbUduSUpVdjJoeXdLeWhJVnMzV0taTk11b0lpeklmMzZBM29YVmd6V3dqWlhENkJnZ0dRRjdNSWd3TVV5dURwbUM3QjFzem1wSHd2Y0Y2aU5GWFcyS2tSR3RsTmVfQ1ZzWWFvbU5Ld05YYlBiTVNmMm5rVGxHVEVDcjJzUVM4RjZxQ1gtbWp5clFFalNZbmtMWThuZzFDczlsSjA?oc=5</t>
+  </si>
+  <si>
+    <t>How Credit Cards Keep America’s Small Businesses Running Strong - U.S. Chamber of Commerce</t>
+  </si>
+  <si>
+    <t>How Credit Cards Keep America’s Small Businesses Running Strong  U.S. Chamber of Commerce</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOOEZRTVRzZlF2RzVaVVZXdm55a1JWRzlHenl6OWQ4czBNa0hLbFF1dWdFMXI4RExnQVhmQWpzb2tEanNvNEU1UzQ5ZXRhaXgzY3BUazl3WFdkb1VwMGowMkl2eEhoT0x1djA1LVltOTZOWlBTOXQ5YzItUkRLcmhXd0RvRHhkZi0tZERvX19FWUpEazZwdHlhVDZZekk?oc=5</t>
+  </si>
+  <si>
+    <t>Troutman Pepper Locke Weekly Consumer Financial Services Newsletter – February 18, 2026 - Consumer Financial Services Law Monitor</t>
+  </si>
+  <si>
+    <t>Troutman Pepper Locke Weekly Consumer Financial Services Newsletter – February 18, 2026  Consumer Financial Services Law Monitor</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPUExOOWVkYWxmODJERVdlUlpCOFhXdDFmTXVWdW54TnFhOWZvNUdBWERLVnd3aXR5aFNwaHk1QnVSZVREVzkybjhoemhPYTNhVkZQdFFlelJmS19vQV9ZNWxVVE9SN05mVEtaVDV0b1ZvNHRXazI0TmFLX1c1TFVkNnUxVExBbnFCVWZwLTA0NTJFS3BjRWk5TWRGa3JHRTFxa2JfSm11WC1OdEtEWHZ5Mzc0V1NXSC1mVW5HUUtjTlJ2bGpQOEIwUzlmcGF2dXNoMHFzTnVLeVM3RXBlOXc?oc=5</t>
+  </si>
+  <si>
+    <t>BBVA welcomes Shepherd - Securities Finance Times</t>
+  </si>
+  <si>
+    <t>BBVA welcomes Shepherd  Securities Finance Times</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxORVBDSXlvSTBQR0w4WTc1WkhzNDdGMmhuSWlpOE82Mm5uTnBNVnBUTUJSMWVuNUp4OXVGdV90M0pZelBNcXBUdmZOVWQtVlN2eWV4bFpBSG1ZcFN2eHNSS1hJam90R0dRWXRROEtsLXlRMTVWcFJtVGdSR3FpNWZkRjN4ekRlZUU4cEJvTmtUUVdwLS11T1RuN1F6UWJxcFJ5UXBZ?oc=5</t>
+  </si>
+  <si>
+    <t>Earnings live: Palo Alto Networks stock sinks after company cuts full-year forecast - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Earnings live: Palo Alto Networks stock sinks after company cuts full-year forecast  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQVWE1S2hNazUwaEp3UTQ4ZWcwY1FXY2JnVG4yQ2ZQeTRVdUxKdVhFcDBDZnFzTmNNRUFIMWJPek80ZTNKS2VqWFAzTEVPXzREN1kzQnVzZkdvMG5qN1VOR2dVNFBnSzdEaGVUUmI5TGhBbGFwQUJIVno5bHc0YzdBck9SNjRBcnNwRndFTFN0dGFId01wVlU4bEhGOUNSRUN6aEIwNnByeGJnd3FiM2ZXMkQ4X0FnZ0xQeHJlRWd2UFphNFBIeDBDNlpVeWNOQQ?oc=5</t>
+  </si>
+  <si>
+    <t>Nvidia and Meta expand GPU team up with millions of additional AI chips - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Nvidia and Meta expand GPU team up with millions of additional AI chips  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNaEc1R3NCLTZRdDgwVWd6UDR5ZXB5SXd4Q0c2dlBUbVpnT1ZzRU8xMnh5bWNEa1BuS25zRHg3Qk45OW1QaVk3MlE1MEhta25icVhvYkw5UXd0MjU2U2gtVmljdFBrMzM1X1FKQzRPNG9uVllMb0lRSXFvQWx3TWFmaDAyaTNIMFhabl9maFdRek1jcVpBOEJaeFMzbUgxbF82dXRKTjVCZzRqZm9iNkUwbjNyQmZ6WkYw?oc=5</t>
+  </si>
+  <si>
+    <t>Chicago Atlantic Real Estate Finance Schedules Fourth Quarter 2025 Earnings Release and Conference Call Date - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Chicago Atlantic Real Estate Finance Schedules Fourth Quarter 2025 Earnings Release and Conference Call Date  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNazBfQm5fMm1UTGZMVF9JQm5FLXNnZHpwekp6R3lNQTk5aGYtd2J2eW9KemNpSHZWNzQtVVZ6NU92dTh6eEFSOTZ5NThjeV9yd0VXMU43djVCQTBLYUhJeks1b2xXX21HYXdVNjFOdzNwZDRrNmlRX1dFTGNyUjYtMHZPUUVaTWo5bWc?oc=5</t>
+  </si>
+  <si>
+    <t>Unlocking Finance for Nature-based Solutions in Indian Cities - Climate Policy Initiative</t>
+  </si>
+  <si>
+    <t>Unlocking Finance for Nature-based Solutions in Indian Cities  Climate Policy Initiative</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNbE9VZDZKVktsajJEVG0yM1ZfWEJ3Ums3RHRTM0FOZTFEZnFwa1NFSXBSbXpLMUpzNUktWGtqSzRVN052RllQUDNMY2x3TWlFSnNUS2VyNzF5X05ZWmx1MTlYSVlwOS05WDhjcmpCZTBacHc1Q29Ba2lZUkVuclMtaFJ6ejI3Z2lkMHVYdEFJREJIdXF2ZUVXT0VMMlFaLWRoeHFKY2xMS2syRTJWZDVQaVRraTQ?oc=5</t>
+  </si>
+  <si>
+    <t>Stock market today: Dow, S&amp;P 500, Nasdaq rise as AI worries recede, with Fed minutes ahead - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Stock market today: Dow, S&amp;P 500, Nasdaq rise as AI worries recede, with Fed minutes ahead  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQcEhkYkxjdlVSbDVfTk83VmVuZ2pVTmgzNjFsRFRjc0VqelNPX1c1RFZ4am1Ra3U5TUlVWnFNTVZkTlNTRGpzanNCcUVybTlGNHNMaXR4ajc4VVZqbW55cFp5ZWJlR3NGZmM1OFEyMmFqblBQVmNwdkdLRzRSMWdfVVpwZmYyRndHczgtOHYxWTNSQ3V1WmkzcTJod0d6X0pmY3B2d0ItTmx1OWpCenVtdzUtc09PeW1JWVgwcDQxYUJIZktZRHBGTC1idnc2cFFINVE?oc=5</t>
+  </si>
+  <si>
+    <t>Snap Finance Study Finds Majority of U.S. Households Delayed Essential Purchases in 2025 as Credit Pressures Persist Into 2026 - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Snap Finance Study Finds Majority of U.S. Households Delayed Essential Purchases in 2025 as Credit Pressures Persist Into 2026  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOTzNzdHpaNkF0TUlxNHJwdGtIRzQzdTBlNXpkUWRTbVdna1M0eE1IU1NvS1otYTAzVEFub2lvVWlKeHd6QkY3RmJ0T3NqSkVBX29Ya25DbkNydnZDRG55OGxDTksydXo4Y3JWSXNRd1U3UUY5Zm0zdlExbDVkZkxzVmxlU05Rdw?oc=5</t>
+  </si>
+  <si>
+    <t>Lightrock grabs an exit opportunity from Indian small business lender Aye Finance - ImpactAlpha</t>
+  </si>
+  <si>
+    <t>Lightrock grabs an exit opportunity from Indian small business lender Aye Finance  ImpactAlpha</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPbW5lcmJoSERuOFp0MGYzaHJXS2Q4c2FTNUgyODYybUlOZ2JKUlVLcTcwYlRoNmRxbC0tejNBZXFaSHhEaTR2Q1VDT1BEREtLWjhiM2JDSFFpM2JGMUYyazI4a2ZkTm9Ja2pCRmNtcGhqTlJzcFowVlNKWmxtOHpSR1g1X1hEaXZyVXB1Y0ZlYVlkV3N3VTVTT2U3Y1ZKMHE2VkNSeHpKNWYtUQ?oc=5</t>
+  </si>
+  <si>
+    <t>OPENLANE, Inc. Reports 2025 Financial Results - PR Newswire</t>
+  </si>
+  <si>
+    <t>OPENLANE, Inc. Reports 2025 Financial Results  PR Newswire</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNZ3FFQzNzUG81QkNjTDgycHBKSUh3NURtVi1WUkR0cGFoODg3LUFyX25YYjVYNFIzU0U2cW9YT2pkcUNxTnpWb2VoUFpGTGI2N2I0Y2tmZ1hwWVlQRzhNVU1LdnBzYkx6QUpKSlRLQmJiMHFuV0NSNkhpTEZpVTIxeTRwVmUxc2c3S01fYnVWZVJDR2Z3VzlvV2MweUw0bXJk?oc=5</t>
+  </si>
+  <si>
+    <t>Are Finance Stocks Lagging Barclays (BCS) This Year? - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Are Finance Stocks Lagging Barclays (BCS) This Year?  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPbkt4OTRYNGtDSjRKUTF5Y3hVZ242YzN0Nmlub0kzMl9KbnRRU00tMHdLVEl3aTY0V0Y5QWFzRDAtQ0M5WlVGV3ZxV1NzN3VpaWt2UVhVNWZVTDlScHA1bzg5TFlpN2p4Q0FGbHVhVVNuaWNzOTVQMTVoeklfR1hOT3h0R1ZlYmpQ?oc=5</t>
+  </si>
+  <si>
+    <t>West Virginia Senate Finance Committee approves appropriations bill for Hancock County Schools - News and Sentinel</t>
+  </si>
+  <si>
+    <t>West Virginia Senate Finance Committee approves appropriations bill for Hancock County Schools  News and Sentinel</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxORmNQWEtJSnc0OEQ2Yl92TldtMHJrVEdaZUdNdHNvb0pWdmpLcGdTV0xXZE5EcmJsWWFLSmxaOENUdUFqel92bTRjZ1g0TU9uLXVHTXNTY2x0VmVYV1Y4V1p4RTZKVDVNUGZHY0l3V3dWdmtuVGxMcmtOQVpralpLaDdGNXJ6OUt6dEpsMlNHQzNSOXpsclJBX1lOMXYzdkptaGlJRkRhNVdIaWowc2pFTTM5VlRFVlJsM0FCaU81TDl0by1fVVRCcUhYdThWYUdJbVRwUElna0hEVjQtM0NhYUlBcUtBUQ?oc=5</t>
+  </si>
+  <si>
+    <t>Analog Devices Reports Fiscal First Quarter 2026 Financial Results - PR Newswire</t>
+  </si>
+  <si>
+    <t>Analog Devices Reports Fiscal First Quarter 2026 Financial Results  PR Newswire</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPdk5GakFqU2s3RjN1N0VIb3RsZ0ZPQ1NqRVFXZXMtZ1QtV1AxWUxzWjVDemJrQmppMm9WTWZyMk5COVRDUF9WWk9zalhYamlIaUZOMlRVMTF6SUNJMnJRWEFZQ2hEeUVXb0dRNUpsdk9ydmxEVXlVcW9OdUhQX2VmNFpyZkJvQWdob0h4VzlWMGJKWTFUVTJySXZ0NGhJdmp1SWdVSGZLUkoxaFVfMEJoTG43QzZuYTlkTXRsNF9NWQ?oc=5</t>
   </si>
   <si>
     <t>Financial scams are on the rise — but what’s being done about it? - The Hill</t>
@@ -1742,6 +1970,276 @@
     <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQbFU0OFZxQ2tVdlpqamVrdldYbTE1N0NkOWw4RjlnQ3lDaFVIanpfTFNrbllSVWMySl9DS0FmZzlWSDRCTEloTEF2Vms5QmRPaFpJcjM0T3RTa3JtY3UtbW1tVlpHQkxYYWRlTTI4NWMwaXp2SVdYZDdZUlRYMHV4RmVXWdIBiAFBVV95cUxOZ1ZOWTllSWJKWEFaLTl4ZEk4LUx5dzl3M2tiMEhKZWhLb0dpaW16QnJ3RzRudExGS2NPeGZjYVVBbnItVGxfNE1pWUxyZG1SMmMxSEdxSVhIZndmM0FpRDdTbFFrNHluWVh6a2M5T3RRT2FsdkdJdlhJaGc1WXp1dVNFNXhlQ2hI?oc=5</t>
   </si>
   <si>
+    <t>JPMorgan names Catherine O'Donnell head of North America Leveraged Finance - Reuters</t>
+  </si>
+  <si>
+    <t>JPMorgan names Catherine O'Donnell head of North America Leveraged Finance  Reuters</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOWEpseFJwUG1ZQno2N1VKRENxaUhBQjIyWDRwTHZSVXJmWGNndkF6dkxITFJkMENyb3NVMjRwaXRPOTd1TnU1LTNXdzdWTk55Tmk0b1ZzUG5RdzBEbGJWbXFOY2hfaHl2QldMdUF6RmhfdGVqMXhibk03cGNXVmVZaDVMUm92N0d5WWZkVHFuc254cGpMSG5SOXVBRnpNLVQyRWE3MjNxTlFvY1dkbkIzb2ZmSlk1eDZrb0VkRUpQcmQ?oc=5</t>
+  </si>
+  <si>
+    <t>Will investors buy the transition bond label? - Environmental Finance</t>
+  </si>
+  <si>
+    <t>Will investors buy the transition bond label?  Environmental Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOaFF0YzF2bWd3eHM4WHR5NHVzSlNRNTFUYk1QLWxCbjd6V2dzRkxHU2ttOGxsV1ZPVEtxTnBscVNLYjFYNGtEUGhIRzNaMUNUVGxaZkkwY2hOd1V2VVN0Y1RfM21SYXdnUlJtdktzWDkxN0JVTU41c0xuOTFrTFM2LU1jellYOTNaTGh6NGJhOWpXSFRxUnZZcG12Q3pVZV9sSHU0TnBGYw?oc=5</t>
+  </si>
+  <si>
+    <t>Gator Capital Management’s Investment Thesis for TFS Financial Corporation (TFSL) - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Gator Capital Management’s Investment Thesis for TFS Financial Corporation (TFSL)  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQQVpxUHI5eVNWd1FLVmJEdmtqbFd4Y2FfenVZbnNyVGdIWjJKM3VBUURxSVVRMi1tQjJPUWVaX2d2N051QVpqV2kzb05TdFRPcWpyejNKWDExUVRQUjFBX280MGRuM3BhZjNwYXR0N0pwOFlzN3RFRTQyM3dFRVdnVFdIMGZrMWFWSUY5YWs5dkJqdw?oc=5</t>
+  </si>
+  <si>
+    <t>2026 Africa SABRE Awards: African Development Bank’s access-to-finance “AFAWA: Banking on Women” communications wins top global campaign honors - African Development Bank Group</t>
+  </si>
+  <si>
+    <t>2026 Africa SABRE Awards: African Development Bank’s access-to-finance “AFAWA: Banking on Women” communications wins top global campaign honors  African Development Bank Group</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMingJBVV95cUxPNFVQU1NQV2VGeEtVMWFlUHRTa1ByUFUxV29fZ255Xzk3eUR2UUJpVWJuU2xGd09JYTlWaWM5ejZza00wM19QMWZSYjU3THlVSGoyU0ZXdGRpYktEeXJOMzZ2N2VkblZZQjd3emkxU2l6eVJ1amdabGlwelhlVE9fUUhhM1N0MEJaUXJsRVg5WGVpeHlDRGJyLWZiSXkzWk94OWxBRTdrYlJhdUdvT0dmalZka1FTT0FGb293dlo2M2kyZ0psR3NDbDM4SXRSZUFRb3c2NGJlbzhxMk1vckFnZlhwMjF1WkFMc0djc01kd2h4eFZ5dG5uZUx0ekFKR3FBbzJucHI5R0pMQjYySTJkUEVGNTR5cGplOVQ4WUJn?oc=5</t>
+  </si>
+  <si>
+    <t>Tuition, financial aid rates set for 2026–27 academic year - University of Rochester</t>
+  </si>
+  <si>
+    <t>Tuition, financial aid rates set for 2026–27 academic year  University of Rochester</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNclRRcDI0YUNSbzR1aWhpc29FZVBtT0ZZTlkxRXpkdjUyZXJfN0NBSTZjaFJLeDIxbHFNS2J0NWN6QURmZDI5OWg1NHdSYzVzTlhzbDM2R0gwVzNiXzJkWlpjcTlQNVBNOGpFc1BSbTRVQm81V0dfeDRQZzRJRzFNdmNKT3A5OC1qclB5dkxCaWNBOWpWZlBCOFFncw?oc=5</t>
+  </si>
+  <si>
+    <t>Gorilla Technology Acquires Shackleton Finance to Establish Regulated Capital Platform and Fund AI Infrastructure Growth - Investing News Network</t>
+  </si>
+  <si>
+    <t>Gorilla Technology Acquires Shackleton Finance to Establish Regulated Capital Platform and Fund AI Infrastructure Growth  Investing News Network</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPNmZQaXZmQVBnOURjeVFnZ2Y4U3U2MU1LVHRQUTdMLTUyWXFvM2htN3RJaVQwQmU2M203N2x1SkYwNVhtZnZ3QXNqNDZEVzU5N1pmTUhMX096M1ZhMUd2U2p6VXNrMWNnX092TEhMVUNQbWlua0JOc1hFYkNST1BzZ2E4cW95TVhCSDltX2xZeXJYUzY3Q0JZckxMUkQzUUhVX2tVc1YxbDg2WWhZWXd2YkctWEd1ME5qbGcyY1RTYl9tcWFSVHZUOWdtZTl3SkZoWU42WlRuTm9rWlRRZG8zaw?oc=5</t>
+  </si>
+  <si>
+    <t>Stock market today: Dow, S&amp;P 500, Nasdaq futures rise as AI worries recede, with Fed minutes ahead - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Stock market today: Dow, S&amp;P 500, Nasdaq futures rise as AI worries recede, with Fed minutes ahead  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQQWYwUXZORzFQZ1lfcUhPRnZVODdGLTdXbWRtVjVCVXRaV0dRQ2ktQmVYUXhDV0hULXFBclcyeDcyc0FuamRGdkI3SDRHYlFSa1JNa1NDSzM0engwclZWTnBqZmNYa0stRl9vcllHQ2E5cEZBc0hveVZ6M2MtLVBLTC0zaV9uWEVRYnpCemYwSUxuYlNiZ0VhRXl2c2RQblIyY0xFY2h6WElsbFJ5LXZaVUtpN09yRS1uTm9PTEFVQTRjSW5iNDNWMUVFRkhiNl9USXRyYV9BRVpiZ1ll?oc=5</t>
+  </si>
+  <si>
+    <t>Finance Chair Warns of Prediction Market Impact on Sports Gaming - State Affairs</t>
+  </si>
+  <si>
+    <t>Finance Chair Warns of Prediction Market Impact on Sports Gaming  State Affairs</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE04U3ZjVE9SNjRpN0hGSkEyNUNqdWMwclFieHV0UlpZNHdGRV9lSmdrdVlhcnVaSHJmQ3lpb3J6YnBnS2p2VEN4R0xwMjJ0d2NkNURTNFNpdzFOZ2xPTmppdGFxOFNJQTh2WHFFRTNxeGY1YkpXX01sWTJOUVBUNkE?oc=5</t>
+  </si>
+  <si>
+    <t>Morning Bid: Changing of Lagarde - Reuters</t>
+  </si>
+  <si>
+    <t>Morning Bid: Changing of Lagarde  Reuters</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPbExHYkdzZWlmeWtDWkJaVGtsV2ptaFRRT0tkT2l1cW9FMDN1NXNHdmoyWEFkN0JPakhxX2l1WFVWMlJ3M3NBNFplM2dwZC16OEl0MjdzYWVMcXlObGJMT2RsTExOaGNYUXZoVkVzcVZpUWR4V3VFYjFnb1NkSEFEUERB?oc=5</t>
+  </si>
+  <si>
+    <t>Medicare Advantage growth slows - Healthcare Finance News</t>
+  </si>
+  <si>
+    <t>Medicare Advantage growth slows  Healthcare Finance News</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5pQnk4Q0VjOEViR3Uyc29jUVota3pxNjFkOHVDOXJYX0RzNjA4TWxVVkd2NnRFU09oelViOGVjM2laRkFKRHREN2tId3lOWWM3TVVzeXd2Q0dBSTBvcnFua0JWYm9ibzY4aDVVTzgtQVBvVW9fWjh6cVVLWXhrWjg?oc=5</t>
+  </si>
+  <si>
+    <t>Let Idaho fix campaign finance, get dark money out of politics | Opinion - Idaho Statesman</t>
+  </si>
+  <si>
+    <t>Let Idaho fix campaign finance, get dark money out of politics | Opinion  Idaho Statesman</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNWnMya0FLQWJQdFdvYVlfT3EzLXFsMFFoQU83OVdmMDI4ZlVmbTNjd0ZXeXBfWGN0VlZVdE9PZWVYZms3c3p6QUp6ZlZoOE9pdHFGaFZFN3lJazlxeWppOEpkN2ZiVUI2TDRadHhuc0dCRy1DekFmOEdRVnkySDdtcU5B0gGCAUFVX3lxTE42d2trUFl6Ql9PYjh6MFhsaU1KS1BQc2ZwWnZkTnRrX3pIbTJoc0czaHUweGVsVHRNSmNZX1ZMZ3hqeXpRdGJKb3RaUVAwRlB2VjZGVmJ0Wmh6LWMzQzdnOWFPbDV3cDhNX3pvV0tSVXZtRXNTOGVYbVYxbGRpbUxJZmc?oc=5</t>
+  </si>
+  <si>
+    <t>Symposium on International Investment Law &amp; Contemporary Crises: Divergent Approaches to the Nationality of Corporate Claimants in Banking and Finance Investor-State Arbitration - Opinio Juris</t>
+  </si>
+  <si>
+    <t>Symposium on International Investment Law &amp; Contemporary Crises: Divergent Approaches to the Nationality of Corporate Claimants in Banking and Finance Investor-State Arbitration  Opinio Juris</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiswJBVV95cUxOVzVCTXM1OXlwdTg3WG1qR1poQW00WjBXeFhtNF9IMEhhWEZKbTBtV0lEUFNUWURScUFPVzFjOEQtMFQycnJmTmlUTFZaZm52X055djVCNDlxT1lEQXRuTnQ2Zk9iVEtLSHJiWEI2SkpsTmVCOUx3dlJkUERIcWNpMHF1WWpKeVJuMDI3bC1kZ0p1RnFuZzdoZlpqY2pVQkJTbGtqT2FpRkh4OGZqLUJJaDBCQzNTdmIxLS1mdnJ3T3pCOXZ0dGlwa0hRYTNDUXIyOFVsZjNycV9wT0tsTlhpTFRZWG5FazRaWVRzcjFaYXlYRUxEV1BnQi1jdDVqZzF1ZXQwdXdsS1pVRzQ5bnN5VTFyQVBKV05YYlFOUlZFV095TDJpOW9INEZQLXo0UXgzRnVN?oc=5</t>
+  </si>
+  <si>
+    <t>Sheffield Financial, Mercury Marine launch financing partnership for outboard engines and boat packages - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Sheffield Financial, Mercury Marine launch financing partnership for outboard engines and boat packages  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNRDdXZFRmVHVSYUxLME9OTWN2R0g0TDFDR2ptUl80UmZmNVlyVkZPTWkyTmotTXBja2NqLUVxdk1EWnFucU51d3F3UlZTWTlydy1TNVFRa0lfX1hnT3YwMXNyQldaVEphSHpYSFNBYjlPcmJCcGxVdDhKSUZBX0NVY0Z6UnFVMzhUcTJXNlVyNUM?oc=5</t>
+  </si>
+  <si>
+    <t>UK's YouGov appoints former ITV finance chief as chair - Reuters</t>
+  </si>
+  <si>
+    <t>UK's YouGov appoints former ITV finance chief as chair  Reuters</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNUldhNkVfU0otcmZKSGRkQU8waHdmWnpUQVIzTzQwOHBsejlIdEFjenVGWDh4YmZsMXcycTZNbTVLdzFkMF8xZlBrUE5UMHgzYURabUFtRHFQWHhTTXBHa3pYcjhGMzVoZUlyZVZ4WE9WU3o5TjdzTHhIME05S0JRR05DRjNuMFBZajlLSV9lbEZIbk5CZTBpaGVn?oc=5</t>
+  </si>
+  <si>
+    <t>Four health systems deploy AI to control spend - Healthcare Finance News</t>
+  </si>
+  <si>
+    <t>Four health systems deploy AI to control spend  Healthcare Finance News</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNc1kycHlPNTVqbVNZY0dFNjlfem0zamM5cDVhWjNmc3FSc0ZNcUVQMmlfODJnUVF2S3hsOUV6N1REUDYxMXZwY2diRkhlY0thSmFKZVpEeUZ0ZWE3cFU5dDJEZGhXQ2poc0VlU2RSbXFlM3Q0cW9WUnhfTmFKdzhZeHBOWGd0S3dUUHVVa09NYw?oc=5</t>
+  </si>
+  <si>
+    <t>Senate bill decreasing campaign finance transparency passed - theintermountain.com</t>
+  </si>
+  <si>
+    <t>Senate bill decreasing campaign finance transparency passed  theintermountain.com</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNcVJRNTA1YVFuTldWNjFfNnV2bV9wYS1UNHR2UWszUEQ2NlNlRjRGaEFIS3NoQ3c3UExHVmF4UHFZeThYQUgtSURkN1ZPV1hBRUx5RndTV2VqT3JzQTVvc1NyOHpINnAxQS1zLWJHMlBLLXVSSGQ3TXd0ZHJoblhSWlFfMWFhaXhaRTRWR25vdkJhVURNaGtDX29MNjJfWFQtbXhWTFBkVXhUdnhYcENsZl9VNlFCaTIx?oc=5</t>
+  </si>
+  <si>
+    <t>Xerox partners with Texas PE firm, secures $450M in financing - Hartford Business Journal</t>
+  </si>
+  <si>
+    <t>Xerox partners with Texas PE firm, secures $450M in financing  Hartford Business Journal</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQSDFpZ0hmb213MU02blo3Rk9nU3phencxblN0YnBvTW5kZEtDN1gzdWtEaU5nc2pyNmFUYjNTM1VaRDVOSGNZMF9kUEQ0Z1F3cVVsczlkaEw2RkhFSnhLSXVwbHREcEZCUUFJbXpiT3dEN2plOU5tOTZBTVRMNmNoNXNzQ1VlOHEtdFpUMUNGZE9SN083cXFfaUk2Z3cwZw?oc=5</t>
+  </si>
+  <si>
+    <t>Japan Election Supermajority Boosts Market Confidence In Economic Recovery - Global Finance Magazine</t>
+  </si>
+  <si>
+    <t>Japan Election Supermajority Boosts Market Confidence In Economic Recovery  Global Finance Magazine</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPenFOalRHdHhVR2dmNUR4SDhSeEVzLU1ZLUVYUk1UMXZwNGgtTWI4REJISU90TlhIeXRHaEtRY19RalVwSXNjUE9zUXBWNUFsbTZEQURudWE4WmpQOTdFNE9MUkZFMlFDcFg3NkVBQnk1a21UMF9tR0dXcV9DM0trOTZtSF96YTNHMm43U1VvUUlrNTE0cGN5UWwwZU15T1Q1TlZJQ3pyRTA3eHAxZ1NuWWZVX3VFcVM1UlJOY1VR?oc=5</t>
+  </si>
+  <si>
+    <t>Embedded Finance Reshapes SME Cash-Flow Stability: Implications For Advisors - Wealth Briefing</t>
+  </si>
+  <si>
+    <t>Embedded Finance Reshapes SME Cash-Flow Stability: Implications For Advisors  Wealth Briefing</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOcFNnTkg3WGFKSWI3c2toU0RhTmJzdHNyVndiOW5sSDVyaWVqVkZkQ2FqMEREUWVsWFhWUXVZdGdBNEZXYUV5WmxtSE1YOVVEZTRaY2pEanFtczNXOTN2NFNmeWhkSlFSRGVfc2YxcGllVFFYaXgxVnA2cFctbGs3ei1USEFtM042eGZqeE0xS0dmY1ZaUkZKRy1fcmNUWkxyVFNhUlN6RTA0N3cwRW9FYUM2QXprMTUwd2tVRGJERnZrRng1VmJYYmJvX0h3dw?oc=5</t>
+  </si>
+  <si>
+    <t>The capex crucible: What finance teams can learn from data center builds - McKinsey &amp; Company</t>
+  </si>
+  <si>
+    <t>The capex crucible: What finance teams can learn from data center builds  McKinsey &amp; Company</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNLUNwUVFROUdldVdjQ0ZwMnM5RmE5Y3BmTXo0bWhWd1Y2ZVdjbEJhSllULXRIdThRWV9rc2xURGk3V2NRcU0waWpNYXFjNGpXWlBqcm15R0RkYUdRVy1PWUFQNmVRUXVVOXJ4MXNxQlI3Yk8xZ0dvNFg2QjVKUl9PWHBLVDAzX1BicHA4dnUwazRjVE9ITkVLbWJiUjhzZGloVG0zQm1LM1ItRjlkQVVDYldCejR3Q0F3Q2RNU2x0S3dEbUJoR3N3eW5uVTZsX1RPLUVwOGExb0phbDJETG1femxFVmVpVlI3?oc=5</t>
+  </si>
+  <si>
+    <t>Financial &amp; Tax Information - Crescent Energy</t>
+  </si>
+  <si>
+    <t>Financial &amp; Tax Information  Crescent Energy</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOT2QzcEFjdlE0Ujd1TE1tUWtXZXhPajJkSkJBcUNaVHBaSTJSV0xZamFUd0UydjBPSC1waDAzNUd0dTQ0c2lHeEM5YTRoUGxFQ0JIUGFrTU51UUpTNzVoYXUyNDR0RzVGR202WHY5QkdRRjh0N0hVbFVqNjVpRVdTR3RScEJZRnZVVThyRk9YRW5GUmQxVXVaLXhudw?oc=5</t>
+  </si>
+  <si>
+    <t>Commentary: Campaign finance reform suffers the risk of ‘a deal that has yet to be real - The Portland Tribune</t>
+  </si>
+  <si>
+    <t>Commentary: Campaign finance reform suffers the risk of ‘a deal that has yet to be real  The Portland Tribune</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNUWZMLXk4dms5VEh5YWJIMVZLSVdjOGExcXRQZEFhSDAzQ0d3WXRrYVhraXVDUXkyQjV4NnhQNUJxUlN0cTFRRGVORDNjOU9hS2NOZ2VMZ2NSY2w0YzRsMFQyZWJYQWJNZFNnakdvX0NZbTdjaFlSQ0dvc2dIZExUc0ctWHNGVU42QmpTcmVMblJLcE9KNlhCQTczUlJrU0JTWF93aF9OczVOcUhKSU0wVHd5bk1vSm1zS2l4S2VPMkI2OEE?oc=5</t>
+  </si>
+  <si>
+    <t>Stock market today: Dow, S&amp;P 500, Nasdaq futures climb with AI disruption in focus, Fed minutes ahead - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Stock market today: Dow, S&amp;P 500, Nasdaq futures climb with AI disruption in focus, Fed minutes ahead  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNM2lKWUJWMWdzZExXazVwM3M0Y0w5WnBKYUI1SHZWSDNnSkgxUVgxSUNVOEpneDh6NFNPdS1PZDJVWWhLbndnMWk4bFNUS3ZOWVJQVUpTTldhcUdEdmxDeTRDaS1hVURCUmgtR2RBb3d2TDBYbGVLUk5zZUl3cHQ5MmhiRkk0WTF6YXZZeXEtdG9EcF92Qlg3ang3TTFZMElfRWRQamFaRGdrcG5Ta3I0OHVPTGNMc3o3Q0F4Y1k0VVk4a2o5NEd1Y1lTQ0xkdVpNNlIyUU5uamZNZmJNREtLcA?oc=5</t>
+  </si>
+  <si>
+    <t>red violet to Announce Fourth Quarter and Full Year 2025 Financial Results on March 4, 2026 - Yahoo Finance UK</t>
+  </si>
+  <si>
+    <t>red violet to Announce Fourth Quarter and Full Year 2025 Financial Results on March 4, 2026  Yahoo Finance UK</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNUmpwMW1xVEFBUWZjcWRMRG1VVjRZTDFYT1pvQ3NqLVM0ZlQyX2pCc1ZyVHNQWGpaaTVUVVd2NHNMWHhXRmRQREVoWFJlZmg0Z25Yc29mNzFiU1AzR2U1N2swWWJ3S093Z21fV2d0VTlQTUtuUXlGMFJEa3VCNU5veWRTMmxxUkFRLU5N?oc=5</t>
+  </si>
+  <si>
+    <t>Top 10: AI Tools for Finance - AI Magazine</t>
+  </si>
+  <si>
+    <t>Top 10: AI Tools for Finance  AI Magazine</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBMangwQjkyOTJGb2d1SDI0U1N6M2o2cERWekxqbmlWT2FrZ3gtcU5ROElabGIxTjM5eEUwb2JpR09VS1UwQjAtYXFCUHEyTDU3VVdNNmtaUkxCdVdyaC1TUmVaVWNqNFU?oc=5</t>
+  </si>
+  <si>
+    <t>Pasinex Announces Q4 2025 Financial Results - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Pasinex Announces Q4 2025 Financial Results  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPVDJNaFBkZHlKN0g4QV9DRmRlZUdHSHVHbkdXYUxiYmJmRV96SFlJWEFoNEY4NFRMX2NxZ29peVh6dG9PSVpNN1cwa0xiSGVQYnp6cFdlbE1aMDhMc0lnckkwbUJCcGVJM3RQcEhHbFRpWlpGcllPU0Y2bHlFYmtaVWR3R2RiMWV5?oc=5</t>
+  </si>
+  <si>
+    <t>5 Financial Transaction Stocks to Watch Despite Elevated Expense Level - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>5 Financial Transaction Stocks to Watch Despite Elevated Expense Level  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPdThLN21OaFZvSC1IZ2ZyeEdoUVc0TnQxNUJjLXdGYkJ1UGMtSDBtSFVycXFOTktWOHlScU03YjVzc1ZiWnQwSnphYWpNSHdtVVJBQTUteHlSbWtwZ3ZJOWJkODl6NnBwd1JtaU0wdExoX0JQTjNKd3BLcHN4R1NtNC03VDBJTlpVcmc?oc=5</t>
+  </si>
+  <si>
+    <t>Papua New Guinea: 29 financial institutions decline to finance TotalEnergies liquefied natural gas project - Business and Human Rights Centre</t>
+  </si>
+  <si>
+    <t>Papua New Guinea: 29 financial institutions decline to finance TotalEnergies liquefied natural gas project  Business and Human Rights Centre</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxQZE11X3dpa0xGRFVUUl9XbUFULXpyc1R2N21NTTdNUlNIb0ZBSGdaVVA5YW1QbE8wMG9zd3JTakJvNDhfSkc3RXR4Z1Zkd2FfcHRDUXlwTThhLXpVV3JRaTFfSEl1alRkQ3NjeWtwakhSd2hKUlRHSjlYaWlBSUNueXJBbWV0amxycC1GOTM0aXEzMlM3M0VxNlFBZVRSRDJPdlJybDZGU1k0Tk5SbTR3VGlFN1lfOV9xSXQ1NzBzTDVNWHE4bzNXdHlvQjg2TWxaMzl5TTN2RWFmVjZrRUcyMm5KcGJNMlo3MzVfdVM3MA?oc=5</t>
+  </si>
+  <si>
+    <t>1 Financial Stock That Could Turn $250 Per Month Into $1.4 Million - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>1 Financial Stock That Could Turn $250 Per Month Into $1.4 Million  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9LV2tVdFpfN252eWtFWGtYaFhTM1pJbk5SOGtoVUdraE90YkRuNWtxRmw5VEJHS3NGT25lRkdyeENGNFc0a3ZFZHI3NldxbF85b3BoemZPdnRXeHZRT3BHQlZIUjRIa0xsYjVXV1VMTVR6NlcwODJ4UllMREFNSTQ?oc=5</t>
+  </si>
+  <si>
+    <t>Moderna stock surges as FDA reverses course, agrees to review new flu shot - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Moderna stock surges as FDA reverses course, agrees to review new flu shot  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQZ0t2N0F6U19YUjNIcE5WeGE0Ukt5VjZYSlRjWUNpd25HRnZpV0l0Mnd4N01OU3F6THRGY3FTWWREdFYzVXhVNUJyVDBxRWRVWm9Kc3VFOGl3OWhNZXYyaUs4LW9fSnBHajRSUXhvUUsxQ1gtelZiOXNnR0pnbnlOU3EwVHFvLWdNT2NUdnY3OWlzc2tiZU9mQTZZN0I2aW9RRExXVEhuTHZhSzFySnZsWTZPeDl0eWRTVE1n?oc=5</t>
+  </si>
+  <si>
     <t>‘He’s jumping in all the way’: A Trump financial regulator backs prediction markets in their clash against states - Politico</t>
   </si>
   <si>
@@ -1751,456 +2249,6 @@
     <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNX3hNc0hjMW1FVW5WaVZOSnhIcmlMQjYxc1gycEdZWkczSXFPeUF0ZVh6SWg0RERvbVE1eXoyN2FyY0J0R2VQbmt0ZjZDY3BNRFpxMk5hZm4tNDl3eDdyM2tnSGFxN19udmV0LVlJbmpwbzI2cUh5WU5YZVdvYWVHRi04U2hlUnNVMm5tdE5n?oc=5</t>
   </si>
   <si>
-    <t>Euro uses Trump-shaped world order to encroach on U.S. financial power - Axios</t>
-  </si>
-  <si>
-    <t>Euro uses Trump-shaped world order to encroach on U.S. financial power  Axios</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTFAzTlV0M18zcHktRHBESXRFN0NZXzBLNkNOUGJhNUNLb1JwUVU3b0pSendjWDZWUm1RYlRrbk9NaVk3SldhRHAzcFJRWUVWd3hJWU0xUGNTeHZPdHFJRFpV?oc=5</t>
-  </si>
-  <si>
-    <t>Economic Sector Performance Dashboards - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Economic Sector Performance Dashboards  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiSkFVX3lxTE1aZHRnWXJQdlUwdmU4ZExFUzhEVXA5TXBHSFBsNS15TzJCSWtfMGRtU09HNENQMl9mTzlBenQyVmtTOFBKaFJDQ2ZB?oc=5</t>
-  </si>
-  <si>
-    <t>Coffee &amp; Donuts with the Mayor and Finance February 28 - City of West Chicago, Illinois</t>
-  </si>
-  <si>
-    <t>Coffee &amp; Donuts with the Mayor and Finance February 28  City of West Chicago, Illinois</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNR2VZNUNzbDNRYWNJMEVURm53elA3TU85SVdudUIzQ0Z5OTROdG44dXB5WlpqbkdPNHNSb044eHFvODZzQXJFTGJpM3NaajkyTTNid3ZVNjg0WldTaHA2eW5vRkdaWVBRUEttQnNqaGE4STFEZF9LQVhlRHdmTlc3ZVRscXRkMExyREE?oc=5</t>
-  </si>
-  <si>
-    <t>Governor Moore Testifies Before Senate Finance Committee in Support of Legislative Agenda to Make Maryland More Affordable and More Competitive - Office of Governor Wes Moore (.gov)</t>
-  </si>
-  <si>
-    <t>Governor Moore Testifies Before Senate Finance Committee in Support of Legislative Agenda to Make Maryland More Affordable and More Competitive  Office of Governor Wes Moore (.gov)</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxQM1pHd3I0RG5XejdpVWJEcUxramNPeU1WOUxlU0MyczlaS0pLMUw2Tm1nSVQzcGNPRWpQT1I3cXVLcXBUaUpYcGxGSkg3OHp1U3Y2eDZhV2RtRV9FR3J6QUV6Y2hyblRGeVNkdU1HT0ZEOFc4Q1RhREJCN29JVlptRzk2TWZoaHhncjhwekdHb0xTVTFMMjBDUnl2QmtqOXBpUmgyaUlTaE1XeW5WOVJDaWR0X3NPaXZieDd3MjREM3NCYU0wSzBWVGptbDhUWGIwcVFDUHdvTmhRdnBQd21HazlmTDRBUGx3VDdrZE02b01PZG1JeFpLMlJPTTd3Y21DSFNIZ2Zn?oc=5</t>
-  </si>
-  <si>
-    <t>Avalara Recognized on G2's 2026 Best Software Awards for Accounting and Finance Products - PR Newswire</t>
-  </si>
-  <si>
-    <t>Avalara Recognized on G2's 2026 Best Software Awards for Accounting and Finance Products  PR Newswire</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOOExlVW1PTkhpeVRVeVJqS1A3WVdydlhPNGx5cWhmZS1TQ3pBM3hnZGZwSFhkVWtnRnlRNm1tcnlySzVnYk5uZVRrbVNSV3BMQXEwTkhJTTZweVlZVWpxcndnZ0pxcGdhOTBJQ25MY1lKcm9WdnZWaldvMVR6cnhCNEl1aVBaVDRrTGgwMmVHMl9jQVIwc3pZeHVVTGVDb2hpZTAwa3M0MFcwRWhuaW81R0JIY2JEanRpc0c0aFB2dGs0OTZQSDhIVUhHSjByeWFuMEZ0eHBEbzVIX1k?oc=5</t>
-  </si>
-  <si>
-    <t>Program - Milken Institute</t>
-  </si>
-  <si>
-    <t>Program  Milken Institute</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE9rdkpHVDFFMmpRcTFFc0FlTnJ2bElINVdKNm1OeDVVWXVVMl8yVnpETHpKalVCc2o2T3NtSVhVWlBodzBVdFZycTQ5MksxbWFIbXh2eC1wbWNOMUt6MkxQcHdiTFdxZFBhQ2JQUFNKUQ?oc=5</t>
-  </si>
-  <si>
-    <t>Konica Minolta Wins the Bronze Prize in the Seventh ESG Finance Awards Japan of the Ministry of the Environment - Konica Minolta</t>
-  </si>
-  <si>
-    <t>Konica Minolta Wins the Bronze Prize in the Seventh ESG Finance Awards Japan of the Ministry of the Environment  Konica Minolta</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1XVnlJT3NZTlNITVVJU2JrUV9yejAtMTIxa05DXzY4ME0zWVBoRTBvOUduLWp1OTR4N21EbkdOa1VCQjBqYURmUUpVQ0p6VzZSX1BfMENPRTBScFpFSGxsRGloZzlPY1pVak9qNWNiMmVfLWNVdzhXVQ?oc=5</t>
-  </si>
-  <si>
-    <t>Women in Securities Finance appoints Hill Sands - Securities Finance Times</t>
-  </si>
-  <si>
-    <t>Women in Securities Finance appoints Hill Sands  Securities Finance Times</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQMjJkLTZVcm84eTNLM3RfeFl2d21odEx4ZlJSNUtUSkpPVzVockVkRmtOY00xcGg4VFltTXNoUFJRVkVFX0habzNBMlZNN3RmODJLc0R6djdOOWkteGtPb3FfazcwbUQ2MDlUTjNTaEJuM0IycDdKSUJHak5LbFNxeEFDMGVRWXJYTTFsQlRoRWcwWlQ5X1FQUnVEend5R1B2ejUw?oc=5</t>
-  </si>
-  <si>
-    <t>The Real Bottleneck in Finance Isn’t Payments. It’s Settlement. - FinTech Weekly</t>
-  </si>
-  <si>
-    <t>The Real Bottleneck in Finance Isn’t Payments. It’s Settlement.  FinTech Weekly</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOR3RLRlRYOFVvWE9LX1c1UzRubldLcjg1eXpSbXE3YlNvb2U3ZVdQZWZFVnBYOHhWYkNSN0JKZ2t0MFdSRGVLUmRtYmFxbUEzM0hBNXFmYlJJbEZZNUMwbkpFazNVNUdTTklFVmg4N3NGX2JUWDFpRV9ScXRRWG9pa1A1Q1pxc093U2c?oc=5</t>
-  </si>
-  <si>
-    <t>New Climate Finance Initiative Supports Climate Adaptation Efforts in Glacier-Dependent Regions - Columbia University in the City of New York</t>
-  </si>
-  <si>
-    <t>New Climate Finance Initiative Supports Climate Adaptation Efforts in Glacier-Dependent Regions  Columbia University in the City of New York</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOMTN2TUpQT0dqaGR5VU9SSng0YzJibE1DZGdJOUVVWm4xM0RDVkUteVBpS0lZb3k5VDhxVEsyekNWNXUzR2YtN3pOV2hNRDQ4WVI5VHpyaDNnVXNmc21CNlh4SDdJd0V3V3dyWU9hc3VObGotYmZvQzNrWVRRTUFCSUVTU2Zial9JRWU0c1ZNZWw1eFFCdmxFZ2JxdDJkLWNxa0NEM2lFUlFtdkNHSjZQeWUwNl81TEJCdkY4QnVwb2JIRmE4ZGlGUVNaQ3FFN1BIb2k2RG5FbU8?oc=5</t>
-  </si>
-  <si>
-    <t>AI adoption already hitting Irish graduate jobs, finance department says - Reuters</t>
-  </si>
-  <si>
-    <t>AI adoption already hitting Irish graduate jobs, finance department says  Reuters</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNY0ZlYUU3ZWpFUFF0WEk1eXRkc1ZwbUduSUpVdjJoeXdLeWhJVnMzV0taTk11b0lpeklmMzZBM29YVmd6V3dqWlhENkJnZ0dRRjdNSWd3TVV5dURwbUM3QjFzem1wSHd2Y0Y2aU5GWFcyS2tSR3RsTmVfQ1ZzWWFvbU5Ld05YYlBiTVNmMm5rVGxHVEVDcjJzUVM4RjZxQ1gtbWp5clFFalNZbmtMWThuZzFDczlsSjA?oc=5</t>
-  </si>
-  <si>
-    <t>Symposium on International Investment Law &amp; Contemporary Crises: Energy Finance Market Design &amp; IIA Claims - Opinio Juris</t>
-  </si>
-  <si>
-    <t>Symposium on International Investment Law &amp; Contemporary Crises: Energy Finance Market Design &amp; IIA Claims  Opinio Juris</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNdE85WEhsdkw2YTBwVW14aklibzR3X0pLUVVkZEVlM2xjNEFzRXBzMkVINmQyc1VZMExFV0R1WmRCZHlac2FzQS03djdrSk9SdU1sM1ZOS2JlSGRGS0RDU3lQaktUNlBPN0VVclhWbjdJUXdkalVPM0stRXp4S3luVUJRNkVyV2NnUVpoTHhQM2VVV3F2QzBfT2VUNDNyVENwQWJyNV82TldkZE1ITnNiWGVhRGM1TlA1Z3NPcHJ4Rjg4S1pSeXFXNjc2Wlh6X21obUE?oc=5</t>
-  </si>
-  <si>
-    <t>How Credit Cards Keep America’s Small Businesses Running Strong - U.S. Chamber of Commerce</t>
-  </si>
-  <si>
-    <t>How Credit Cards Keep America’s Small Businesses Running Strong  U.S. Chamber of Commerce</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOOEZRTVRzZlF2RzVaVVZXdm55a1JWRzlHenl6OWQ4czBNa0hLbFF1dWdFMXI4RExnQVhmQWpzb2tEanNvNEU1UzQ5ZXRhaXgzY3BUazl3WFdkb1VwMGowMkl2eEhoT0x1djA1LVltOTZOWlBTOXQ5YzItUkRLcmhXd0RvRHhkZi0tZERvX19FWUpEazZwdHlhVDZZekk?oc=5</t>
-  </si>
-  <si>
-    <t>BBVA welcomes Shepherd - Securities Finance Times</t>
-  </si>
-  <si>
-    <t>BBVA welcomes Shepherd  Securities Finance Times</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxORVBDSXlvSTBQR0w4WTc1WkhzNDdGMmhuSWlpOE82Mm5uTnBNVnBUTUJSMWVuNUp4OXVGdV90M0pZelBNcXBUdmZOVWQtVlN2eWV4bFpBSG1ZcFN2eHNSS1hJam90R0dRWXRROEtsLXlRMTVWcFJtVGdSR3FpNWZkRjN4ekRlZUU4cEJvTmtUUVdwLS11T1RuN1F6UWJxcFJ5UXBZ?oc=5</t>
-  </si>
-  <si>
-    <t>Troutman Pepper Locke Weekly Consumer Financial Services Newsletter – February 18, 2026 - Consumer Financial Services Law Monitor</t>
-  </si>
-  <si>
-    <t>Troutman Pepper Locke Weekly Consumer Financial Services Newsletter – February 18, 2026  Consumer Financial Services Law Monitor</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPUExOOWVkYWxmODJERVdlUlpCOFhXdDFmTXVWdW54TnFhOWZvNUdBWERLVnd3aXR5aFNwaHk1QnVSZVREVzkybjhoemhPYTNhVkZQdFFlelJmS19vQV9ZNWxVVE9SN05mVEtaVDV0b1ZvNHRXazI0TmFLX1c1TFVkNnUxVExBbnFCVWZwLTA0NTJFS3BjRWk5TWRGa3JHRTFxa2JfSm11WC1OdEtEWHZ5Mzc0V1NXSC1mVW5HUUtjTlJ2bGpQOEIwUzlmcGF2dXNoMHFzTnVLeVM3RXBlOXc?oc=5</t>
-  </si>
-  <si>
-    <t>Nvidia and Meta expand GPU team up with millions of additional AI chips - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Nvidia and Meta expand GPU team up with millions of additional AI chips  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNaEc1R3NCLTZRdDgwVWd6UDR5ZXB5SXd4Q0c2dlBUbVpnT1ZzRU8xMnh5bWNEa1BuS25zRHg3Qk45OW1QaVk3MlE1MEhta25icVhvYkw5UXd0MjU2U2gtVmljdFBrMzM1X1FKQzRPNG9uVllMb0lRSXFvQWx3TWFmaDAyaTNIMFhabl9maFdRek1jcVpBOEJaeFMzbUgxbF82dXRKTjVCZzRqZm9iNkUwbjNyQmZ6WkYw?oc=5</t>
-  </si>
-  <si>
-    <t>Chicago Atlantic Real Estate Finance Schedules Fourth Quarter 2025 Earnings Release and Conference Call Date - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Chicago Atlantic Real Estate Finance Schedules Fourth Quarter 2025 Earnings Release and Conference Call Date  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNazBfQm5fMm1UTGZMVF9JQm5FLXNnZHpwekp6R3lNQTk5aGYtd2J2eW9KemNpSHZWNzQtVVZ6NU92dTh6eEFSOTZ5NThjeV9yd0VXMU43djVCQTBLYUhJeks1b2xXX21HYXdVNjFOdzNwZDRrNmlRX1dFTGNyUjYtMHZPUUVaTWo5bWc?oc=5</t>
-  </si>
-  <si>
-    <t>Snap Finance Study Finds Majority of U.S. Households Delayed Essential Purchases in 2025 as Credit Pressures Persist Into 2026 - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Snap Finance Study Finds Majority of U.S. Households Delayed Essential Purchases in 2025 as Credit Pressures Persist Into 2026  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOTzNzdHpaNkF0TUlxNHJwdGtIRzQzdTBlNXpkUWRTbVdna1M0eE1IU1NvS1otYTAzVEFub2lvVWlKeHd6QkY3RmJ0T3NqSkVBX29Ya25DbkNydnZDRG55OGxDTksydXo4Y3JWSXNRd1U3UUY5Zm0zdlExbDVkZkxzVmxlU05Rdw?oc=5</t>
-  </si>
-  <si>
-    <t>Are Finance Stocks Lagging Barclays (BCS) This Year? - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Are Finance Stocks Lagging Barclays (BCS) This Year?  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPbkt4OTRYNGtDSjRKUTF5Y3hVZ242YzN0Nmlub0kzMl9KbnRRU00tMHdLVEl3aTY0V0Y5QWFzRDAtQ0M5WlVGV3ZxV1NzN3VpaWt2UVhVNWZVTDlScHA1bzg5TFlpN2p4Q0FGbHVhVVNuaWNzOTVQMTVoeklfR1hOT3h0R1ZlYmpQ?oc=5</t>
-  </si>
-  <si>
-    <t>Unlocking Finance for Nature-based Solutions in Indian Cities - Climate Policy Initiative</t>
-  </si>
-  <si>
-    <t>Unlocking Finance for Nature-based Solutions in Indian Cities  Climate Policy Initiative</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNbE9VZDZKVktsajJEVG0yM1ZfWEJ3Ums3RHRTM0FOZTFEZnFwa1NFSXBSbXpLMUpzNUktWGtqSzRVN052RllQUDNMY2x3TWlFSnNUS2VyNzF5X05ZWmx1MTlYSVlwOS05WDhjcmpCZTBacHc1Q29Ba2lZUkVuclMtaFJ6ejI3Z2lkMHVYdEFJREJIdXF2ZUVXT0VMMlFaLWRoeHFKY2xMS2syRTJWZDVQaVRraTQ?oc=5</t>
-  </si>
-  <si>
-    <t>West Virginia Senate Finance Committee approves appropriations bill for Hancock County Schools - News and Sentinel</t>
-  </si>
-  <si>
-    <t>West Virginia Senate Finance Committee approves appropriations bill for Hancock County Schools  News and Sentinel</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxORmNQWEtJSnc0OEQ2Yl92TldtMHJrVEdaZUdNdHNvb0pWdmpLcGdTV0xXZE5EcmJsWWFLSmxaOENUdUFqel92bTRjZ1g0TU9uLXVHTXNTY2x0VmVYV1Y4V1p4RTZKVDVNUGZHY0l3V3dWdmtuVGxMcmtOQVpralpLaDdGNXJ6OUt6dEpsMlNHQzNSOXpsclJBX1lOMXYzdkptaGlJRkRhNVdIaWowc2pFTTM5VlRFVlJsM0FCaU81TDl0by1fVVRCcUhYdThWYUdJbVRwUElna0hEVjQtM0NhYUlBcUtBUQ?oc=5</t>
-  </si>
-  <si>
-    <t>Lightrock grabs an exit opportunity from Indian small business lender Aye Finance - ImpactAlpha</t>
-  </si>
-  <si>
-    <t>Lightrock grabs an exit opportunity from Indian small business lender Aye Finance  ImpactAlpha</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPbW5lcmJoSERuOFp0MGYzaHJXS2Q4c2FTNUgyODYybUlOZ2JKUlVLcTcwYlRoNmRxbC0tejNBZXFaSHhEaTR2Q1VDT1BEREtLWjhiM2JDSFFpM2JGMUYyazI4a2ZkTm9Ja2pCRmNtcGhqTlJzcFowVlNKWmxtOHpSR1g1X1hEaXZyVXB1Y0ZlYVlkV3N3VTVTT2U3Y1ZKMHE2VkNSeHpKNWYtUQ?oc=5</t>
-  </si>
-  <si>
-    <t>OPENLANE, Inc. Reports 2025 Financial Results - PR Newswire</t>
-  </si>
-  <si>
-    <t>OPENLANE, Inc. Reports 2025 Financial Results  PR Newswire</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNZ3FFQzNzUG81QkNjTDgycHBKSUh3NURtVi1WUkR0cGFoODg3LUFyX25YYjVYNFIzU0U2cW9YT2pkcUNxTnpWb2VoUFpGTGI2N2I0Y2tmZ1hwWVlQRzhNVU1LdnBzYkx6QUpKSlRLQmJiMHFuV0NSNkhpTEZpVTIxeTRwVmUxc2c3S01fYnVWZVJDR2Z3VzlvV2MweUw0bXJk?oc=5</t>
-  </si>
-  <si>
-    <t>JPMorgan names Catherine O'Donnell head of North America Leveraged Finance - Reuters</t>
-  </si>
-  <si>
-    <t>JPMorgan names Catherine O'Donnell head of North America Leveraged Finance  Reuters</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOWEpseFJwUG1ZQno2N1VKRENxaUhBQjIyWDRwTHZSVXJmWGNndkF6dkxITFJkMENyb3NVMjRwaXRPOTd1TnU1LTNXdzdWTk55Tmk0b1ZzUG5RdzBEbGJWbXFOY2hfaHl2QldMdUF6RmhfdGVqMXhibk03cGNXVmVZaDVMUm92N0d5WWZkVHFuc254cGpMSG5SOXVBRnpNLVQyRWE3MjNxTlFvY1dkbkIzb2ZmSlk1eDZrb0VkRUpQcmQ?oc=5</t>
-  </si>
-  <si>
-    <t>Will investors buy the transition bond label? - Environmental Finance</t>
-  </si>
-  <si>
-    <t>Will investors buy the transition bond label?  Environmental Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOaFF0YzF2bWd3eHM4WHR5NHVzSlNRNTFUYk1QLWxCbjd6V2dzRkxHU2ttOGxsV1ZPVEtxTnBscVNLYjFYNGtEUGhIRzNaMUNUVGxaZkkwY2hOd1V2VVN0Y1RfM21SYXdnUlJtdktzWDkxN0JVTU41c0xuOTFrTFM2LU1jellYOTNaTGh6NGJhOWpXSFRxUnZZcG12Q3pVZV9sSHU0TnBGYw?oc=5</t>
-  </si>
-  <si>
-    <t>Gator Capital Management’s Investment Thesis for TFS Financial Corporation (TFSL) - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Gator Capital Management’s Investment Thesis for TFS Financial Corporation (TFSL)  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQQVpxUHI5eVNWd1FLVmJEdmtqbFd4Y2FfenVZbnNyVGdIWjJKM3VBUURxSVVRMi1tQjJPUWVaX2d2N051QVpqV2kzb05TdFRPcWpyejNKWDExUVRQUjFBX280MGRuM3BhZjNwYXR0N0pwOFlzN3RFRTQyM3dFRVdnVFdIMGZrMWFWSUY5YWs5dkJqdw?oc=5</t>
-  </si>
-  <si>
-    <t>Finance Chair Warns of Prediction Market Impact on Sports Gaming - State Affairs</t>
-  </si>
-  <si>
-    <t>Finance Chair Warns of Prediction Market Impact on Sports Gaming  State Affairs</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE04U3ZjVE9SNjRpN0hGSkEyNUNqdWMwclFieHV0UlpZNHdGRV9lSmdrdVlhcnVaSHJmQ3lpb3J6YnBnS2p2VEN4R0xwMjJ0d2NkNURTNFNpdzFOZ2xPTmppdGFxOFNJQTh2WHFFRTNxeGY1YkpXX01sWTJOUVBUNkE?oc=5</t>
-  </si>
-  <si>
-    <t>Morning Bid: Changing of Lagarde - Reuters</t>
-  </si>
-  <si>
-    <t>Morning Bid: Changing of Lagarde  Reuters</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPbExHYkdzZWlmeWtDWkJaVGtsV2ptaFRRT0tkT2l1cW9FMDN1NXNHdmoyWEFkN0JPakhxX2l1WFVWMlJ3M3NBNFplM2dwZC16OEl0MjdzYWVMcXlObGJMT2RsTExOaGNYUXZoVkVzcVZpUWR4V3VFYjFnb1NkSEFEUERB?oc=5</t>
-  </si>
-  <si>
-    <t>Medicare Advantage growth slows - Healthcare Finance News</t>
-  </si>
-  <si>
-    <t>Medicare Advantage growth slows  Healthcare Finance News</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5pQnk4Q0VjOEViR3Uyc29jUVota3pxNjFkOHVDOXJYX0RzNjA4TWxVVkd2NnRFU09oelViOGVjM2laRkFKRHREN2tId3lOWWM3TVVzeXd2Q0dBSTBvcnFua0JWYm9ibzY4aDVVTzgtQVBvVW9fWjh6cVVLWXhrWjg?oc=5</t>
-  </si>
-  <si>
-    <t>Analog Devices Reports Fiscal First Quarter 2026 Financial Results - PR Newswire</t>
-  </si>
-  <si>
-    <t>Analog Devices Reports Fiscal First Quarter 2026 Financial Results  PR Newswire</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPdk5GakFqU2s3RjN1N0VIb3RsZ0ZPQ1NqRVFXZXMtZ1QtV1AxWUxzWjVDemJrQmppMm9WTWZyMk5COVRDUF9WWk9zalhYamlIaUZOMlRVMTF6SUNJMnJRWEFZQ2hEeUVXb0dRNUpsdk9ydmxEVXlVcW9OdUhQX2VmNFpyZkJvQWdob0h4VzlWMGJKWTFUVTJySXZ0NGhJdmp1SWdVSGZLUkoxaFVfMEJoTG43QzZuYTlkTXRsNF9NWQ?oc=5</t>
-  </si>
-  <si>
-    <t>Gorilla Technology Acquires Shackleton Finance to Establish Regulated Capital Platform and Fund AI Infrastructure Growth - Investing News Network</t>
-  </si>
-  <si>
-    <t>Gorilla Technology Acquires Shackleton Finance to Establish Regulated Capital Platform and Fund AI Infrastructure Growth  Investing News Network</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPNmZQaXZmQVBnOURjeVFnZ2Y4U3U2MU1LVHRQUTdMLTUyWXFvM2htN3RJaVQwQmU2M203N2x1SkYwNVhtZnZ3QXNqNDZEVzU5N1pmTUhMX096M1ZhMUd2U2p6VXNrMWNnX092TEhMVUNQbWlua0JOc1hFYkNST1BzZ2E4cW95TVhCSDltX2xZeXJYUzY3Q0JZckxMUkQzUUhVX2tVc1YxbDg2WWhZWXd2YkctWEd1ME5qbGcyY1RTYl9tcWFSVHZUOWdtZTl3SkZoWU42WlRuTm9rWlRRZG8zaw?oc=5</t>
-  </si>
-  <si>
-    <t>Tuition, financial aid rates set for 2026–27 academic year - University of Rochester</t>
-  </si>
-  <si>
-    <t>Tuition, financial aid rates set for 2026–27 academic year  University of Rochester</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNclRRcDI0YUNSbzR1aWhpc29FZVBtT0ZZTlkxRXpkdjUyZXJfN0NBSTZjaFJLeDIxbHFNS2J0NWN6QURmZDI5OWg1NHdSYzVzTlhzbDM2R0gwVzNiXzJkWlpjcTlQNVBNOGpFc1BSbTRVQm81V0dfeDRQZzRJRzFNdmNKT3A5OC1qclB5dkxCaWNBOWpWZlBCOFFncw?oc=5</t>
-  </si>
-  <si>
-    <t>Sheffield Financial, Mercury Marine launch financing partnership for outboard engines and boat packages - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Sheffield Financial, Mercury Marine launch financing partnership for outboard engines and boat packages  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNRDdXZFRmVHVSYUxLME9OTWN2R0g0TDFDR2ptUl80UmZmNVlyVkZPTWkyTmotTXBja2NqLUVxdk1EWnFucU51d3F3UlZTWTlydy1TNVFRa0lfX1hnT3YwMXNyQldaVEphSHpYSFNBYjlPcmJCcGxVdDhKSUZBX0NVY0Z6UnFVMzhUcTJXNlVyNUM?oc=5</t>
-  </si>
-  <si>
-    <t>UK's YouGov appoints former ITV finance chief as chair - Reuters</t>
-  </si>
-  <si>
-    <t>UK's YouGov appoints former ITV finance chief as chair  Reuters</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNUldhNkVfU0otcmZKSGRkQU8waHdmWnpUQVIzTzQwOHBsejlIdEFjenVGWDh4YmZsMXcycTZNbTVLdzFkMF8xZlBrUE5UMHgzYURabUFtRHFQWHhTTXBHa3pYcjhGMzVoZUlyZVZ4WE9WU3o5TjdzTHhIME05S0JRR05DRjNuMFBZajlLSV9lbEZIbk5CZTBpaGVn?oc=5</t>
-  </si>
-  <si>
-    <t>Four health systems deploy AI to control spend - Healthcare Finance News</t>
-  </si>
-  <si>
-    <t>Four health systems deploy AI to control spend  Healthcare Finance News</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNc1kycHlPNTVqbVNZY0dFNjlfem0zamM5cDVhWjNmc3FSc0ZNcUVQMmlfODJnUVF2S3hsOUV6N1REUDYxMXZwY2diRkhlY0thSmFKZVpEeUZ0ZWE3cFU5dDJEZGhXQ2poc0VlU2RSbXFlM3Q0cW9WUnhfTmFKdzhZeHBOWGd0S3dUUHVVa09NYw?oc=5</t>
-  </si>
-  <si>
-    <t>2026 Africa SABRE Awards: African Development Bank’s access-to-finance “AFAWA: Banking on Women” communications wins top global campaign honors - African Development Bank Group</t>
-  </si>
-  <si>
-    <t>2026 Africa SABRE Awards: African Development Bank’s access-to-finance “AFAWA: Banking on Women” communications wins top global campaign honors  African Development Bank Group</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMingJBVV95cUxPNFVQU1NQV2VGeEtVMWFlUHRTa1ByUFUxV29fZ255Xzk3eUR2UUJpVWJuU2xGd09JYTlWaWM5ejZza00wM19QMWZSYjU3THlVSGoyU0ZXdGRpYktEeXJOMzZ2N2VkblZZQjd3emkxU2l6eVJ1amdabGlwelhlVE9fUUhhM1N0MEJaUXJsRVg5WGVpeHlDRGJyLWZiSXkzWk94OWxBRTdrYlJhdUdvT0dmalZka1FTT0FGb293dlo2M2kyZ0psR3NDbDM4SXRSZUFRb3c2NGJlbzhxMk1vckFnZlhwMjF1WkFMc0djc01kd2h4eFZ5dG5uZUx0ekFKR3FBbzJucHI5R0pMQjYySTJkUEVGNTR5cGplOVQ4WUJn?oc=5</t>
-  </si>
-  <si>
-    <t>Let Idaho fix campaign finance, get dark money out of politics | Opinion - Idaho Statesman</t>
-  </si>
-  <si>
-    <t>Let Idaho fix campaign finance, get dark money out of politics | Opinion  Idaho Statesman</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNWnMya0FLQWJQdFdvYVlfT3EzLXFsMFFoQU83OVdmMDI4ZlVmbTNjd0ZXeXBfWGN0VlZVdE9PZWVYZms3c3p6QUp6ZlZoOE9pdHFGaFZFN3lJazlxeWppOEpkN2ZiVUI2TDRadHhuc0dCRy1DekFmOEdRVnkySDdtcU5B0gGCAUFVX3lxTE42d2trUFl6Ql9PYjh6MFhsaU1KS1BQc2ZwWnZkTnRrX3pIbTJoc0czaHUweGVsVHRNSmNZX1ZMZ3hqeXpRdGJKb3RaUVAwRlB2VjZGVmJ0Wmh6LWMzQzdnOWFPbDV3cDhNX3pvV0tSVXZtRXNTOGVYbVYxbGRpbUxJZmc?oc=5</t>
-  </si>
-  <si>
-    <t>Senate bill decreasing campaign finance transparency passed - theintermountain.com</t>
-  </si>
-  <si>
-    <t>Senate bill decreasing campaign finance transparency passed  theintermountain.com</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNcVJRNTA1YVFuTldWNjFfNnV2bV9wYS1UNHR2UWszUEQ2NlNlRjRGaEFIS3NoQ3c3UExHVmF4UHFZeThYQUgtSURkN1ZPV1hBRUx5RndTV2VqT3JzQTVvc1NyOHpINnAxQS1zLWJHMlBLLXVSSGQ3TXd0ZHJoblhSWlFfMWFhaXhaRTRWR25vdkJhVURNaGtDX29MNjJfWFQtbXhWTFBkVXhUdnhYcENsZl9VNlFCaTIx?oc=5</t>
-  </si>
-  <si>
-    <t>Xerox partners with Texas PE firm, secures $450M in financing - Hartford Business Journal</t>
-  </si>
-  <si>
-    <t>Xerox partners with Texas PE firm, secures $450M in financing  Hartford Business Journal</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQSDFpZ0hmb213MU02blo3Rk9nU3phencxblN0YnBvTW5kZEtDN1gzdWtEaU5nc2pyNmFUYjNTM1VaRDVOSGNZMF9kUEQ0Z1F3cVVsczlkaEw2RkhFSnhLSXVwbHREcEZCUUFJbXpiT3dEN2plOU5tOTZBTVRMNmNoNXNzQ1VlOHEtdFpUMUNGZE9SN083cXFfaUk2Z3cwZw?oc=5</t>
-  </si>
-  <si>
-    <t>Japan Election Supermajority Boosts Market Confidence In Economic Recovery - Global Finance Magazine</t>
-  </si>
-  <si>
-    <t>Japan Election Supermajority Boosts Market Confidence In Economic Recovery  Global Finance Magazine</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPenFOalRHdHhVR2dmNUR4SDhSeEVzLU1ZLUVYUk1UMXZwNGgtTWI4REJISU90TlhIeXRHaEtRY19RalVwSXNjUE9zUXBWNUFsbTZEQURudWE4WmpQOTdFNE9MUkZFMlFDcFg3NkVBQnk1a21UMF9tR0dXcV9DM0trOTZtSF96YTNHMm43U1VvUUlrNTE0cGN5UWwwZU15T1Q1TlZJQ3pyRTA3eHAxZ1NuWWZVX3VFcVM1UlJOY1VR?oc=5</t>
-  </si>
-  <si>
-    <t>Symposium on International Investment Law &amp; Contemporary Crises: Divergent Approaches to the Nationality of Corporate Claimants in Banking and Finance Investor-State Arbitration - Opinio Juris</t>
-  </si>
-  <si>
-    <t>Symposium on International Investment Law &amp; Contemporary Crises: Divergent Approaches to the Nationality of Corporate Claimants in Banking and Finance Investor-State Arbitration  Opinio Juris</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiswJBVV95cUxOVzVCTXM1OXlwdTg3WG1qR1poQW00WjBXeFhtNF9IMEhhWEZKbTBtV0lEUFNUWURScUFPVzFjOEQtMFQycnJmTmlUTFZaZm52X055djVCNDlxT1lEQXRuTnQ2Zk9iVEtLSHJiWEI2SkpsTmVCOUx3dlJkUERIcWNpMHF1WWpKeVJuMDI3bC1kZ0p1RnFuZzdoZlpqY2pVQkJTbGtqT2FpRkh4OGZqLUJJaDBCQzNTdmIxLS1mdnJ3T3pCOXZ0dGlwa0hRYTNDUXIyOFVsZjNycV9wT0tsTlhpTFRZWG5FazRaWVRzcjFaYXlYRUxEV1BnQi1jdDVqZzF1ZXQwdXdsS1pVRzQ5bnN5VTFyQVBKV05YYlFOUlZFV095TDJpOW9INEZQLXo0UXgzRnVN?oc=5</t>
-  </si>
-  <si>
-    <t>red violet to Announce Fourth Quarter and Full Year 2025 Financial Results on March 4, 2026 - Yahoo Finance UK</t>
-  </si>
-  <si>
-    <t>red violet to Announce Fourth Quarter and Full Year 2025 Financial Results on March 4, 2026  Yahoo Finance UK</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNUmpwMW1xVEFBUWZjcWRMRG1VVjRZTDFYT1pvQ3NqLVM0ZlQyX2pCc1ZyVHNQWGpaaTVUVVd2NHNMWHhXRmRQREVoWFJlZmg0Z25Yc29mNzFiU1AzR2U1N2swWWJ3S093Z21fV2d0VTlQTUtuUXlGMFJEa3VCNU5veWRTMmxxUkFRLU5N?oc=5</t>
-  </si>
-  <si>
-    <t>Commentary: Campaign finance reform suffers the risk of ‘a deal that has yet to be real - The Portland Tribune</t>
-  </si>
-  <si>
-    <t>Commentary: Campaign finance reform suffers the risk of ‘a deal that has yet to be real  The Portland Tribune</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNUWZMLXk4dms5VEh5YWJIMVZLSVdjOGExcXRQZEFhSDAzQ0d3WXRrYVhraXVDUXkyQjV4NnhQNUJxUlN0cTFRRGVORDNjOU9hS2NOZ2VMZ2NSY2w0YzRsMFQyZWJYQWJNZFNnakdvX0NZbTdjaFlSQ0dvc2dIZExUc0ctWHNGVU42QmpTcmVMblJLcE9KNlhCQTczUlJrU0JTWF93aF9OczVOcUhKSU0wVHd5bk1vSm1zS2l4S2VPMkI2OEE?oc=5</t>
-  </si>
-  <si>
-    <t>Top 10: AI Tools for Finance - AI Magazine</t>
-  </si>
-  <si>
-    <t>Top 10: AI Tools for Finance  AI Magazine</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBMangwQjkyOTJGb2d1SDI0U1N6M2o2cERWekxqbmlWT2FrZ3gtcU5ROElabGIxTjM5eEUwb2JpR09VS1UwQjAtYXFCUHEyTDU3VVdNNmtaUkxCdVdyaC1TUmVaVWNqNFU?oc=5</t>
-  </si>
-  <si>
-    <t>Pasinex Announces Q4 2025 Financial Results - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Pasinex Announces Q4 2025 Financial Results  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPVDJNaFBkZHlKN0g4QV9DRmRlZUdHSHVHbkdXYUxiYmJmRV96SFlJWEFoNEY4NFRMX2NxZ29peVh6dG9PSVpNN1cwa0xiSGVQYnp6cFdlbE1aMDhMc0lnckkwbUJCcGVJM3RQcEhHbFRpWlpGcllPU0Y2bHlFYmtaVWR3R2RiMWV5?oc=5</t>
-  </si>
-  <si>
-    <t>Financial &amp; Tax Information - Crescent Energy</t>
-  </si>
-  <si>
-    <t>Financial &amp; Tax Information  Crescent Energy</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOT2QzcEFjdlE0Ujd1TE1tUWtXZXhPajJkSkJBcUNaVHBaSTJSV0xZamFUd0UydjBPSC1waDAzNUd0dTQ0c2lHeEM5YTRoUGxFQ0JIUGFrTU51UUpTNzVoYXUyNDR0RzVGR202WHY5QkdRRjh0N0hVbFVqNjVpRVdTR3RScEJZRnZVVThyRk9YRW5GUmQxVXVaLXhudw?oc=5</t>
-  </si>
-  <si>
-    <t>1 Financial Stock That Could Turn $250 Per Month Into $1.4 Million - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>1 Financial Stock That Could Turn $250 Per Month Into $1.4 Million  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9LV2tVdFpfN252eWtFWGtYaFhTM1pJbk5SOGtoVUdraE90YkRuNWtxRmw5VEJHS3NGT25lRkdyeENGNFc0a3ZFZHI3NldxbF85b3BoemZPdnRXeHZRT3BHQlZIUjRIa0xsYjVXV1VMTVR6NlcwODJ4UllMREFNSTQ?oc=5</t>
-  </si>
-  <si>
-    <t>Moderna stock surges as FDA reverses course, agrees to review new flu shot - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Moderna stock surges as FDA reverses course, agrees to review new flu shot  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQZ0t2N0F6U19YUjNIcE5WeGE0Ukt5VjZYSlRjWUNpd25HRnZpV0l0Mnd4N01OU3F6THRGY3FTWWREdFYzVXhVNUJyVDBxRWRVWm9Kc3VFOGl3OWhNZXYyaUs4LW9fSnBHajRSUXhvUUsxQ1gtelZiOXNnR0pnbnlOU3EwVHFvLWdNT2NUdnY3OWlzc2tiZU9mQTZZN0I2aW9RRExXVEhuTHZhSzFySnZsWTZPeDl0eWRTVE1n?oc=5</t>
-  </si>
-  <si>
-    <t>The capex crucible: What finance teams can learn from data center builds - McKinsey &amp; Company</t>
-  </si>
-  <si>
-    <t>The capex crucible: What finance teams can learn from data center builds  McKinsey &amp; Company</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNLUNwUVFROUdldVdjQ0ZwMnM5RmE5Y3BmTXo0bWhWd1Y2ZVdjbEJhSllULXRIdThRWV9rc2xURGk3V2NRcU0waWpNYXFjNGpXWlBqcm15R0RkYUdRVy1PWUFQNmVRUXVVOXJ4MXNxQlI3Yk8xZ0dvNFg2QjVKUl9PWHBLVDAzX1BicHA4dnUwazRjVE9ITkVLbWJiUjhzZGloVG0zQm1LM1ItRjlkQVVDYldCejR3Q0F3Q2RNU2x0S3dEbUJoR3N3eW5uVTZsX1RPLUVwOGExb0phbDJETG1femxFVmVpVlI3?oc=5</t>
-  </si>
-  <si>
-    <t>Papua New Guinea: 29 financial institutions decline to finance TotalEnergies liquefied natural gas project - Business and Human Rights Centre</t>
-  </si>
-  <si>
-    <t>Papua New Guinea: 29 financial institutions decline to finance TotalEnergies liquefied natural gas project  Business and Human Rights Centre</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxQZE11X3dpa0xGRFVUUl9XbUFULXpyc1R2N21NTTdNUlNIb0ZBSGdaVVA5YW1QbE8wMG9zd3JTakJvNDhfSkc3RXR4Z1Zkd2FfcHRDUXlwTThhLXpVV3JRaTFfSEl1alRkQ3NjeWtwakhSd2hKUlRHSjlYaWlBSUNueXJBbWV0amxycC1GOTM0aXEzMlM3M0VxNlFBZVRSRDJPdlJybDZGU1k0Tk5SbTR3VGlFN1lfOV9xSXQ1NzBzTDVNWHE4bzNXdHlvQjg2TWxaMzl5TTN2RWFmVjZrRUcyMm5KcGJNMlo3MzVfdVM3MA?oc=5</t>
-  </si>
-  <si>
     <t>Gold price below $5,000 as investors wait on Fed guidance for clues - Yahoo Finance UK</t>
   </si>
   <si>
@@ -2210,6 +2258,15 @@
     <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNMUUxWklvNENGNjNoaF9ER2hvVEp0ZjNEb3hWUHdqY0lzQW9VZWd3VGtRQ1VmcWMyT2wzOUh0X0pqbXNGLWduMGFlajhPZUlaTlpfREhfdXRWbDFUem1tRnlkRVNrSXUtaWhVRERwRUNlTTFHcVYxMFFwNWN0dzVwVXdja09wa0U1SmxlTFZYdWRZa01MdWJtOGI1R1J3RTdZSFdaOU51dkFRRVBrb181UnhQWUNhS2g3YjVfV1JKODNfWjJvQzlxVFVxMGRIZw?oc=5</t>
   </si>
   <si>
+    <t>OFS Financial Services Provides Insurance So You Don’t Have to Choose Between Care and Cost - ThurstonTalk</t>
+  </si>
+  <si>
+    <t>OFS Financial Services Provides Insurance So You Don’t Have to Choose Between Care and Cost  ThurstonTalk</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNcEdHdTZEVDAxNFQyT3pxNGhSdlpSU2FkdG5FYVZEY2lNU1R4YWRzV2lfalhzS005OUdDNzlpd1VuSkZhN3hTMGVqNTdZMVF6a1NRNU9lWjlLYlZaNklGTWcwVDVrYllxTFRVbXF3Umk3dzBoNkpLVlVnWjRQMXgxbThDZkZYb1puRDROU0tldHlaeXduV05qaUxBS240SGZ5UVdQbDlCZ0x4bUQxQ0NrVVJRTnZNVi1TcWE4eFJtZU9SSUVoc1haakg0Zw?oc=5</t>
+  </si>
+  <si>
     <t>ADMA Biologics to Report Fourth Quarter and Full Year 2025 Financial Results on February 25, 2026 - Yahoo Finance</t>
   </si>
   <si>
@@ -2246,6 +2303,42 @@
     <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxNYlB5bmZWdHFBeVJWWGhxNmY5bmRZU1Azd25LNnZHLWpYVkwxWmlnTDF2QXlKb2JZcEJlbGVTT1lScHkxeU1od1N4TVotZkJvT3lRYV9sejB2QXNvWDRhTzljZTVjV2g4NUdTenN0LWpHdHhZQjBxRlRBOFpkSzBKZmVYVHhXS1RHZWRyM1FJa01UVDhqZXh5VVV5dUJPMUNVdHluRXlUN2Nyby1CalB3NkFMYW1UZ1Z5b2F2NkVtVVV3UGFjU2FwdTVjdjhzU0Z0N2hjb0Q1Z09YUmFYN0d2ZmJONFlVYzlOclMzYnhwWDZURWRHUUE?oc=5</t>
   </si>
   <si>
+    <t>Hawaiʻi Was Once A National Leader In Long-Term Care Financing - Honolulu Civil Beat</t>
+  </si>
+  <si>
+    <t>Hawaiʻi Was Once A National Leader In Long-Term Care Financing  Honolulu Civil Beat</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQNkJBUVJVMUd1Mld5MlFVSkZVYXNnUFV1MF9EeEVKX1dSSWxpcGpUbjBGR1BTdTBEem05UmlYdW1HdXlISHhhakVjYndQQUpRU3QxY1R0MFdiSFpNd0xOdE9La0Z2NFlUUkZhUWxHMC1SQ1gzZ1BDYXVVN1NZUElid0dLdmUwMVRyay04VmpnR2dkTVU4M1QtcU5PSlhyaF9kV1hyQQ?oc=5</t>
+  </si>
+  <si>
+    <t>Scottish Water taps Oracle to support agile transformation - Oracle</t>
+  </si>
+  <si>
+    <t>Scottish Water taps Oracle to support agile transformation  Oracle</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE04cnh1aG1Vcnp6bzI0R2ozajBGckJLcy10RG9JdTFlbDVacWRXSzA2V0hZa3d3bHVNY1NiVGRNVDNIM0pHVVM4SEozUG5zOFRmTmU3NVl4X2FyVDVq?oc=5</t>
+  </si>
+  <si>
+    <t>The adoption and efficacy of large language models in US consumer financial complaints - Nature</t>
+  </si>
+  <si>
+    <t>The adoption and efficacy of large language models in US consumer financial complaints  Nature</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE5rbk5HUG1SQ0xjRWVvSF9fTFFsWHh6MGhZaV9KRWRxaTF5LTZ2TnlpWDZOTW1Gb0J0UUJjSEt5ZkVKRldxd05qNXRxak9QN004c2otaF9uRWg4MjVWeWdR?oc=5</t>
+  </si>
+  <si>
+    <t>Endowment &amp; Budget Overview - Carnegie Science</t>
+  </si>
+  <si>
+    <t>Endowment &amp; Budget Overview  Carnegie Science</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9YZXY5aVdtbFpHdk1mQVZvaDgtWEdyaHpYd3N0a0dWZ3NQYlpfaEtwY3c1c2ZDQ0lfX05jdzBGaGZZZGR2UjhiZnZHMFJVa1FmVDFDSVIzbTBCMl9SNG9JVVMwTHl2MnVheEFfbXFWamQ?oc=5</t>
+  </si>
+  <si>
     <t>Luotea plc will publish Financial Statements Release for 2025 on 27 February 2026 - Yahoo Finance</t>
   </si>
   <si>
@@ -2255,6 +2348,15 @@
     <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOV2t0cklVS29jTS1qa1Z3eDhNQms4bWVLUmV3MW94QTVMZnFJVXltbENYZmlPdmRneDM2RWJZbkxtT2o1WU1kdUVNSklKLXJfWU5VMWhMRmJuTzhkaW1jSGtnaFpmREk5Y2liRWVJb1FULWVubEdmTEtQX1ZUSmxRcXdveWJtdWsxODZuc2NR?oc=5</t>
   </si>
   <si>
+    <t>Swift Current Energy Secures Project Financing and Tax Equity for 122 MW Energy Facility in Maine - PR Newswire</t>
+  </si>
+  <si>
+    <t>Swift Current Energy Secures Project Financing and Tax Equity for 122 MW Energy Facility in Maine  PR Newswire</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOa2ZNV3VUc3ZrNktDSF9Hc1BaeGh4aFJaQWg1Uk5oSDFsdy1qQkRKSDVtWjVUV3pnVzloNHFWZ1BnUld1UGJpcnJLLUJsV2V2SVJMcW9QX0RXNDVvLXVhcUpiLXVWSWU0bWdsa3k4SnQ5OXFJeFFwQS13Wk00eGQ1RFc4WkxBcGk0azBXc1hYT3NFenk4R1hHYmFqTDZicXJvdVpiYWtXUFVjT3VBenZuMkx1UFJqSDhIVFczVUlTdl94QmVVWGJsSXd1TTRSWUx5NmVvR2ZxelBSOEtFNkZEU1laNzdOUDY3?oc=5</t>
+  </si>
+  <si>
     <t>Wingstop Inc. Reports Fourth Quarter and Fiscal Year 2025 Financial Results - PR Newswire</t>
   </si>
   <si>
@@ -2291,22 +2393,22 @@
     <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxOSXF3Qlc4SzVaLUtQS1lRT0RGS3BQVUN2aEtPQjVBcThGV2c2M2gzaTBSVFVTOUhkb0VGSlF2d3JMenA2eGdmU1FQODI1NlB6Y2ZKckV3ZTY4LWx3NnlnYlFFLUNlTzdfWXpCLUs0QjZjWG9PUmxQWE9XLTNmYlZ4VDBtLTREWFMyWkpLazlDN1J1aEJCX25qYU9OSUlkSzBaaTBrQXJTU3JQRk1JZHJOX2k2TnJyN0ZMdkJPQ29meUFJOVBDQ3FhY2lULWpOR3ROTml5VW5Ma0ZYZnR3LTNkdkNhY1FNbWxtdlZJX2hZaWE?oc=5</t>
   </si>
   <si>
-    <t>Scottish Water taps Oracle to support agile transformation - Oracle</t>
-  </si>
-  <si>
-    <t>Scottish Water taps Oracle to support agile transformation  Oracle</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE04cnh1aG1Vcnp6bzI0R2ozajBGckJLcy10RG9JdTFlbDVacWRXSzA2V0hZa3d3bHVNY1NiVGRNVDNIM0pHVVM4SEozUG5zOFRmTmU3NVl4X2FyVDVq?oc=5</t>
-  </si>
-  <si>
-    <t>OFS Financial Services Provides Insurance So You Don’t Have to Choose Between Care and Cost - ThurstonTalk</t>
-  </si>
-  <si>
-    <t>OFS Financial Services Provides Insurance So You Don’t Have to Choose Between Care and Cost  ThurstonTalk</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNcEdHdTZEVDAxNFQyT3pxNGhSdlpSU2FkdG5FYVZEY2lNU1R4YWRzV2lfalhzS005OUdDNzlpd1VuSkZhN3hTMGVqNTdZMVF6a1NRNU9lWjlLYlZaNklGTWcwVDVrYllxTFRVbXF3Umk3dzBoNkpLVlVnWjRQMXgxbThDZkZYb1puRDROU0tldHlaeXduV05qaUxBS240SGZ5UVdQbDlCZ0x4bUQxQ0NrVVJRTnZNVi1TcWE4eFJtZU9SSUVoc1haakg0Zw?oc=5</t>
+    <t>SME finance: the geographic gap in equity financing - Centre for Cities</t>
+  </si>
+  <si>
+    <t>SME finance: the geographic gap in equity financing  Centre for Cities</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQMnB0NmlfT2UxUFBXcTN3Um9NOU03UzVYNTdwNmMweC0tbVVDVk1hWVEyQ2hjUVhfblpfY0doUGhpckdHMm9vUDJPXzI3LVpQNG1aR09PbUlpeGVMTzBCTi1QYmhvRjJyR1hiUlBMcWFWVjVpZER2SkxiSUhKeXVrQU5TeEFxY1VIMmF5SjBRWGdLb3c?oc=5</t>
+  </si>
+  <si>
+    <t>Nvidia in focus: Meta partnership expanded, Arm stake sold - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Nvidia in focus: Meta partnership expanded, Arm stake sold  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOSFdMSEFMSDJ5Mk1nTk5xdkhTTHdDQzlJS3NZY2xKTnloYy1Nb2FQYk9QdHBoR3hqZlNOQkxzVHFTbEI5NGJ2OFA0Ulc2clhVR09nYTc3OU5jdVhMTFRDV0w2dERzWVVVQmJJWURFWUh3OEh0OTYwM2lHMkN2em9qcXotNE1sa1dzZjNaU1pn?oc=5</t>
   </si>
   <si>
     <t>Verastem Oncology to Report Fourth Quarter and Full Year 2025 Financial Results on March 4, 2026 - Yahoo Finance</t>
@@ -2318,15 +2420,6 @@
     <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOeHVlU1QyOWNaQnd4MlQ3dkF0RXdPczhfc0NJRDZpd2c1bDNQQThrblhraWQ2S0xhdk1kVGtDTkRrVktTZFE4c0hkcGlYS1hRdVYya0JnUlNrcEFQY09tcHBSNlhQS2pkdVByS3pFc0gydl9NOGRoQW5zX2ZLT0NZMzNkem9pRjBtQnhTZ3lB?oc=5</t>
   </si>
   <si>
-    <t>Nvidia in focus: Meta partnership expanded, Arm stake sold - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Nvidia in focus: Meta partnership expanded, Arm stake sold  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOSFdMSEFMSDJ5Mk1nTk5xdkhTTHdDQzlJS3NZY2xKTnloYy1Nb2FQYk9QdHBoR3hqZlNOQkxzVHFTbEI5NGJ2OFA0Ulc2clhVR09nYTc3OU5jdVhMTFRDV0w2dERzWVVVQmJJWURFWUh3OEh0OTYwM2lHMkN2em9qcXotNE1sa1dzZjNaU1pn?oc=5</t>
-  </si>
-  <si>
     <t>Palantir upgraded, Workday downgraded: Wall Street's top analyst calls - Yahoo Finance</t>
   </si>
   <si>
@@ -2354,15 +2447,6 @@
     <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNWk9Ha2ZHM3NrNmNMMjh2ZFlaX0dxdXdiYnBucXpHNTZZcTE1RGl6SGRCUzdMSW9yYzNqTGxRckhYT0NwUzhHVkxYSGcydVlrbTl6NzdyeG9SOW1aRmpUZ041T1V2OVNRdmRlaHVQVHRsWGpPUUlIc3I1a2dwWWJoTDFIQU90TmhxR2NQanZ1YmNkZw?oc=5</t>
   </si>
   <si>
-    <t>Swift Current Energy Secures Project Financing and Tax Equity for 122 MW Energy Facility in Maine - PR Newswire</t>
-  </si>
-  <si>
-    <t>Swift Current Energy Secures Project Financing and Tax Equity for 122 MW Energy Facility in Maine  PR Newswire</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOa2ZNV3VUc3ZrNktDSF9Hc1BaeGh4aFJaQWg1Uk5oSDFsdy1qQkRKSDVtWjVUV3pnVzloNHFWZ1BnUld1UGJpcnJLLUJsV2V2SVJMcW9QX0RXNDVvLXVhcUpiLXVWSWU0bWdsa3k4SnQ5OXFJeFFwQS13Wk00eGQ1RFc4WkxBcGk0azBXc1hYT3NFenk4R1hHYmFqTDZicXJvdVpiYWtXUFVjT3VBenZuMkx1UFJqSDhIVFczVUlTdl94QmVVWGJsSXd1TTRSWUx5NmVvR2ZxelBSOEtFNkZEU1laNzdOUDY3?oc=5</t>
-  </si>
-  <si>
     <t>Harrow To Report Fourth Quarter and Year-End 2025 Financial Results After Market Close on March 2, 2026 - Yahoo Finance</t>
   </si>
   <si>
@@ -2390,96 +2474,6 @@
     <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNUktiOHpfaDBaekR6MmlpQVVTOXZ6TUZKYWxzblF4eE1acE54eXlNYWwtOVdYbmxadjhKNk5Vc1ZXVFFlNzQ1Zkt1Y0hfbDBlQ2VPOEM1Q3lEQ0FNam9SWkh2ZWFmZXE0azdWalotcFZmVzJTWGhVdWp3ZlJWRnk0VUlTRFFQNGtaRWc?oc=5</t>
   </si>
   <si>
-    <t>Hawaiʻi Was Once A National Leader In Long-Term Care Financing - Honolulu Civil Beat</t>
-  </si>
-  <si>
-    <t>Hawaiʻi Was Once A National Leader In Long-Term Care Financing  Honolulu Civil Beat</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQNkJBUVJVMUd1Mld5MlFVSkZVYXNnUFV1MF9EeEVKX1dSSWxpcGpUbjBGR1BTdTBEem05UmlYdW1HdXlISHhhakVjYndQQUpRU3QxY1R0MFdiSFpNd0xOdE9La0Z2NFlUUkZhUWxHMC1SQ1gzZ1BDYXVVN1NZUElid0dLdmUwMVRyay04VmpnR2dkTVU4M1QtcU5PSlhyaF9kV1hyQQ?oc=5</t>
-  </si>
-  <si>
-    <t>The adoption and efficacy of large language models in US consumer financial complaints - Nature</t>
-  </si>
-  <si>
-    <t>The adoption and efficacy of large language models in US consumer financial complaints  Nature</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE5rbk5HUG1SQ0xjRWVvSF9fTFFsWHh6MGhZaV9KRWRxaTF5LTZ2TnlpWDZOTW1Gb0J0UUJjSEt5ZkVKRldxd05qNXRxak9QN004c2otaF9uRWg4MjVWeWdR?oc=5</t>
-  </si>
-  <si>
-    <t>NewAmsterdam Pharma Reports Full Year 2025 Financial Results and Provides Corporate Update - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>NewAmsterdam Pharma Reports Full Year 2025 Financial Results and Provides Corporate Update  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPM0xkQ2h2UEN6cXdCRUprYkdxM3dSWV9mbG40R0tLcGtxY1BUaUJaU3hTaDM5dlcwRDVwcVU2eFZEbnczRnliY2ZncmxGbzNMa3lxSUM2dklkeW5Tc19GS2F1TnI2UTVVbkRsNlhndi1VWG5hX2tFOTBnYk9KNjdJa1lTbXJaQW82dUVz?oc=5</t>
-  </si>
-  <si>
-    <t>Endowment &amp; Budget Overview - Carnegie Science</t>
-  </si>
-  <si>
-    <t>Endowment &amp; Budget Overview  Carnegie Science</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9YZXY5aVdtbFpHdk1mQVZvaDgtWEdyaHpYd3N0a0dWZ3NQYlpfaEtwY3c1c2ZDQ0lfX05jdzBGaGZZZGR2UjhiZnZHMFJVa1FmVDFDSVIzbTBCMl9SNG9JVVMwTHl2MnVheEFfbXFWamQ?oc=5</t>
-  </si>
-  <si>
-    <t>Nvidia and Meta expand GPU team with millions of additional AI chips - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Nvidia and Meta expand GPU team with millions of additional AI chips  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNN3NVRzF3eEtIRXh5YzJzaU5TdldkbFExWFA4bi1zUGw5TEYweXd0QlluUk44cU5vSUJ1dUxNa1dEY2djdHFlS1ROMkw4RjNXa2Uza1EwRVlzLTAzSjNvbngtaEtYQUxqZkJXMVE1N0dQdTU2OFhmSWdLREJSeGNSV2RNcG5xYjdJbDZLWU9zcDlvYzVlQzFZa3IyZ0FqX2xwY0pQWU1HdkVuMWlJZmlXU0NRT18?oc=5</t>
-  </si>
-  <si>
-    <t>Charleston launches Financial Empowerment Center for residents - Live 5 News</t>
-  </si>
-  <si>
-    <t>Charleston launches Financial Empowerment Center for residents  Live 5 News</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOQXhWZFN3ek1UV3F2UjBhVXhKZlpva3pXUFRBdnJtYk5LYUc0aHdYLVlTbEw2MDRyd3hjZlNSdmUtVHEzb0FPT1RQRWtMbWN4LXdzS3c0bWZ1bEU5UDJ1V2J0OFJGemNmSEg5RE5zandQTXJPYjNIUzVucGdIcVBORTFPdldCY3Q1SjMtQjA2NS1BMmdoTkM0RXhwdXbSAbABQVVfeXFMTVFLTldMZmRxZnBLS3ltT2JQaDJFcEJWR2tMZXlVOWtNSWxDbVRMNDJUSlk1WkJVYndMSmMxTlNkT3VpclJtak1DcGtKSDR5eTIzeGtGWk9hVzBtOEZUcndOeDFtQXJLbGgxRl9mWTRzQVpydC1MX2RXZVc5VWN6cDQyc1RqRnVkeklSRUV1SU9tcHZheFRHbTFkcTFjQkI1OW9FdTF6LV9lT3FNSXNKWjY?oc=5</t>
-  </si>
-  <si>
-    <t>Bill to boost financial aid for students at WA’s private colleges moves out of Senate - Washington State Standard</t>
-  </si>
-  <si>
-    <t>Bill to boost financial aid for students at WA’s private colleges moves out of Senate  Washington State Standard</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQeDJBX2M3WlM2QlZvLTVPb1NuSTZXcHN6bV9zM0RBamNKN1ZnUGFpQXlFazNTWWNydWp1NEhadEhyWkRkUnI5SjhXMHJDQUZZM0xNRW4xU2duS1hqMk03QXlPbmhsalJ1ZjhjbThLdGdYMW50enlWY0l0UjE1dG15Z0FzVGl3UmlvWnQybDZJMk9qQlFqalY3dWhIYTEzVkQwckFNLXFzN3d4UVlVWDFsRTdZZ0VaeE1yMUtzWkpPNmhGeEhIUi1IVHdDNUlTVUs2VWc?oc=5</t>
-  </si>
-  <si>
-    <t>Saving What's Left At The End Of The Month Sounds Sensible. It Might Be Secretly Sabotaging Your Financial Future, Along With These Habits - Yahoo Finance UK</t>
-  </si>
-  <si>
-    <t>Saving What's Left At The End Of The Month Sounds Sensible. It Might Be Secretly Sabotaging Your Financial Future, Along With These Habits  Yahoo Finance UK</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNYTU5S3FPbExaZG9ZZzgwcDd2Tk84dWhmUEY5MHhtY1h4bk04cG1aNkZNWHRRN1MzUTh3bDVnY0pfUVN5SjBINEVxRXRrN2c2SHI1bUpoNVI3SFpqd2l1a25LRE1iUjFZUWZ2ak45T0RTd2NkQlJ5b0VRNE5BMHgzMGxB?oc=5</t>
-  </si>
-  <si>
-    <t>Some People Think This AI Stock Is Evil -- But It Has Been Wildly Successful Financially - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Some People Think This AI Stock Is Evil -- But It Has Been Wildly Successful Financially  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFBuSld4MnRyYUE2R3hUM3VRSVNmd0hoSmUyckN4ZXBCMHBPZXR6dTZYdjZ5OGNQaU51U3pQQk94Y19feXppZVJycUVZaFFoUHpPTFF5NmtsQWJxUmV2cVZIYkJwU0pZZkRzRU9JSEZnUm9IdDlZbzRLcEJPNmM?oc=5</t>
-  </si>
-  <si>
-    <t>Sweden's financial watchdog fines SBB for accounting violations - Reuters</t>
-  </si>
-  <si>
-    <t>Sweden's financial watchdog fines SBB for accounting violations  Reuters</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQdDdzRU5RUmg1QndtNy05VFJzNHk0Q1NfVFVsNzF0U2pjNUZaek9fMmZKUXBiNGlEbG9uNG5tQ2QxNmtqREFXWEZTczJyejFkZEhCSHFHanROc1ZUYjRfZ0Ryd3VsTUtDNWY4bTdCU2lJczJ0QndSN3VIOU0tMDRXaDBMbUNKYzhVeVVZVVVDTWN6Z0dwcUZORzhQOXZVcGtnOW4zaUdrWjdINXNpRks4eQ?oc=5</t>
-  </si>
-  <si>
     <t>Mortgage Rates Today, Wednesday, February 18: Rates Remain Low</t>
   </si>
   <si>
@@ -2771,6 +2765,12 @@
     <t>https://www.investing.com/news/stock-market-news/moodys-forecasts-upbeat-2026-profit-on-strong-demand-for-credit-ratings-4510892</t>
   </si>
   <si>
+    <t>LIVE: White House briefing with Karoline Leavitt</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=f0LW2vYWuag</t>
+  </si>
+  <si>
     <t>LIVE: House's Hakeem Jeffries holds a briefing in Washington</t>
   </si>
   <si>
@@ -2853,12 +2853,6 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=osMjcYVxqEg</t>
-  </si>
-  <si>
-    <t>BAE Systems sees years of growth in ‘new era’ of defense spending</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=eBgrSqQEDX4</t>
   </si>
   <si>
     <t>Candidaturas de empresas a linha de crédito à tesouraria devido ao mau tempo somam 905 milhões</t>
@@ -3029,6 +3023,15 @@
     <t>https://www.doutorfinancas.pt/vida-e-familia/aumento-abono-de-familia-2026/</t>
   </si>
   <si>
+    <t>Isabel Ferraz é a nova Diretora Comercial da Mapfre Portugal</t>
+  </si>
+  <si>
+    <t>A seguradora Mapfre Portugal anunciou a nomeação de Isabel Ferraz como nova Diretora Comercial da Mapfre Portugal em comunicado. A gestora portuguesa fica responsável por liderar toda a área comercial da Mapfre no país, incluindo canais estratégicos de acordos de distribuição, brokers, digital e a área de Marketing e Clientes. Isabel Ferraz regressa a Portugal […]</t>
+  </si>
+  <si>
+    <t>https://eco.sapo.pt/2026/02/18/isabel-ferraz-e-a-nova-diretora-comercial-da-mapfre-portugal/</t>
+  </si>
+  <si>
     <t>FC Porto teve prejuízos de 866 mil euros no primeiro semestre</t>
   </si>
   <si>
@@ -3215,15 +3218,6 @@
     <t>https://eco.sapo.pt/2026/02/18/companhia-ferroviaria-alema-sofre-ciberataque-de-grande-magnitude/</t>
   </si>
   <si>
-    <t>Nova SBE: em defesa do progresso</t>
-  </si>
-  <si>
-    <t>A rubrica Geração de Ideias dá voz aos distinguidos com o Prémio Professor Jacinto Nunes, atribuído pelo Banco de Portugal, e que distingue os melhores alunos da licenciatura em Economia. Joaquim Rodrigues foi distinguido enquanto aluno da NOVA SBE, relativamente à edição de 2024/2025. O progresso acontece quando alguém, na sua área de influência (limitada) […]</t>
-  </si>
-  <si>
-    <t>https://eco.sapo.pt/opiniao/nova-sbe-em-defesa-do-progresso/</t>
-  </si>
-  <si>
     <t>The Best Way to See the New York City Skyline? Sleep Inside It at This NoMad Hotel</t>
   </si>
   <si>
@@ -3249,6 +3243,16 @@
   </si>
   <si>
     <t>https://www.independent.co.uk/tech/ai-delusion-psychosis-chatgpt-b2922989.html</t>
+  </si>
+  <si>
+    <t>Gold Will Likely Outperform Bitcoin for Years As ‘Quantum Cloud’ Hangs Over BTC’s Head: Analyst Willy Woo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyst Willy Woo believes gold will likely continue to outperform Bitcoin (BTC) for years to come. Woo tells his 1.2 million followers on X that BTC’s 12-year uptrend against the precious metal has been broken. He believes it’s due to concerns that quantum computers could eventually break BTC’s cryptographic security. “12-year trend broken. BTC should […]
+The post Gold Will Likely Outperform Bitcoin for Years As ‘Quantum Cloud’ Hangs Over BTC’s Head: Analyst Willy Woo appeared first on The Daily Hodl.</t>
+  </si>
+  <si>
+    <t>https://dailyhodl.com/2026/02/18/gold-will-likely-outperform-bitcoin-for-years-as-quantum-cloud-hangs-over-btcs-head-analyst-willy-woo/</t>
   </si>
   <si>
     <t>Crypto Flows To Human Traffickers Reaches ‘Hundreds of Millions of Dollars,’ Surging 85% in One Year: Chainalysis</t>
@@ -3299,6 +3303,15 @@
   </si>
   <si>
     <t>https://dailyhodl.com/2026/02/17/ymax-opens-early-access-to-stablecoin-yield-orchestration-platform/</t>
+  </si>
+  <si>
+    <t>Treasury bills seen as primary driver of Bitcoin's price: Report</t>
+  </si>
+  <si>
+    <t>New Keyrock research finds not all newly created money impacts risk assets due to how fresh liquidity flows through the economy.</t>
+  </si>
+  <si>
+    <t>https://cointelegraph.com/news/treasury-bills-primary-driver-bitcoin-price?utm_source=rss_feed&amp;utm_medium=rss&amp;utm_campaign=rss_partner_inbound</t>
   </si>
   <si>
     <t>Bitcoin 2024 buyers steady BTC price as trader sees $52K 'next week or so'</t>
@@ -4026,7 +4039,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D430"/>
+  <dimension ref="A1:D431"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -4485,13 +4498,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C33" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
@@ -4499,13 +4512,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
@@ -4513,13 +4526,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C35" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -4527,13 +4540,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B36" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C36" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -4541,13 +4554,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B37" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C37" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -4555,13 +4568,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -4569,13 +4582,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B39" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C39" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -4583,13 +4596,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B40" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C40" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -4597,13 +4610,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B41" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C41" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -4611,13 +4624,13 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B42" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C42" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -4625,13 +4638,13 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B43" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C43" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -4639,13 +4652,13 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B44" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C44" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -4653,13 +4666,13 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B45" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C45" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -4667,13 +4680,13 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B46" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C46" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -4681,13 +4694,13 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B47" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C47" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -4695,13 +4708,13 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B48" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C48" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -4709,13 +4722,13 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B49" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C49" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -4723,13 +4736,13 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B50" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C50" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -4737,13 +4750,13 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B51" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C51" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -4751,13 +4764,13 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B52" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C52" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -4765,13 +4778,13 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B53" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C53" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -4779,13 +4792,13 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B54" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C54" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -4793,13 +4806,13 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B55" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C55" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -4807,13 +4820,13 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B56" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C56" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -4821,13 +4834,13 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B57" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C57" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -4835,13 +4848,13 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B58" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C58" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -4849,13 +4862,13 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B59" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C59" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -4863,13 +4876,13 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B60" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C60" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -4877,13 +4890,13 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B61" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C61" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
@@ -4891,13 +4904,13 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B62" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C62" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
@@ -4905,13 +4918,13 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B63" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C63" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
@@ -4919,13 +4932,13 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B64" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C64" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
@@ -4933,13 +4946,13 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B65" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C65" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D65" t="s">
         <v>7</v>
@@ -4947,13 +4960,13 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B66" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C66" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D66" t="s">
         <v>7</v>
@@ -4961,13 +4974,13 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B67" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C67" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D67" t="s">
         <v>7</v>
@@ -4975,13 +4988,13 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B68" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C68" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D68" t="s">
         <v>7</v>
@@ -4989,13 +5002,13 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B69" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C69" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D69" t="s">
         <v>7</v>
@@ -5003,13 +5016,13 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B70" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C70" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D70" t="s">
         <v>7</v>
@@ -5017,13 +5030,13 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B71" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C71" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D71" t="s">
         <v>7</v>
@@ -5031,13 +5044,13 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B72" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C72" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D72" t="s">
         <v>7</v>
@@ -5045,13 +5058,13 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B73" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C73" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D73" t="s">
         <v>7</v>
@@ -5059,13 +5072,13 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B74" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C74" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D74" t="s">
         <v>7</v>
@@ -5073,13 +5086,13 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C75" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D75" t="s">
         <v>7</v>
@@ -5087,13 +5100,13 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B76" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C76" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D76" t="s">
         <v>7</v>
@@ -5101,13 +5114,13 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B77" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C77" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
@@ -5115,13 +5128,13 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B78" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C78" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D78" t="s">
         <v>7</v>
@@ -5129,13 +5142,13 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B79" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C79" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D79" t="s">
         <v>7</v>
@@ -5143,13 +5156,13 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B80" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C80" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D80" t="s">
         <v>7</v>
@@ -5157,13 +5170,13 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B81" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C81" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D81" t="s">
         <v>7</v>
@@ -5171,13 +5184,13 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B82" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C82" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D82" t="s">
         <v>7</v>
@@ -5185,13 +5198,13 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B83" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C83" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D83" t="s">
         <v>7</v>
@@ -5199,13 +5212,13 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B84" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C84" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D84" t="s">
         <v>7</v>
@@ -5213,13 +5226,13 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B85" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C85" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D85" t="s">
         <v>7</v>
@@ -5227,13 +5240,13 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B86" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C86" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D86" t="s">
         <v>7</v>
@@ -5241,13 +5254,13 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B87" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C87" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D87" t="s">
         <v>7</v>
@@ -5255,13 +5268,13 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B88" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D88" t="s">
         <v>7</v>
@@ -5269,13 +5282,13 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B89" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C89" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D89" t="s">
         <v>7</v>
@@ -5283,13 +5296,13 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B90" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C90" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D90" t="s">
         <v>7</v>
@@ -5297,13 +5310,13 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B91" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C91" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D91" t="s">
         <v>7</v>
@@ -5311,13 +5324,13 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B92" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C92" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D92" t="s">
         <v>7</v>
@@ -5325,13 +5338,13 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B93" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C93" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D93" t="s">
         <v>7</v>
@@ -5339,13 +5352,13 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B94" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C94" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D94" t="s">
         <v>7</v>
@@ -5353,13 +5366,13 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B95" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C95" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D95" t="s">
         <v>7</v>
@@ -5367,13 +5380,13 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B96" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C96" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D96" t="s">
         <v>7</v>
@@ -5381,13 +5394,13 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B97" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C97" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D97" t="s">
         <v>7</v>
@@ -5395,13 +5408,13 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B98" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C98" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D98" t="s">
         <v>7</v>
@@ -5409,13 +5422,13 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B99" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C99" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D99" t="s">
         <v>7</v>
@@ -5423,13 +5436,13 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B100" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C100" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D100" t="s">
         <v>7</v>
@@ -5437,13 +5450,13 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B101" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C101" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D101" t="s">
         <v>7</v>
@@ -5451,13 +5464,13 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B102" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C102" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D102" t="s">
         <v>7</v>
@@ -5465,13 +5478,13 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B103" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C103" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
@@ -5479,13 +5492,13 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B104" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C104" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D104" t="s">
         <v>7</v>
@@ -5493,13 +5506,13 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B105" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C105" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D105" t="s">
         <v>7</v>
@@ -5507,13 +5520,13 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B106" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C106" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D106" t="s">
         <v>7</v>
@@ -5521,13 +5534,13 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B107" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C107" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D107" t="s">
         <v>7</v>
@@ -5535,13 +5548,13 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B108" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C108" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D108" t="s">
         <v>7</v>
@@ -5549,13 +5562,13 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B109" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C109" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D109" t="s">
         <v>7</v>
@@ -5563,13 +5576,13 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B110" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C110" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D110" t="s">
         <v>7</v>
@@ -5577,13 +5590,13 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B111" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C111" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D111" t="s">
         <v>7</v>
@@ -5591,13 +5604,13 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B112" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C112" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
@@ -5605,13 +5618,13 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B113" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C113" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
@@ -5619,13 +5632,13 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B114" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C114" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D114" t="s">
         <v>7</v>
@@ -5633,13 +5646,13 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B115" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C115" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D115" t="s">
         <v>7</v>
@@ -5647,13 +5660,13 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B116" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C116" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D116" t="s">
         <v>7</v>
@@ -5661,13 +5674,13 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B117" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C117" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D117" t="s">
         <v>7</v>
@@ -5675,13 +5688,13 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B118" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C118" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D118" t="s">
         <v>7</v>
@@ -5689,13 +5702,13 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B119" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C119" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D119" t="s">
         <v>7</v>
@@ -5703,13 +5716,13 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B120" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C120" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D120" t="s">
         <v>7</v>
@@ -5717,13 +5730,13 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B121" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C121" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
@@ -5731,13 +5744,13 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B122" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C122" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D122" t="s">
         <v>7</v>
@@ -5745,13 +5758,13 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B123" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C123" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -5759,13 +5772,13 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B124" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C124" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D124" t="s">
         <v>7</v>
@@ -5773,13 +5786,13 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B125" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C125" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D125" t="s">
         <v>7</v>
@@ -5787,13 +5800,13 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B126" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C126" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D126" t="s">
         <v>7</v>
@@ -5801,13 +5814,13 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B127" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C127" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D127" t="s">
         <v>7</v>
@@ -5815,13 +5828,13 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B128" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C128" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D128" t="s">
         <v>7</v>
@@ -5829,13 +5842,13 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B129" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C129" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D129" t="s">
         <v>7</v>
@@ -5843,13 +5856,13 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B130" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C130" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D130" t="s">
         <v>7</v>
@@ -5857,13 +5870,13 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B131" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C131" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D131" t="s">
         <v>7</v>
@@ -5871,13 +5884,13 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B132" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C132" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D132" t="s">
         <v>7</v>
@@ -5885,13 +5898,13 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B133" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C133" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D133" t="s">
         <v>7</v>
@@ -5899,13 +5912,13 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C134" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D134" t="s">
         <v>7</v>
@@ -5913,13 +5926,13 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B135" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C135" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D135" t="s">
         <v>7</v>
@@ -5927,13 +5940,13 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B136" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C136" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D136" t="s">
         <v>7</v>
@@ -5941,13 +5954,13 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B137" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C137" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D137" t="s">
         <v>7</v>
@@ -5955,13 +5968,13 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B138" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C138" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D138" t="s">
         <v>7</v>
@@ -5969,13 +5982,13 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B139" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C139" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
@@ -5983,13 +5996,13 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B140" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C140" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D140" t="s">
         <v>7</v>
@@ -5997,13 +6010,13 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B141" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C141" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
@@ -6011,13 +6024,13 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B142" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C142" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
@@ -6025,13 +6038,13 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B143" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C143" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
@@ -6039,13 +6052,13 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B144" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C144" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
@@ -6053,13 +6066,13 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B145" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C145" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D145" t="s">
         <v>7</v>
@@ -6067,13 +6080,13 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B146" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C146" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D146" t="s">
         <v>7</v>
@@ -6081,13 +6094,13 @@
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B147" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C147" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D147" t="s">
         <v>7</v>
@@ -6095,13 +6108,13 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B148" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C148" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D148" t="s">
         <v>7</v>
@@ -6109,13 +6122,13 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B149" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C149" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D149" t="s">
         <v>7</v>
@@ -6123,13 +6136,13 @@
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B150" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C150" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D150" t="s">
         <v>7</v>
@@ -6137,13 +6150,13 @@
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B151" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C151" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D151" t="s">
         <v>7</v>
@@ -6151,13 +6164,13 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B152" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C152" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D152" t="s">
         <v>7</v>
@@ -6165,13 +6178,13 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B153" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C153" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D153" t="s">
         <v>7</v>
@@ -6179,13 +6192,13 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B154" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C154" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D154" t="s">
         <v>7</v>
@@ -6193,13 +6206,13 @@
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B155" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C155" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D155" t="s">
         <v>7</v>
@@ -6207,13 +6220,13 @@
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B156" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C156" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D156" t="s">
         <v>7</v>
@@ -6221,13 +6234,13 @@
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B157" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C157" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D157" t="s">
         <v>7</v>
@@ -6235,13 +6248,13 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B158" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C158" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D158" t="s">
         <v>7</v>
@@ -6249,13 +6262,13 @@
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B159" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C159" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D159" t="s">
         <v>7</v>
@@ -6263,13 +6276,13 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B160" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C160" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D160" t="s">
         <v>7</v>
@@ -6277,13 +6290,13 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B161" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C161" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -6291,13 +6304,13 @@
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B162" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C162" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D162" t="s">
         <v>7</v>
@@ -6305,13 +6318,13 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B163" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C163" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
@@ -6319,13 +6332,13 @@
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B164" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C164" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D164" t="s">
         <v>7</v>
@@ -6333,13 +6346,13 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B165" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C165" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D165" t="s">
         <v>7</v>
@@ -6347,13 +6360,13 @@
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B166" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C166" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D166" t="s">
         <v>7</v>
@@ -6361,13 +6374,13 @@
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B167" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C167" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D167" t="s">
         <v>7</v>
@@ -6375,13 +6388,13 @@
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B168" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C168" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D168" t="s">
         <v>7</v>
@@ -6389,13 +6402,13 @@
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B169" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C169" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D169" t="s">
         <v>7</v>
@@ -6403,13 +6416,13 @@
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B170" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C170" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D170" t="s">
         <v>7</v>
@@ -6417,13 +6430,13 @@
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B171" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C171" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
@@ -6431,13 +6444,13 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B172" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C172" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D172" t="s">
         <v>7</v>
@@ -6445,13 +6458,13 @@
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B173" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C173" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D173" t="s">
         <v>7</v>
@@ -6459,13 +6472,13 @@
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B174" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C174" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -6473,13 +6486,13 @@
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B175" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C175" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -6487,13 +6500,13 @@
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B176" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C176" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
@@ -6501,13 +6514,13 @@
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B177" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C177" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -6515,13 +6528,13 @@
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B178" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C178" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -6529,13 +6542,13 @@
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B179" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C179" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
@@ -6543,13 +6556,13 @@
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B180" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C180" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -6557,13 +6570,13 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B181" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C181" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -6571,13 +6584,13 @@
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B182" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C182" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D182" t="s">
         <v>7</v>
@@ -6585,13 +6598,13 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B183" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C183" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
@@ -6599,13 +6612,13 @@
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B184" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C184" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D184" t="s">
         <v>7</v>
@@ -6613,13 +6626,13 @@
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B185" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C185" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D185" t="s">
         <v>7</v>
@@ -6627,13 +6640,13 @@
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B186" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C186" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D186" t="s">
         <v>7</v>
@@ -6641,13 +6654,13 @@
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B187" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C187" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
@@ -6655,13 +6668,13 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B188" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C188" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D188" t="s">
         <v>7</v>
@@ -6669,13 +6682,13 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B189" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C189" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D189" t="s">
         <v>7</v>
@@ -6683,13 +6696,13 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B190" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C190" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D190" t="s">
         <v>7</v>
@@ -6697,13 +6710,13 @@
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B191" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C191" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D191" t="s">
         <v>7</v>
@@ -6711,13 +6724,13 @@
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B192" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C192" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D192" t="s">
         <v>7</v>
@@ -6725,13 +6738,13 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B193" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C193" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D193" t="s">
         <v>7</v>
@@ -6739,13 +6752,13 @@
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B194" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C194" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D194" t="s">
         <v>7</v>
@@ -6753,13 +6766,13 @@
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B195" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C195" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D195" t="s">
         <v>7</v>
@@ -6767,13 +6780,13 @@
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B196" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C196" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D196" t="s">
         <v>7</v>
@@ -6781,13 +6794,13 @@
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B197" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C197" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D197" t="s">
         <v>7</v>
@@ -6795,13 +6808,13 @@
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B198" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C198" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D198" t="s">
         <v>7</v>
@@ -6809,13 +6822,13 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B199" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C199" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D199" t="s">
         <v>7</v>
@@ -6823,13 +6836,13 @@
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B200" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C200" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D200" t="s">
         <v>7</v>
@@ -6837,13 +6850,13 @@
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B201" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C201" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D201" t="s">
         <v>7</v>
@@ -6851,13 +6864,13 @@
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B202" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C202" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -6865,13 +6878,13 @@
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B203" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C203" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -6879,13 +6892,13 @@
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B204" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C204" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D204" t="s">
         <v>7</v>
@@ -6893,13 +6906,13 @@
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B205" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C205" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D205" t="s">
         <v>7</v>
@@ -6907,13 +6920,13 @@
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B206" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C206" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D206" t="s">
         <v>7</v>
@@ -6921,13 +6934,13 @@
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B207" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C207" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D207" t="s">
         <v>7</v>
@@ -6935,13 +6948,13 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B208" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C208" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D208" t="s">
         <v>7</v>
@@ -6949,13 +6962,13 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B209" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C209" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D209" t="s">
         <v>7</v>
@@ -6963,13 +6976,13 @@
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B210" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C210" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D210" t="s">
         <v>7</v>
@@ -6977,13 +6990,13 @@
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B211" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C211" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D211" t="s">
         <v>7</v>
@@ -6991,13 +7004,13 @@
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B212" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C212" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D212" t="s">
         <v>7</v>
@@ -7005,13 +7018,13 @@
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B213" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C213" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D213" t="s">
         <v>7</v>
@@ -7019,13 +7032,13 @@
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B214" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C214" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D214" t="s">
         <v>7</v>
@@ -7033,13 +7046,13 @@
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B215" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C215" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D215" t="s">
         <v>7</v>
@@ -7047,13 +7060,13 @@
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B216" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C216" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D216" t="s">
         <v>7</v>
@@ -7061,13 +7074,13 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B217" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C217" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D217" t="s">
         <v>7</v>
@@ -7075,13 +7088,13 @@
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B218" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C218" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D218" t="s">
         <v>7</v>
@@ -7089,13 +7102,13 @@
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B219" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C219" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D219" t="s">
         <v>7</v>
@@ -7103,13 +7116,13 @@
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B220" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C220" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D220" t="s">
         <v>7</v>
@@ -7117,13 +7130,13 @@
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B221" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C221" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D221" t="s">
         <v>7</v>
@@ -7131,13 +7144,13 @@
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B222" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C222" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D222" t="s">
         <v>7</v>
@@ -7145,13 +7158,13 @@
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B223" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C223" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D223" t="s">
         <v>7</v>
@@ -7159,13 +7172,13 @@
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B224" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C224" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D224" t="s">
         <v>7</v>
@@ -7173,13 +7186,13 @@
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B225" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C225" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D225" t="s">
         <v>7</v>
@@ -7187,13 +7200,13 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B226" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C226" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D226" t="s">
         <v>7</v>
@@ -7201,13 +7214,13 @@
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B227" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C227" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D227" t="s">
         <v>7</v>
@@ -7215,13 +7228,13 @@
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B228" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C228" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D228" t="s">
         <v>7</v>
@@ -7229,13 +7242,13 @@
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B229" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C229" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D229" t="s">
         <v>7</v>
@@ -7243,13 +7256,13 @@
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B230" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C230" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
@@ -7257,13 +7270,13 @@
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B231" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C231" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D231" t="s">
         <v>7</v>
@@ -7271,13 +7284,13 @@
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B232" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C232" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D232" t="s">
         <v>7</v>
@@ -7285,13 +7298,13 @@
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B233" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C233" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D233" t="s">
         <v>7</v>
@@ -7299,13 +7312,13 @@
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B234" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C234" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D234" t="s">
         <v>7</v>
@@ -7313,13 +7326,13 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B235" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C235" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D235" t="s">
         <v>7</v>
@@ -7327,13 +7340,13 @@
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B236" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C236" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D236" t="s">
         <v>7</v>
@@ -7341,13 +7354,13 @@
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B237" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C237" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D237" t="s">
         <v>7</v>
@@ -7355,13 +7368,13 @@
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B238" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C238" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D238" t="s">
         <v>7</v>
@@ -7369,13 +7382,13 @@
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B239" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C239" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D239" t="s">
         <v>7</v>
@@ -7383,13 +7396,13 @@
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B240" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C240" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D240" t="s">
         <v>7</v>
@@ -7397,13 +7410,13 @@
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B241" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C241" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D241" t="s">
         <v>7</v>
@@ -7411,13 +7424,13 @@
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B242" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C242" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D242" t="s">
         <v>7</v>
@@ -7425,13 +7438,13 @@
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B243" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C243" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D243" t="s">
         <v>7</v>
@@ -7439,13 +7452,13 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B244" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C244" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D244" t="s">
         <v>7</v>
@@ -7453,13 +7466,13 @@
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B245" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C245" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D245" t="s">
         <v>7</v>
@@ -7467,13 +7480,13 @@
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B246" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C246" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D246" t="s">
         <v>7</v>
@@ -7481,13 +7494,13 @@
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B247" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C247" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D247" t="s">
         <v>7</v>
@@ -7495,13 +7508,13 @@
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B248" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C248" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D248" t="s">
         <v>7</v>
@@ -7509,13 +7522,13 @@
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B249" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C249" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D249" t="s">
         <v>7</v>
@@ -7523,13 +7536,13 @@
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B250" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C250" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D250" t="s">
         <v>7</v>
@@ -7537,13 +7550,13 @@
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B251" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C251" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D251" t="s">
         <v>7</v>
@@ -7551,13 +7564,13 @@
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B252" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C252" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D252" t="s">
         <v>7</v>
@@ -7565,13 +7578,13 @@
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B253" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C253" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D253" t="s">
         <v>7</v>
@@ -7579,13 +7592,13 @@
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B254" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C254" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D254" t="s">
         <v>7</v>
@@ -7593,13 +7606,13 @@
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B255" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C255" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D255" t="s">
         <v>7</v>
@@ -7607,13 +7620,13 @@
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B256" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C256" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D256" t="s">
         <v>7</v>
@@ -7621,13 +7634,13 @@
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B257" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C257" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D257" t="s">
         <v>7</v>
@@ -7635,13 +7648,13 @@
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B258" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C258" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D258" t="s">
         <v>7</v>
@@ -7649,13 +7662,13 @@
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B259" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C259" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D259" t="s">
         <v>7</v>
@@ -7663,13 +7676,13 @@
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B260" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C260" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D260" t="s">
         <v>7</v>
@@ -7677,13 +7690,13 @@
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B261" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C261" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D261" t="s">
         <v>7</v>
@@ -7691,13 +7704,13 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B262" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C262" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D262" t="s">
         <v>7</v>
@@ -7705,13 +7718,13 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B263" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C263" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D263" t="s">
         <v>7</v>
@@ -7719,13 +7732,13 @@
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B264" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C264" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D264" t="s">
         <v>7</v>
@@ -7733,13 +7746,13 @@
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B265" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C265" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D265" t="s">
         <v>7</v>
@@ -7747,13 +7760,13 @@
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B266" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C266" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D266" t="s">
         <v>7</v>
@@ -7761,13 +7774,13 @@
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B267" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C267" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D267" t="s">
         <v>7</v>
@@ -7775,13 +7788,13 @@
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B268" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C268" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D268" t="s">
         <v>7</v>
@@ -7789,13 +7802,13 @@
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B269" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C269" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D269" t="s">
         <v>7</v>
@@ -7803,13 +7816,13 @@
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B270" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C270" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D270" t="s">
         <v>7</v>
@@ -7817,13 +7830,13 @@
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B271" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C271" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D271" t="s">
         <v>7</v>
@@ -7831,13 +7844,13 @@
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B272" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C272" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D272" t="s">
         <v>7</v>
@@ -7845,13 +7858,13 @@
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B273" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C273" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D273" t="s">
         <v>7</v>
@@ -7859,13 +7872,13 @@
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B274" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C274" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D274" t="s">
         <v>7</v>
@@ -7873,13 +7886,13 @@
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B275" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C275" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D275" t="s">
         <v>7</v>
@@ -7887,13 +7900,13 @@
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B276" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C276" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D276" t="s">
         <v>7</v>
@@ -7901,13 +7914,13 @@
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B277" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C277" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D277" t="s">
         <v>7</v>
@@ -7915,13 +7928,13 @@
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B278" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C278" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D278" t="s">
         <v>7</v>
@@ -7929,13 +7942,13 @@
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B279" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C279" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D279" t="s">
         <v>7</v>
@@ -7943,13 +7956,13 @@
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B280" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C280" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D280" t="s">
         <v>7</v>
@@ -7957,13 +7970,13 @@
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B281" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C281" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D281" t="s">
         <v>7</v>
@@ -7971,13 +7984,13 @@
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B282" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C282" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D282" t="s">
         <v>7</v>
@@ -7985,13 +7998,13 @@
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B283" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C283" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D283" t="s">
         <v>7</v>
@@ -7999,13 +8012,13 @@
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B284" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C284" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D284" t="s">
         <v>7</v>
@@ -8013,13 +8026,13 @@
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B285" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C285" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D285" t="s">
         <v>7</v>
@@ -8027,13 +8040,13 @@
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B286" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C286" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D286" t="s">
         <v>7</v>
@@ -8041,13 +8054,13 @@
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B287" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C287" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D287" t="s">
         <v>7</v>
@@ -8055,13 +8068,13 @@
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B288" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C288" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D288" t="s">
         <v>7</v>
@@ -8069,13 +8082,13 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B289" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C289" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D289" t="s">
         <v>7</v>
@@ -8083,9 +8096,6 @@
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>863</v>
-      </c>
-      <c r="B290" t="s">
         <v>864</v>
       </c>
       <c r="C290" t="s">
@@ -8440,8 +8450,11 @@
       <c r="A322" t="s">
         <v>928</v>
       </c>
+      <c r="B322" t="s">
+        <v>929</v>
+      </c>
       <c r="C322" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D322" t="s">
         <v>7</v>
@@ -8449,13 +8462,13 @@
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B323" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C323" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="D323" t="s">
         <v>7</v>
@@ -8463,13 +8476,13 @@
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B324" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="C324" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="D324" t="s">
         <v>7</v>
@@ -8477,13 +8490,13 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B325" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C325" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="D325" t="s">
         <v>7</v>
@@ -8491,13 +8504,13 @@
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B326" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C326" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="D326" t="s">
         <v>7</v>
@@ -8505,13 +8518,13 @@
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B327" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C327" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="D327" t="s">
         <v>7</v>
@@ -8519,13 +8532,13 @@
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B328" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="C328" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="D328" t="s">
         <v>7</v>
@@ -8533,13 +8546,13 @@
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B329" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C329" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="D329" t="s">
         <v>7</v>
@@ -8547,13 +8560,13 @@
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B330" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C330" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="D330" t="s">
         <v>7</v>
@@ -8561,13 +8574,13 @@
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B331" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C331" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="D331" t="s">
         <v>7</v>
@@ -8575,9 +8588,6 @@
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>957</v>
-      </c>
-      <c r="B332" t="s">
         <v>958</v>
       </c>
       <c r="C332" t="s">
@@ -8655,10 +8665,10 @@
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>972</v>
+        <v>878</v>
       </c>
       <c r="C339" t="s">
-        <v>973</v>
+        <v>879</v>
       </c>
       <c r="D339" t="s">
         <v>7</v>
@@ -8666,10 +8676,10 @@
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>880</v>
+        <v>972</v>
       </c>
       <c r="C340" t="s">
-        <v>881</v>
+        <v>973</v>
       </c>
       <c r="D340" t="s">
         <v>7</v>
@@ -8677,10 +8687,10 @@
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>974</v>
+        <v>880</v>
       </c>
       <c r="C341" t="s">
-        <v>975</v>
+        <v>881</v>
       </c>
       <c r="D341" t="s">
         <v>7</v>
@@ -8699,10 +8709,13 @@
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>884</v>
+        <v>974</v>
+      </c>
+      <c r="B343" t="s">
+        <v>975</v>
       </c>
       <c r="C343" t="s">
-        <v>885</v>
+        <v>976</v>
       </c>
       <c r="D343" t="s">
         <v>7</v>
@@ -8710,13 +8723,13 @@
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B344" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="C344" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="D344" t="s">
         <v>7</v>
@@ -8724,13 +8737,13 @@
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B345" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C345" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="D345" t="s">
         <v>7</v>
@@ -8738,13 +8751,13 @@
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B346" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C346" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="D346" t="s">
         <v>7</v>
@@ -8752,13 +8765,13 @@
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B347" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C347" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="D347" t="s">
         <v>7</v>
@@ -8766,13 +8779,13 @@
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B348" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C348" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="D348" t="s">
         <v>7</v>
@@ -8780,13 +8793,13 @@
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B349" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C349" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D349" t="s">
         <v>7</v>
@@ -8794,13 +8807,13 @@
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B350" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C350" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="D350" t="s">
         <v>7</v>
@@ -8808,13 +8821,13 @@
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B351" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C351" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="D351" t="s">
         <v>7</v>
@@ -8822,13 +8835,13 @@
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B352" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C352" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D352" t="s">
         <v>7</v>
@@ -8836,13 +8849,13 @@
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B353" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C353" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="D353" t="s">
         <v>7</v>
@@ -8850,13 +8863,13 @@
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B354" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C354" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="D354" t="s">
         <v>7</v>
@@ -8864,13 +8877,13 @@
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B355" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C355" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="D355" t="s">
         <v>7</v>
@@ -8878,13 +8891,13 @@
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B356" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C356" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D356" t="s">
         <v>7</v>
@@ -8892,13 +8905,13 @@
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B357" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="C357" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="D357" t="s">
         <v>7</v>
@@ -8906,13 +8919,13 @@
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B358" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C358" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D358" t="s">
         <v>7</v>
@@ -8920,13 +8933,13 @@
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B359" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="C359" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="D359" t="s">
         <v>7</v>
@@ -8934,13 +8947,13 @@
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B360" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="C360" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="D360" t="s">
         <v>7</v>
@@ -8948,13 +8961,13 @@
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B361" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C361" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D361" t="s">
         <v>7</v>
@@ -8962,13 +8975,13 @@
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B362" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="C362" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="D362" t="s">
         <v>7</v>
@@ -8976,13 +8989,13 @@
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B363" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C363" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="D363" t="s">
         <v>7</v>
@@ -8990,13 +9003,13 @@
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B364" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="C364" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="D364" t="s">
         <v>7</v>
@@ -9004,13 +9017,13 @@
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B365" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="C365" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D365" t="s">
         <v>7</v>
@@ -9018,13 +9031,13 @@
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B366" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="C366" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="D366" t="s">
         <v>7</v>
@@ -9032,13 +9045,13 @@
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B367" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C367" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="D367" t="s">
         <v>7</v>
@@ -9046,13 +9059,13 @@
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B368" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="C368" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="D368" t="s">
         <v>7</v>
@@ -9060,13 +9073,13 @@
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B369" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="C369" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="D369" t="s">
         <v>7</v>
@@ -9074,13 +9087,13 @@
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B370" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="C370" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="D370" t="s">
         <v>7</v>
@@ -9088,13 +9101,13 @@
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B371" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C371" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="D371" t="s">
         <v>7</v>
@@ -9102,13 +9115,13 @@
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B372" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="C372" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="D372" t="s">
         <v>7</v>
@@ -9116,13 +9129,13 @@
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B373" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="C373" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="D373" t="s">
         <v>7</v>
@@ -9130,13 +9143,13 @@
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B374" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C374" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="D374" t="s">
         <v>7</v>
@@ -9144,13 +9157,13 @@
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B375" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="C375" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="D375" t="s">
         <v>7</v>
@@ -9158,13 +9171,13 @@
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B376" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="C376" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="D376" t="s">
         <v>7</v>
@@ -9172,13 +9185,13 @@
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B377" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C377" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="D377" t="s">
         <v>7</v>
@@ -9186,13 +9199,13 @@
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B378" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C378" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="D378" t="s">
         <v>7</v>
@@ -9200,13 +9213,13 @@
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B379" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="C379" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="D379" t="s">
         <v>7</v>
@@ -9214,13 +9227,13 @@
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B380" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="C380" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="D380" t="s">
         <v>7</v>
@@ -9228,13 +9241,13 @@
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B381" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="C381" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="D381" t="s">
         <v>7</v>
@@ -9242,13 +9255,13 @@
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B382" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="C382" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="D382" t="s">
         <v>7</v>
@@ -9256,13 +9269,13 @@
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B383" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C383" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="D383" t="s">
         <v>7</v>
@@ -9270,13 +9283,13 @@
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B384" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="C384" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="D384" t="s">
         <v>7</v>
@@ -9284,13 +9297,13 @@
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B385" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="C385" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="D385" t="s">
         <v>7</v>
@@ -9298,13 +9311,13 @@
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B386" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="C386" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="D386" t="s">
         <v>7</v>
@@ -9312,13 +9325,13 @@
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B387" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="C387" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="D387" t="s">
         <v>7</v>
@@ -9326,13 +9339,13 @@
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B388" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="C388" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="D388" t="s">
         <v>7</v>
@@ -9340,13 +9353,13 @@
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B389" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C389" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D389" t="s">
         <v>7</v>
@@ -9354,13 +9367,13 @@
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B390" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="C390" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D390" t="s">
         <v>7</v>
@@ -9368,13 +9381,13 @@
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B391" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="C391" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D391" t="s">
         <v>7</v>
@@ -9382,13 +9395,13 @@
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B392" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="C392" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D392" t="s">
         <v>7</v>
@@ -9396,13 +9409,13 @@
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B393" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C393" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D393" t="s">
         <v>7</v>
@@ -9410,13 +9423,13 @@
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B394" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="C394" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="D394" t="s">
         <v>7</v>
@@ -9424,13 +9437,13 @@
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B395" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="C395" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="D395" t="s">
         <v>7</v>
@@ -9438,13 +9451,13 @@
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B396" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="C396" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="D396" t="s">
         <v>7</v>
@@ -9452,13 +9465,13 @@
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B397" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="C397" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="D397" t="s">
         <v>7</v>
@@ -9466,13 +9479,13 @@
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B398" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C398" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D398" t="s">
         <v>7</v>
@@ -9480,13 +9493,13 @@
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B399" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="C399" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="D399" t="s">
         <v>7</v>
@@ -9494,13 +9507,13 @@
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B400" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="C400" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="D400" t="s">
         <v>7</v>
@@ -9508,13 +9521,13 @@
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B401" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="C401" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="D401" t="s">
         <v>7</v>
@@ -9522,13 +9535,13 @@
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B402" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="C402" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="D402" t="s">
         <v>7</v>
@@ -9536,13 +9549,13 @@
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B403" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="C403" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="D403" t="s">
         <v>7</v>
@@ -9550,13 +9563,13 @@
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B404" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="C404" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="D404" t="s">
         <v>7</v>
@@ -9564,13 +9577,13 @@
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>236</v>
+        <v>1159</v>
       </c>
       <c r="B405" t="s">
-        <v>237</v>
+        <v>1160</v>
       </c>
       <c r="C405" t="s">
-        <v>238</v>
+        <v>1161</v>
       </c>
       <c r="D405" t="s">
         <v>7</v>
@@ -9578,13 +9591,13 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
+        <v>237</v>
+      </c>
+      <c r="B406" t="s">
+        <v>238</v>
+      </c>
+      <c r="C406" t="s">
         <v>239</v>
-      </c>
-      <c r="B406" t="s">
-        <v>240</v>
-      </c>
-      <c r="C406" t="s">
-        <v>241</v>
       </c>
       <c r="D406" t="s">
         <v>7</v>
@@ -9592,13 +9605,13 @@
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>1158</v>
+        <v>240</v>
       </c>
       <c r="B407" t="s">
-        <v>1159</v>
+        <v>241</v>
       </c>
       <c r="C407" t="s">
-        <v>1160</v>
+        <v>242</v>
       </c>
       <c r="D407" t="s">
         <v>7</v>
@@ -9606,13 +9619,13 @@
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B408" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="C408" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D408" t="s">
         <v>7</v>
@@ -9620,13 +9633,13 @@
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B409" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="C409" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="D409" t="s">
         <v>7</v>
@@ -9634,13 +9647,13 @@
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B410" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="C410" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="D410" t="s">
         <v>7</v>
@@ -9648,13 +9661,13 @@
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B411" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C411" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="D411" t="s">
         <v>7</v>
@@ -9662,13 +9675,13 @@
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B412" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="C412" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="D412" t="s">
         <v>7</v>
@@ -9676,13 +9689,13 @@
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B413" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="C413" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="D413" t="s">
         <v>7</v>
@@ -9690,13 +9703,13 @@
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B414" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="C414" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="D414" t="s">
         <v>7</v>
@@ -9704,13 +9717,13 @@
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>242</v>
+        <v>1183</v>
       </c>
       <c r="B415" t="s">
-        <v>243</v>
+        <v>1184</v>
       </c>
       <c r="C415" t="s">
-        <v>244</v>
+        <v>1185</v>
       </c>
       <c r="D415" t="s">
         <v>7</v>
@@ -9718,13 +9731,13 @@
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
+        <v>243</v>
+      </c>
+      <c r="B416" t="s">
+        <v>244</v>
+      </c>
+      <c r="C416" t="s">
         <v>245</v>
-      </c>
-      <c r="B416" t="s">
-        <v>246</v>
-      </c>
-      <c r="C416" t="s">
-        <v>247</v>
       </c>
       <c r="D416" t="s">
         <v>7</v>
@@ -9732,13 +9745,13 @@
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
+        <v>246</v>
+      </c>
+      <c r="B417" t="s">
+        <v>247</v>
+      </c>
+      <c r="C417" t="s">
         <v>248</v>
-      </c>
-      <c r="B417" t="s">
-        <v>249</v>
-      </c>
-      <c r="C417" t="s">
-        <v>250</v>
       </c>
       <c r="D417" t="s">
         <v>7</v>
@@ -9746,13 +9759,13 @@
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
+        <v>249</v>
+      </c>
+      <c r="B418" t="s">
+        <v>250</v>
+      </c>
+      <c r="C418" t="s">
         <v>251</v>
-      </c>
-      <c r="B418" t="s">
-        <v>252</v>
-      </c>
-      <c r="C418" t="s">
-        <v>253</v>
       </c>
       <c r="D418" t="s">
         <v>7</v>
@@ -9760,13 +9773,13 @@
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
+        <v>252</v>
+      </c>
+      <c r="B419" t="s">
+        <v>253</v>
+      </c>
+      <c r="C419" t="s">
         <v>254</v>
-      </c>
-      <c r="B419" t="s">
-        <v>255</v>
-      </c>
-      <c r="C419" t="s">
-        <v>256</v>
       </c>
       <c r="D419" t="s">
         <v>7</v>
@@ -9774,13 +9787,13 @@
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
+        <v>255</v>
+      </c>
+      <c r="B420" t="s">
+        <v>256</v>
+      </c>
+      <c r="C420" t="s">
         <v>257</v>
-      </c>
-      <c r="B420" t="s">
-        <v>258</v>
-      </c>
-      <c r="C420" t="s">
-        <v>259</v>
       </c>
       <c r="D420" t="s">
         <v>7</v>
@@ -9788,13 +9801,13 @@
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
+        <v>258</v>
+      </c>
+      <c r="B421" t="s">
+        <v>259</v>
+      </c>
+      <c r="C421" t="s">
         <v>260</v>
-      </c>
-      <c r="B421" t="s">
-        <v>261</v>
-      </c>
-      <c r="C421" t="s">
-        <v>262</v>
       </c>
       <c r="D421" t="s">
         <v>7</v>
@@ -9802,13 +9815,13 @@
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
+        <v>261</v>
+      </c>
+      <c r="B422" t="s">
+        <v>262</v>
+      </c>
+      <c r="C422" t="s">
         <v>263</v>
-      </c>
-      <c r="B422" t="s">
-        <v>264</v>
-      </c>
-      <c r="C422" t="s">
-        <v>265</v>
       </c>
       <c r="D422" t="s">
         <v>7</v>
@@ -9816,13 +9829,13 @@
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
+        <v>264</v>
+      </c>
+      <c r="B423" t="s">
+        <v>265</v>
+      </c>
+      <c r="C423" t="s">
         <v>266</v>
-      </c>
-      <c r="B423" t="s">
-        <v>267</v>
-      </c>
-      <c r="C423" t="s">
-        <v>268</v>
       </c>
       <c r="D423" t="s">
         <v>7</v>
@@ -9830,13 +9843,13 @@
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
+        <v>267</v>
+      </c>
+      <c r="B424" t="s">
+        <v>268</v>
+      </c>
+      <c r="C424" t="s">
         <v>269</v>
-      </c>
-      <c r="B424" t="s">
-        <v>270</v>
-      </c>
-      <c r="C424" t="s">
-        <v>271</v>
       </c>
       <c r="D424" t="s">
         <v>7</v>
@@ -9844,13 +9857,13 @@
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
+        <v>270</v>
+      </c>
+      <c r="B425" t="s">
+        <v>271</v>
+      </c>
+      <c r="C425" t="s">
         <v>272</v>
-      </c>
-      <c r="B425" t="s">
-        <v>273</v>
-      </c>
-      <c r="C425" t="s">
-        <v>274</v>
       </c>
       <c r="D425" t="s">
         <v>7</v>
@@ -9858,13 +9871,13 @@
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
+        <v>273</v>
+      </c>
+      <c r="B426" t="s">
+        <v>274</v>
+      </c>
+      <c r="C426" t="s">
         <v>275</v>
-      </c>
-      <c r="B426" t="s">
-        <v>276</v>
-      </c>
-      <c r="C426" t="s">
-        <v>277</v>
       </c>
       <c r="D426" t="s">
         <v>7</v>
@@ -9872,13 +9885,13 @@
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
+        <v>276</v>
+      </c>
+      <c r="B427" t="s">
+        <v>277</v>
+      </c>
+      <c r="C427" t="s">
         <v>278</v>
-      </c>
-      <c r="B427" t="s">
-        <v>279</v>
-      </c>
-      <c r="C427" t="s">
-        <v>280</v>
       </c>
       <c r="D427" t="s">
         <v>7</v>
@@ -9886,13 +9899,13 @@
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
+        <v>279</v>
+      </c>
+      <c r="B428" t="s">
+        <v>280</v>
+      </c>
+      <c r="C428" t="s">
         <v>281</v>
-      </c>
-      <c r="B428" t="s">
-        <v>282</v>
-      </c>
-      <c r="C428" t="s">
-        <v>283</v>
       </c>
       <c r="D428" t="s">
         <v>7</v>
@@ -9900,13 +9913,13 @@
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
+        <v>282</v>
+      </c>
+      <c r="B429" t="s">
+        <v>283</v>
+      </c>
+      <c r="C429" t="s">
         <v>284</v>
-      </c>
-      <c r="B429" t="s">
-        <v>285</v>
-      </c>
-      <c r="C429" t="s">
-        <v>286</v>
       </c>
       <c r="D429" t="s">
         <v>7</v>
@@ -9914,15 +9927,29 @@
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
+        <v>285</v>
+      </c>
+      <c r="B430" t="s">
+        <v>286</v>
+      </c>
+      <c r="C430" t="s">
         <v>287</v>
       </c>
-      <c r="B430" t="s">
+      <c r="D430" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
         <v>288</v>
       </c>
-      <c r="C430" t="s">
+      <c r="B431" t="s">
         <v>289</v>
       </c>
-      <c r="D430" t="s">
+      <c r="C431" t="s">
+        <v>290</v>
+      </c>
+      <c r="D431" t="s">
         <v>7</v>
       </c>
     </row>

--- a/news_today.xlsx
+++ b/news_today.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1681" uniqueCount="1186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1685" uniqueCount="1189">
   <si>
     <t>Title</t>
   </si>
@@ -154,13 +154,13 @@
     <t>https://www.bbc.com/news/articles/c4g2d4l1x15o?at_medium=RSS&amp;at_campaign=rss</t>
   </si>
   <si>
-    <t>'I would sell a lung for a Hannah Montana tour': Fans react to 20th anniversary special announcement</t>
-  </si>
-  <si>
-    <t>Fans are gearing up for the "Hannahversary" - a special to mark the show's 20th anniversary.</t>
-  </si>
-  <si>
-    <t>https://www.bbc.com/news/articles/c0k1xjm7463o?at_medium=RSS&amp;at_campaign=rss</t>
+    <t>You're never too old, says dancer, 71, cast in Taylor Swift video</t>
+  </si>
+  <si>
+    <t>Denise Sides  was selected from hundreds of applicants to take part in the Opalite video.</t>
+  </si>
+  <si>
+    <t>https://www.bbc.com/news/articles/cly23mrv68ro?at_medium=RSS&amp;at_campaign=rss</t>
   </si>
   <si>
     <t>'Just push us into the sea': The frustration of a coastal community failed by political promises</t>
@@ -699,11 +699,11 @@
     <t>http://www.techmeme.com/260218/p32#a260218p32</t>
   </si>
   <si>
-    <t>Google unveils the $499 Pixel 10A, with a Tensor G4 and 8GB of RAM, like the Pixel 9A, an 11% brighter screen, and 128GB or 256GB storage, shipping from March 4 (Todd Haselton/The Verge)</t>
+    <t>Google unveils the $499 Pixel 10a, with a Tensor G4 and 8GB of RAM, like the Pixel 9a, an 11% brighter screen, and 128GB or 256GB storage, shipping from March 4 (Todd Haselton/The Verge)</t>
   </si>
   <si>
     <t xml:space="preserve">Todd Haselton / The Verge:
-Google unveils the $499 Pixel 10A, with a Tensor G4 and 8GB of RAM, like the Pixel 9A, an 11% brighter screen, and 128GB or 256GB storage, shipping from March 4  —  Google's midrange Pixels have been our top pick for budget Android phones for a while.  They offer good cameras and most of what you need at a budget-friendly price.</t>
+Google unveils the $499 Pixel 10a, with a Tensor G4 and 8GB of RAM, like the Pixel 9a, an 11% brighter screen, and 128GB or 256GB storage, shipping from March 4  —  Google's midrange Pixels have been our top pick for budget Android phones for a while.  They offer good cameras and most of what you need at a budget-friendly price.</t>
   </si>
   <si>
     <t>http://www.techmeme.com/260218/p31#a260218p31</t>
@@ -1700,6 +1700,267 @@
     <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQM3ZROU82Ykp2amNmUUR4LUxHUE9lMGc3Yk5qSG80aDFaeFgwZGVodWN4SWtXc295am42aHlyMTVmSjNRWmEtd1FrOHFmYmtkV3pfUE1fNkNhbktlTllfOHY4RnM5Q1pMV2l0Z0NhU1lJbFFtNWkwN181a0x2M281VWpvZmMtX3lzR0x3aUcydTBDUS1DcWRjSXpMbHh2XzVPT2JLWFVHUENjUFJrcU80?oc=5</t>
   </si>
   <si>
+    <t>Avalara Recognized on G2's 2026 Best Software Awards for Accounting and Finance Products - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Avalara Recognized on G2's 2026 Best Software Awards for Accounting and Finance Products  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPUE0yR3I5bkMzZDVvZlJIVk1ZSTBPa2YtRWswcnBPMXJrRElHRHc4VUk5b3ZWclZUcWNhcTdyaWVYcHhIUXdMWGJEZUhETFRTQUYwSjBhS1lkLUY5TGg5Y3RNU3RZWUNpRVJDX3RTdFlXZEN0MDZvNl83MGdYR3E0TVE0U0k?oc=5</t>
+  </si>
+  <si>
+    <t>Bank of America hikes stake in sinking crypto stock by 1,668% - Yahoo Finance Singapore</t>
+  </si>
+  <si>
+    <t>Bank of America hikes stake in sinking crypto stock by 1,668%  Yahoo Finance Singapore</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQSXJ5UEpsTjZuY2Fsa2c5M29OeTAzSlhScDZ0QnNxT3Rsd2w4ZThSZUNIaVhDdDFQSl81UVk1MmhLQzA0VTdYM0cyUkdXUWlTRlE1RVRYREcxNkJTNWZPOURoM2R0c1BQNmtPVGVzZFZGbFpXNmNlcmYzSGFqUVhMZUcwbFJWSFVi?oc=5</t>
+  </si>
+  <si>
+    <t>Billionaires’ Low Taxes Are Becoming a Problem for the Economy - The Wall Street Journal</t>
+  </si>
+  <si>
+    <t>Billionaires’ Low Taxes Are Becoming a Problem for the Economy  The Wall Street Journal</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMipANBVV95cUxPWkpTWUtnZWZzX3ZMMXFXdUpBemRacTZHaWl1bzk1d3ViRlpna0xpZHVqWktmcHdjQ3BKcVAzZThDdjdTM2xzdWxrRmZqQ1ljd0xyUXJSUkdyMjZ1SzlXMzVWem9KaXlyWlNpdHlrRVFJeXpaRFB5VVJoQUIwc3p6VXgwYlpFMGpGUVBlOE53TjBmVTkxX0dlM3N1WUw1eUw0dExCU3piS1pDUlBtTHZ3bHVmVkhZNXVYTjBpSm03TnRfYzVBLXR4dlp5YXNONmlQTldnWjVIbjlaMXpaa3RqRjl2WS1SQmVZRzFfWW5ucjdxUElYUVZXVE1rZmdvakRkVlZEcUlOSjY0TFlXSXR3TE9qS0J1cjZWS1hhM0hoMFBJLWhvNGF3NDhoZ2pDU1ZJVG4zNXl3clJabjljNGc1VWZBSVhqaGw5N1F2NmNEczlfbDM2UTBrVzM0ckIzV0ExT05UMXE0UkJIMHI3UkFPSW5sRDBaaF8yNGlVNHV1c1BPVEkxTDdsNjFUSTFVaXIxTjd4c1dSRUJZTjdaZnBKdG1nRi0?oc=5</t>
+  </si>
+  <si>
+    <t>Apollo-Backed Fund Lends Wayflyer $250 Million to Finance SMEs - Bloomberg.com</t>
+  </si>
+  <si>
+    <t>Apollo-Backed Fund Lends Wayflyer $250 Million to Finance SMEs  Bloomberg.com</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPQ0FVYnZGaXlNek51bTVtd25PaWJqOFZZWmJqVF9qNUtTRjJIUEhRWTJtNG81YjVUUmZJMHpzWjJUXy1KQWJXUTBUelNxNV9tZGd5ZUtHa21CT2dGWGwzZTNwRWl4em5COWpNdjh4ZXpCWnVTNXpoME04S2R3cjdkSFluSTMzSmxJQ09VZWRsQjFvdXNnRUM0QTdCMTAzNG41YVR1Y2pjd0s5S1FCdHlXUllB?oc=5</t>
+  </si>
+  <si>
+    <t>Economic Sector Performance Dashboards - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Economic Sector Performance Dashboards  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiSkFVX3lxTE1aZHRnWXJQdlUwdmU4ZExFUzhEVXA5TXBHSFBsNS15TzJCSWtfMGRtU09HNENQMl9mTzlBenQyVmtTOFBKaFJDQ2ZB?oc=5</t>
+  </si>
+  <si>
+    <t>Coffee &amp; Donuts with the Mayor and Finance February 28 - City of West Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>Coffee &amp; Donuts with the Mayor and Finance February 28  City of West Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNR2VZNUNzbDNRYWNJMEVURm53elA3TU85SVdudUIzQ0Z5OTROdG44dXB5WlpqbkdPNHNSb044eHFvODZzQXJFTGJpM3NaajkyTTNid3ZVNjg0WldTaHA2eW5vRkdaWVBRUEttQnNqaGE4STFEZF9LQVhlRHdmTlc3ZVRscXRkMExyREE?oc=5</t>
+  </si>
+  <si>
+    <t>Governor Moore Testifies Before Senate Finance Committee in Support of Legislative Agenda to Make Maryland More Affordable and More Competitive - Office of Governor Wes Moore (.gov)</t>
+  </si>
+  <si>
+    <t>Governor Moore Testifies Before Senate Finance Committee in Support of Legislative Agenda to Make Maryland More Affordable and More Competitive  Office of Governor Wes Moore (.gov)</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxQM1pHd3I0RG5XejdpVWJEcUxramNPeU1WOUxlU0MyczlaS0pLMUw2Tm1nSVQzcGNPRWpQT1I3cXVLcXBUaUpYcGxGSkg3OHp1U3Y2eDZhV2RtRV9FR3J6QUV6Y2hyblRGeVNkdU1HT0ZEOFc4Q1RhREJCN29JVlptRzk2TWZoaHhncjhwekdHb0xTVTFMMjBDUnl2QmtqOXBpUmgyaUlTaE1XeW5WOVJDaWR0X3NPaXZieDd3MjREM3NCYU0wSzBWVGptbDhUWGIwcVFDUHdvTmhRdnBQd21HazlmTDRBUGx3VDdrZE02b01PZG1JeFpLMlJPTTd3Y21DSFNIZ2Zn?oc=5</t>
+  </si>
+  <si>
+    <t>Avalara Recognized on G2's 2026 Best Software Awards for Accounting and Finance Products - PR Newswire</t>
+  </si>
+  <si>
+    <t>Avalara Recognized on G2's 2026 Best Software Awards for Accounting and Finance Products  PR Newswire</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOOExlVW1PTkhpeVRVeVJqS1A3WVdydlhPNGx5cWhmZS1TQ3pBM3hnZGZwSFhkVWtnRnlRNm1tcnlySzVnYk5uZVRrbVNSV3BMQXEwTkhJTTZweVlZVWpxcndnZ0pxcGdhOTBJQ25MY1lKcm9WdnZWaldvMVR6cnhCNEl1aVBaVDRrTGgwMmVHMl9jQVIwc3pZeHVVTGVDb2hpZTAwa3M0MFcwRWhuaW81R0JIY2JEanRpc0c0aFB2dGs0OTZQSDhIVUhHSjByeWFuMEZ0eHBEbzVIX1k?oc=5</t>
+  </si>
+  <si>
+    <t>Program - Milken Institute</t>
+  </si>
+  <si>
+    <t>Program  Milken Institute</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE9rdkpHVDFFMmpRcTFFc0FlTnJ2bElINVdKNm1OeDVVWXVVMl8yVnpETHpKalVCc2o2T3NtSVhVWlBodzBVdFZycTQ5MksxbWFIbXh2eC1wbWNOMUt6MkxQcHdiTFdxZFBhQ2JQUFNKUQ?oc=5</t>
+  </si>
+  <si>
+    <t>Konica Minolta Wins the Bronze Prize in the Seventh ESG Finance Awards Japan of the Ministry of the Environment - Konica Minolta</t>
+  </si>
+  <si>
+    <t>Konica Minolta Wins the Bronze Prize in the Seventh ESG Finance Awards Japan of the Ministry of the Environment  Konica Minolta</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1XVnlJT3NZTlNITVVJU2JrUV9yejAtMTIxa05DXzY4ME0zWVBoRTBvOUduLWp1OTR4N21EbkdOa1VCQjBqYURmUUpVQ0p6VzZSX1BfMENPRTBScFpFSGxsRGloZzlPY1pVak9qNWNiMmVfLWNVdzhXVQ?oc=5</t>
+  </si>
+  <si>
+    <t>Women in Securities Finance appoints Hill Sands - Securities Finance Times</t>
+  </si>
+  <si>
+    <t>Women in Securities Finance appoints Hill Sands  Securities Finance Times</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQMjJkLTZVcm84eTNLM3RfeFl2d21odEx4ZlJSNUtUSkpPVzVockVkRmtOY00xcGg4VFltTXNoUFJRVkVFX0habzNBMlZNN3RmODJLc0R6djdOOWkteGtPb3FfazcwbUQ2MDlUTjNTaEJuM0IycDdKSUJHak5LbFNxeEFDMGVRWXJYTTFsQlRoRWcwWlQ5X1FQUnVEend5R1B2ejUw?oc=5</t>
+  </si>
+  <si>
+    <t>The Real Bottleneck in Finance Isn’t Payments. It’s Settlement. - FinTech Weekly</t>
+  </si>
+  <si>
+    <t>The Real Bottleneck in Finance Isn’t Payments. It’s Settlement.  FinTech Weekly</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOR3RLRlRYOFVvWE9LX1c1UzRubldLcjg1eXpSbXE3YlNvb2U3ZVdQZWZFVnBYOHhWYkNSN0JKZ2t0MFdSRGVLUmRtYmFxbUEzM0hBNXFmYlJJbEZZNUMwbkpFazNVNUdTTklFVmg4N3NGX2JUWDFpRV9ScXRRWG9pa1A1Q1pxc093U2c?oc=5</t>
+  </si>
+  <si>
+    <t>New Climate Finance Initiative Supports Climate Adaptation Efforts in Glacier-Dependent Regions - Columbia University in the City of New York</t>
+  </si>
+  <si>
+    <t>New Climate Finance Initiative Supports Climate Adaptation Efforts in Glacier-Dependent Regions  Columbia University in the City of New York</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOMTN2TUpQT0dqaGR5VU9SSng0YzJibE1DZGdJOUVVWm4xM0RDVkUteVBpS0lZb3k5VDhxVEsyekNWNXUzR2YtN3pOV2hNRDQ4WVI5VHpyaDNnVXNmc21CNlh4SDdJd0V3V3dyWU9hc3VObGotYmZvQzNrWVRRTUFCSUVTU2Zial9JRWU0c1ZNZWw1eFFCdmxFZ2JxdDJkLWNxa0NEM2lFUlFtdkNHSjZQeWUwNl81TEJCdkY4QnVwb2JIRmE4ZGlGUVNaQ3FFN1BIb2k2RG5FbU8?oc=5</t>
+  </si>
+  <si>
+    <t>AI adoption already hitting Irish graduate jobs, finance department says - Reuters</t>
+  </si>
+  <si>
+    <t>AI adoption already hitting Irish graduate jobs, finance department says  Reuters</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNY0ZlYUU3ZWpFUFF0WEk1eXRkc1ZwbUduSUpVdjJoeXdLeWhJVnMzV0taTk11b0lpeklmMzZBM29YVmd6V3dqWlhENkJnZ0dRRjdNSWd3TVV5dURwbUM3QjFzem1wSHd2Y0Y2aU5GWFcyS2tSR3RsTmVfQ1ZzWWFvbU5Ld05YYlBiTVNmMm5rVGxHVEVDcjJzUVM4RjZxQ1gtbWp5clFFalNZbmtMWThuZzFDczlsSjA?oc=5</t>
+  </si>
+  <si>
+    <t>Symposium on International Investment Law &amp; Contemporary Crises: Energy Finance Market Design &amp; IIA Claims - Opinio Juris</t>
+  </si>
+  <si>
+    <t>Symposium on International Investment Law &amp; Contemporary Crises: Energy Finance Market Design &amp; IIA Claims  Opinio Juris</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNdE85WEhsdkw2YTBwVW14aklibzR3X0pLUVVkZEVlM2xjNEFzRXBzMkVINmQyc1VZMExFV0R1WmRCZHlac2FzQS03djdrSk9SdU1sM1ZOS2JlSGRGS0RDU3lQaktUNlBPN0VVclhWbjdJUXdkalVPM0stRXp4S3luVUJRNkVyV2NnUVpoTHhQM2VVV3F2QzBfT2VUNDNyVENwQWJyNV82TldkZE1ITnNiWGVhRGM1TlA1Z3NPcHJ4Rjg4S1pSeXFXNjc2Wlh6X21obUE?oc=5</t>
+  </si>
+  <si>
+    <t>How Credit Cards Keep America’s Small Businesses Running Strong - U.S. Chamber of Commerce</t>
+  </si>
+  <si>
+    <t>How Credit Cards Keep America’s Small Businesses Running Strong  U.S. Chamber of Commerce</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOOEZRTVRzZlF2RzVaVVZXdm55a1JWRzlHenl6OWQ4czBNa0hLbFF1dWdFMXI4RExnQVhmQWpzb2tEanNvNEU1UzQ5ZXRhaXgzY3BUazl3WFdkb1VwMGowMkl2eEhoT0x1djA1LVltOTZOWlBTOXQ5YzItUkRLcmhXd0RvRHhkZi0tZERvX19FWUpEazZwdHlhVDZZekk?oc=5</t>
+  </si>
+  <si>
+    <t>BBVA welcomes Shepherd - Securities Finance Times</t>
+  </si>
+  <si>
+    <t>BBVA welcomes Shepherd  Securities Finance Times</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxORVBDSXlvSTBQR0w4WTc1WkhzNDdGMmhuSWlpOE82Mm5uTnBNVnBUTUJSMWVuNUp4OXVGdV90M0pZelBNcXBUdmZOVWQtVlN2eWV4bFpBSG1ZcFN2eHNSS1hJam90R0dRWXRROEtsLXlRMTVWcFJtVGdSR3FpNWZkRjN4ekRlZUU4cEJvTmtUUVdwLS11T1RuN1F6UWJxcFJ5UXBZ?oc=5</t>
+  </si>
+  <si>
+    <t>Troutman Pepper Locke Weekly Consumer Financial Services Newsletter – February 18, 2026 - Consumer Financial Services Law Monitor</t>
+  </si>
+  <si>
+    <t>Troutman Pepper Locke Weekly Consumer Financial Services Newsletter – February 18, 2026  Consumer Financial Services Law Monitor</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPUExOOWVkYWxmODJERVdlUlpCOFhXdDFmTXVWdW54TnFhOWZvNUdBWERLVnd3aXR5aFNwaHk1QnVSZVREVzkybjhoemhPYTNhVkZQdFFlelJmS19vQV9ZNWxVVE9SN05mVEtaVDV0b1ZvNHRXazI0TmFLX1c1TFVkNnUxVExBbnFCVWZwLTA0NTJFS3BjRWk5TWRGa3JHRTFxa2JfSm11WC1OdEtEWHZ5Mzc0V1NXSC1mVW5HUUtjTlJ2bGpQOEIwUzlmcGF2dXNoMHFzTnVLeVM3RXBlOXc?oc=5</t>
+  </si>
+  <si>
+    <t>Earnings live: Palo Alto Networks stock sinks after company cuts full-year forecast - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Earnings live: Palo Alto Networks stock sinks after company cuts full-year forecast  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQVWE1S2hNazUwaEp3UTQ4ZWcwY1FXY2JnVG4yQ2ZQeTRVdUxKdVhFcDBDZnFzTmNNRUFIMWJPek80ZTNKS2VqWFAzTEVPXzREN1kzQnVzZkdvMG5qN1VOR2dVNFBnSzdEaGVUUmI5TGhBbGFwQUJIVno5bHc0YzdBck9SNjRBcnNwRndFTFN0dGFId01wVlU4bEhGOUNSRUN6aEIwNnByeGJnd3FiM2ZXMkQ4X0FnZ0xQeHJlRWd2UFphNFBIeDBDNlpVeWNOQQ?oc=5</t>
+  </si>
+  <si>
+    <t>Nvidia and Meta expand GPU team up with millions of additional AI chips - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Nvidia and Meta expand GPU team up with millions of additional AI chips  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNaEc1R3NCLTZRdDgwVWd6UDR5ZXB5SXd4Q0c2dlBUbVpnT1ZzRU8xMnh5bWNEa1BuS25zRHg3Qk45OW1QaVk3MlE1MEhta25icVhvYkw5UXd0MjU2U2gtVmljdFBrMzM1X1FKQzRPNG9uVllMb0lRSXFvQWx3TWFmaDAyaTNIMFhabl9maFdRek1jcVpBOEJaeFMzbUgxbF82dXRKTjVCZzRqZm9iNkUwbjNyQmZ6WkYw?oc=5</t>
+  </si>
+  <si>
+    <t>Chicago Atlantic Real Estate Finance Schedules Fourth Quarter 2025 Earnings Release and Conference Call Date - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Chicago Atlantic Real Estate Finance Schedules Fourth Quarter 2025 Earnings Release and Conference Call Date  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNazBfQm5fMm1UTGZMVF9JQm5FLXNnZHpwekp6R3lNQTk5aGYtd2J2eW9KemNpSHZWNzQtVVZ6NU92dTh6eEFSOTZ5NThjeV9yd0VXMU43djVCQTBLYUhJeks1b2xXX21HYXdVNjFOdzNwZDRrNmlRX1dFTGNyUjYtMHZPUUVaTWo5bWc?oc=5</t>
+  </si>
+  <si>
+    <t>Stock market today: Dow, S&amp;P 500, Nasdaq rise as AI worries recede, with Fed minutes ahead - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Stock market today: Dow, S&amp;P 500, Nasdaq rise as AI worries recede, with Fed minutes ahead  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQcEhkYkxjdlVSbDVfTk83VmVuZ2pVTmgzNjFsRFRjc0VqelNPX1c1RFZ4am1Ra3U5TUlVWnFNTVZkTlNTRGpzanNCcUVybTlGNHNMaXR4ajc4VVZqbW55cFp5ZWJlR3NGZmM1OFEyMmFqblBQVmNwdkdLRzRSMWdfVVpwZmYyRndHczgtOHYxWTNSQ3V1WmkzcTJod0d6X0pmY3B2d0ItTmx1OWpCenVtdzUtc09PeW1JWVgwcDQxYUJIZktZRHBGTC1idnc2cFFINVE?oc=5</t>
+  </si>
+  <si>
+    <t>Snap Finance Study Finds Majority of U.S. Households Delayed Essential Purchases in 2025 as Credit Pressures Persist Into 2026 - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Snap Finance Study Finds Majority of U.S. Households Delayed Essential Purchases in 2025 as Credit Pressures Persist Into 2026  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOTzNzdHpaNkF0TUlxNHJwdGtIRzQzdTBlNXpkUWRTbVdna1M0eE1IU1NvS1otYTAzVEFub2lvVWlKeHd6QkY3RmJ0T3NqSkVBX29Ya25DbkNydnZDRG55OGxDTksydXo4Y3JWSXNRd1U3UUY5Zm0zdlExbDVkZkxzVmxlU05Rdw?oc=5</t>
+  </si>
+  <si>
+    <t>Are Finance Stocks Lagging Barclays (BCS) This Year? - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Are Finance Stocks Lagging Barclays (BCS) This Year?  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPbkt4OTRYNGtDSjRKUTF5Y3hVZ242YzN0Nmlub0kzMl9KbnRRU00tMHdLVEl3aTY0V0Y5QWFzRDAtQ0M5WlVGV3ZxV1NzN3VpaWt2UVhVNWZVTDlScHA1bzg5TFlpN2p4Q0FGbHVhVVNuaWNzOTVQMTVoeklfR1hOT3h0R1ZlYmpQ?oc=5</t>
+  </si>
+  <si>
+    <t>Unlocking Finance for Nature-based Solutions in Indian Cities - Climate Policy Initiative</t>
+  </si>
+  <si>
+    <t>Unlocking Finance for Nature-based Solutions in Indian Cities  Climate Policy Initiative</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNbE9VZDZKVktsajJEVG0yM1ZfWEJ3Ums3RHRTM0FOZTFEZnFwa1NFSXBSbXpLMUpzNUktWGtqSzRVN052RllQUDNMY2x3TWlFSnNUS2VyNzF5X05ZWmx1MTlYSVlwOS05WDhjcmpCZTBacHc1Q29Ba2lZUkVuclMtaFJ6ejI3Z2lkMHVYdEFJREJIdXF2ZUVXT0VMMlFaLWRoeHFKY2xMS2syRTJWZDVQaVRraTQ?oc=5</t>
+  </si>
+  <si>
+    <t>West Virginia Senate Finance Committee approves appropriations bill for Hancock County Schools - News and Sentinel</t>
+  </si>
+  <si>
+    <t>West Virginia Senate Finance Committee approves appropriations bill for Hancock County Schools  News and Sentinel</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxORmNQWEtJSnc0OEQ2Yl92TldtMHJrVEdaZUdNdHNvb0pWdmpLcGdTV0xXZE5EcmJsWWFLSmxaOENUdUFqel92bTRjZ1g0TU9uLXVHTXNTY2x0VmVYV1Y4V1p4RTZKVDVNUGZHY0l3V3dWdmtuVGxMcmtOQVpralpLaDdGNXJ6OUt6dEpsMlNHQzNSOXpsclJBX1lOMXYzdkptaGlJRkRhNVdIaWowc2pFTTM5VlRFVlJsM0FCaU81TDl0by1fVVRCcUhYdThWYUdJbVRwUElna0hEVjQtM0NhYUlBcUtBUQ?oc=5</t>
+  </si>
+  <si>
+    <t>Lightrock grabs an exit opportunity from Indian small business lender Aye Finance - ImpactAlpha</t>
+  </si>
+  <si>
+    <t>Lightrock grabs an exit opportunity from Indian small business lender Aye Finance  ImpactAlpha</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPbW5lcmJoSERuOFp0MGYzaHJXS2Q4c2FTNUgyODYybUlOZ2JKUlVLcTcwYlRoNmRxbC0tejNBZXFaSHhEaTR2Q1VDT1BEREtLWjhiM2JDSFFpM2JGMUYyazI4a2ZkTm9Ja2pCRmNtcGhqTlJzcFowVlNKWmxtOHpSR1g1X1hEaXZyVXB1Y0ZlYVlkV3N3VTVTT2U3Y1ZKMHE2VkNSeHpKNWYtUQ?oc=5</t>
+  </si>
+  <si>
+    <t>OPENLANE, Inc. Reports 2025 Financial Results - PR Newswire</t>
+  </si>
+  <si>
+    <t>OPENLANE, Inc. Reports 2025 Financial Results  PR Newswire</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNZ3FFQzNzUG81QkNjTDgycHBKSUh3NURtVi1WUkR0cGFoODg3LUFyX25YYjVYNFIzU0U2cW9YT2pkcUNxTnpWb2VoUFpGTGI2N2I0Y2tmZ1hwWVlQRzhNVU1LdnBzYkx6QUpKSlRLQmJiMHFuV0NSNkhpTEZpVTIxeTRwVmUxc2c3S01fYnVWZVJDR2Z3VzlvV2MweUw0bXJk?oc=5</t>
+  </si>
+  <si>
+    <t>Financial scams are on the rise — but what’s being done about it? - The Hill</t>
+  </si>
+  <si>
+    <t>Financial scams are on the rise — but what’s being done about it?  The Hill</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQbFU0OFZxQ2tVdlpqamVrdldYbTE1N0NkOWw4RjlnQ3lDaFVIanpfTFNrbllSVWMySl9DS0FmZzlWSDRCTEloTEF2Vms5QmRPaFpJcjM0T3RTa3JtY3UtbW1tVlpHQkxYYWRlTTI4NWMwaXp2SVdYZDdZUlRYMHV4RmVXWdIBiAFBVV95cUxOZ1ZOWTllSWJKWEFaLTl4ZEk4LUx5dzl3M2tiMEhKZWhLb0dpaW16QnJ3RzRudExGS2NPeGZjYVVBbnItVGxfNE1pWUxyZG1SMmMxSEdxSVhIZndmM0FpRDdTbFFrNHluWVh6a2M5T3RRT2FsdkdJdlhJaGc1WXp1dVNFNXhlQ2hI?oc=5</t>
+  </si>
+  <si>
     <t>Is Synchrony Financial (SYF) Still Attractive After Recent Share Price Pullback? - Yahoo Finance</t>
   </si>
   <si>
@@ -1709,247 +1970,67 @@
     <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQYzJRV0I4UzFRZ2ljeTFwanMwOGZVZ1lIZ05KbUh4QUJCVEM5SDVtMUhmQXl0VDAybUZvMHJTbTVCTEZPTVBnZE5xb2ZWWnRKWXBram52aDZiMGJxeTlfb0l1SldpU2t2RUlCZEpLOEdORUxlQ3FMZWNzbS1oOE5FbUxLUWRMaV8tQkdZTUNfcw?oc=5</t>
   </si>
   <si>
-    <t>Avalara Recognized on G2's 2026 Best Software Awards for Accounting and Finance Products - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Avalara Recognized on G2's 2026 Best Software Awards for Accounting and Finance Products  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPUE0yR3I5bkMzZDVvZlJIVk1ZSTBPa2YtRWswcnBPMXJrRElHRHc4VUk5b3ZWclZUcWNhcTdyaWVYcHhIUXdMWGJEZUhETFRTQUYwSjBhS1lkLUY5TGg5Y3RNU3RZWUNpRVJDX3RTdFlXZEN0MDZvNl83MGdYR3E0TVE0U0k?oc=5</t>
-  </si>
-  <si>
-    <t>Billionaires’ Low Taxes Are Becoming a Problem for the Economy - The Wall Street Journal</t>
-  </si>
-  <si>
-    <t>Billionaires’ Low Taxes Are Becoming a Problem for the Economy  The Wall Street Journal</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMipANBVV95cUxNNjVTREItcVAtQk9uZksyTWQyUUx5a1Vwc2VWRllHM2FzODNVWGQ1RkQ5NnRaRTAtTzRFd1c0U01ReksyRmRrLXFHRUl3V3VlWHdTY0RJVW94Y1RPT25RSVFrSFdaWE5NZU9kMkhVMU44Sm1EMU5KTGNXTm1ZaDJzZldFV3hkakJSVzlaVm1UeldLOWtsZFRxNzBVV0hYOFFNVWZ6aE9uNzN1V0FiTlRLNk95OWFaVEdmekF3WUtCaHZJNmx6bFoxczJiVF9qVzJYZVZYSlh2dDdtWTJYQnR1ZTlwazU0ZVJTYjZZQTBZRFNjcDU1R09LR0stWHVVQnN4dENaMTMyY3ZPS2xSTWFZUkFSNDZiWHZGM25QVXBwaXE3SkhEM09xQ0QyZ2VqaXVoQUNydHNiNEFjQ1M3NmY5b2hCVnZWX1dYUmxhY3I2THhyekxXa1d4NnBIYlVYRXo1OElzd1hCamhXdkJTcklnemdSNm5pSi1FSVNJaS1rbHRqa3RvM0ZMTThNV01RLUdkWUNPVndOQ3JJdHNqakNDdmNKa1Y?oc=5</t>
-  </si>
-  <si>
-    <t>Apollo-Backed Fund Lends Wayflyer $250 Million to Finance SMEs - Bloomberg.com</t>
-  </si>
-  <si>
-    <t>Apollo-Backed Fund Lends Wayflyer $250 Million to Finance SMEs  Bloomberg.com</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPQ0FVYnZGaXlNek51bTVtd25PaWJqOFZZWmJqVF9qNUtTRjJIUEhRWTJtNG81YjVUUmZJMHpzWjJUXy1KQWJXUTBUelNxNV9tZGd5ZUtHa21CT2dGWGwzZTNwRWl4em5COWpNdjh4ZXpCWnVTNXpoME04S2R3cjdkSFluSTMzSmxJQ09VZWRsQjFvdXNnRUM0QTdCMTAzNG41YVR1Y2pjd0s5S1FCdHlXUllB?oc=5</t>
-  </si>
-  <si>
-    <t>Economic Sector Performance Dashboards - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Economic Sector Performance Dashboards  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiSkFVX3lxTE1aZHRnWXJQdlUwdmU4ZExFUzhEVXA5TXBHSFBsNS15TzJCSWtfMGRtU09HNENQMl9mTzlBenQyVmtTOFBKaFJDQ2ZB?oc=5</t>
-  </si>
-  <si>
-    <t>Coffee &amp; Donuts with the Mayor and Finance February 28 - City of West Chicago, Illinois</t>
-  </si>
-  <si>
-    <t>Coffee &amp; Donuts with the Mayor and Finance February 28  City of West Chicago, Illinois</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNR2VZNUNzbDNRYWNJMEVURm53elA3TU85SVdudUIzQ0Z5OTROdG44dXB5WlpqbkdPNHNSb044eHFvODZzQXJFTGJpM3NaajkyTTNid3ZVNjg0WldTaHA2eW5vRkdaWVBRUEttQnNqaGE4STFEZF9LQVhlRHdmTlc3ZVRscXRkMExyREE?oc=5</t>
-  </si>
-  <si>
-    <t>Governor Moore Testifies Before Senate Finance Committee in Support of Legislative Agenda to Make Maryland More Affordable and More Competitive - Office of Governor Wes Moore (.gov)</t>
-  </si>
-  <si>
-    <t>Governor Moore Testifies Before Senate Finance Committee in Support of Legislative Agenda to Make Maryland More Affordable and More Competitive  Office of Governor Wes Moore (.gov)</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxQM1pHd3I0RG5XejdpVWJEcUxramNPeU1WOUxlU0MyczlaS0pLMUw2Tm1nSVQzcGNPRWpQT1I3cXVLcXBUaUpYcGxGSkg3OHp1U3Y2eDZhV2RtRV9FR3J6QUV6Y2hyblRGeVNkdU1HT0ZEOFc4Q1RhREJCN29JVlptRzk2TWZoaHhncjhwekdHb0xTVTFMMjBDUnl2QmtqOXBpUmgyaUlTaE1XeW5WOVJDaWR0X3NPaXZieDd3MjREM3NCYU0wSzBWVGptbDhUWGIwcVFDUHdvTmhRdnBQd21HazlmTDRBUGx3VDdrZE02b01PZG1JeFpLMlJPTTd3Y21DSFNIZ2Zn?oc=5</t>
-  </si>
-  <si>
-    <t>Avalara Recognized on G2's 2026 Best Software Awards for Accounting and Finance Products - PR Newswire</t>
-  </si>
-  <si>
-    <t>Avalara Recognized on G2's 2026 Best Software Awards for Accounting and Finance Products  PR Newswire</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOOExlVW1PTkhpeVRVeVJqS1A3WVdydlhPNGx5cWhmZS1TQ3pBM3hnZGZwSFhkVWtnRnlRNm1tcnlySzVnYk5uZVRrbVNSV3BMQXEwTkhJTTZweVlZVWpxcndnZ0pxcGdhOTBJQ25MY1lKcm9WdnZWaldvMVR6cnhCNEl1aVBaVDRrTGgwMmVHMl9jQVIwc3pZeHVVTGVDb2hpZTAwa3M0MFcwRWhuaW81R0JIY2JEanRpc0c0aFB2dGs0OTZQSDhIVUhHSjByeWFuMEZ0eHBEbzVIX1k?oc=5</t>
-  </si>
-  <si>
-    <t>Program - Milken Institute</t>
-  </si>
-  <si>
-    <t>Program  Milken Institute</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE9rdkpHVDFFMmpRcTFFc0FlTnJ2bElINVdKNm1OeDVVWXVVMl8yVnpETHpKalVCc2o2T3NtSVhVWlBodzBVdFZycTQ5MksxbWFIbXh2eC1wbWNOMUt6MkxQcHdiTFdxZFBhQ2JQUFNKUQ?oc=5</t>
-  </si>
-  <si>
-    <t>Konica Minolta Wins the Bronze Prize in the Seventh ESG Finance Awards Japan of the Ministry of the Environment - Konica Minolta</t>
-  </si>
-  <si>
-    <t>Konica Minolta Wins the Bronze Prize in the Seventh ESG Finance Awards Japan of the Ministry of the Environment  Konica Minolta</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1XVnlJT3NZTlNITVVJU2JrUV9yejAtMTIxa05DXzY4ME0zWVBoRTBvOUduLWp1OTR4N21EbkdOa1VCQjBqYURmUUpVQ0p6VzZSX1BfMENPRTBScFpFSGxsRGloZzlPY1pVak9qNWNiMmVfLWNVdzhXVQ?oc=5</t>
-  </si>
-  <si>
-    <t>New Climate Finance Initiative Supports Climate Adaptation Efforts in Glacier-Dependent Regions - Columbia University in the City of New York</t>
-  </si>
-  <si>
-    <t>New Climate Finance Initiative Supports Climate Adaptation Efforts in Glacier-Dependent Regions  Columbia University in the City of New York</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOMTN2TUpQT0dqaGR5VU9SSng0YzJibE1DZGdJOUVVWm4xM0RDVkUteVBpS0lZb3k5VDhxVEsyekNWNXUzR2YtN3pOV2hNRDQ4WVI5VHpyaDNnVXNmc21CNlh4SDdJd0V3V3dyWU9hc3VObGotYmZvQzNrWVRRTUFCSUVTU2Zial9JRWU0c1ZNZWw1eFFCdmxFZ2JxdDJkLWNxa0NEM2lFUlFtdkNHSjZQeWUwNl81TEJCdkY4QnVwb2JIRmE4ZGlGUVNaQ3FFN1BIb2k2RG5FbU8?oc=5</t>
-  </si>
-  <si>
-    <t>Women in Securities Finance appoints Hill Sands - Securities Finance Times</t>
-  </si>
-  <si>
-    <t>Women in Securities Finance appoints Hill Sands  Securities Finance Times</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQMjJkLTZVcm84eTNLM3RfeFl2d21odEx4ZlJSNUtUSkpPVzVockVkRmtOY00xcGg4VFltTXNoUFJRVkVFX0habzNBMlZNN3RmODJLc0R6djdOOWkteGtPb3FfazcwbUQ2MDlUTjNTaEJuM0IycDdKSUJHak5LbFNxeEFDMGVRWXJYTTFsQlRoRWcwWlQ5X1FQUnVEend5R1B2ejUw?oc=5</t>
-  </si>
-  <si>
-    <t>The Real Bottleneck in Finance Isn’t Payments. It’s Settlement. - FinTech Weekly</t>
-  </si>
-  <si>
-    <t>The Real Bottleneck in Finance Isn’t Payments. It’s Settlement.  FinTech Weekly</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOR3RLRlRYOFVvWE9LX1c1UzRubldLcjg1eXpSbXE3YlNvb2U3ZVdQZWZFVnBYOHhWYkNSN0JKZ2t0MFdSRGVLUmRtYmFxbUEzM0hBNXFmYlJJbEZZNUMwbkpFazNVNUdTTklFVmg4N3NGX2JUWDFpRV9ScXRRWG9pa1A1Q1pxc093U2c?oc=5</t>
-  </si>
-  <si>
-    <t>Symposium on International Investment Law &amp; Contemporary Crises: Energy Finance Market Design &amp; IIA Claims - Opinio Juris</t>
-  </si>
-  <si>
-    <t>Symposium on International Investment Law &amp; Contemporary Crises: Energy Finance Market Design &amp; IIA Claims  Opinio Juris</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNdE85WEhsdkw2YTBwVW14aklibzR3X0pLUVVkZEVlM2xjNEFzRXBzMkVINmQyc1VZMExFV0R1WmRCZHlac2FzQS03djdrSk9SdU1sM1ZOS2JlSGRGS0RDU3lQaktUNlBPN0VVclhWbjdJUXdkalVPM0stRXp4S3luVUJRNkVyV2NnUVpoTHhQM2VVV3F2QzBfT2VUNDNyVENwQWJyNV82TldkZE1ITnNiWGVhRGM1TlA1Z3NPcHJ4Rjg4S1pSeXFXNjc2Wlh6X21obUE?oc=5</t>
-  </si>
-  <si>
-    <t>AI adoption already hitting Irish graduate jobs, finance department says - Reuters</t>
-  </si>
-  <si>
-    <t>AI adoption already hitting Irish graduate jobs, finance department says  Reuters</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNY0ZlYUU3ZWpFUFF0WEk1eXRkc1ZwbUduSUpVdjJoeXdLeWhJVnMzV0taTk11b0lpeklmMzZBM29YVmd6V3dqWlhENkJnZ0dRRjdNSWd3TVV5dURwbUM3QjFzem1wSHd2Y0Y2aU5GWFcyS2tSR3RsTmVfQ1ZzWWFvbU5Ld05YYlBiTVNmMm5rVGxHVEVDcjJzUVM4RjZxQ1gtbWp5clFFalNZbmtMWThuZzFDczlsSjA?oc=5</t>
-  </si>
-  <si>
-    <t>How Credit Cards Keep America’s Small Businesses Running Strong - U.S. Chamber of Commerce</t>
-  </si>
-  <si>
-    <t>How Credit Cards Keep America’s Small Businesses Running Strong  U.S. Chamber of Commerce</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOOEZRTVRzZlF2RzVaVVZXdm55a1JWRzlHenl6OWQ4czBNa0hLbFF1dWdFMXI4RExnQVhmQWpzb2tEanNvNEU1UzQ5ZXRhaXgzY3BUazl3WFdkb1VwMGowMkl2eEhoT0x1djA1LVltOTZOWlBTOXQ5YzItUkRLcmhXd0RvRHhkZi0tZERvX19FWUpEazZwdHlhVDZZekk?oc=5</t>
-  </si>
-  <si>
-    <t>Troutman Pepper Locke Weekly Consumer Financial Services Newsletter – February 18, 2026 - Consumer Financial Services Law Monitor</t>
-  </si>
-  <si>
-    <t>Troutman Pepper Locke Weekly Consumer Financial Services Newsletter – February 18, 2026  Consumer Financial Services Law Monitor</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPUExOOWVkYWxmODJERVdlUlpCOFhXdDFmTXVWdW54TnFhOWZvNUdBWERLVnd3aXR5aFNwaHk1QnVSZVREVzkybjhoemhPYTNhVkZQdFFlelJmS19vQV9ZNWxVVE9SN05mVEtaVDV0b1ZvNHRXazI0TmFLX1c1TFVkNnUxVExBbnFCVWZwLTA0NTJFS3BjRWk5TWRGa3JHRTFxa2JfSm11WC1OdEtEWHZ5Mzc0V1NXSC1mVW5HUUtjTlJ2bGpQOEIwUzlmcGF2dXNoMHFzTnVLeVM3RXBlOXc?oc=5</t>
-  </si>
-  <si>
-    <t>BBVA welcomes Shepherd - Securities Finance Times</t>
-  </si>
-  <si>
-    <t>BBVA welcomes Shepherd  Securities Finance Times</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxORVBDSXlvSTBQR0w4WTc1WkhzNDdGMmhuSWlpOE82Mm5uTnBNVnBUTUJSMWVuNUp4OXVGdV90M0pZelBNcXBUdmZOVWQtVlN2eWV4bFpBSG1ZcFN2eHNSS1hJam90R0dRWXRROEtsLXlRMTVWcFJtVGdSR3FpNWZkRjN4ekRlZUU4cEJvTmtUUVdwLS11T1RuN1F6UWJxcFJ5UXBZ?oc=5</t>
-  </si>
-  <si>
-    <t>Earnings live: Palo Alto Networks stock sinks after company cuts full-year forecast - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Earnings live: Palo Alto Networks stock sinks after company cuts full-year forecast  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQVWE1S2hNazUwaEp3UTQ4ZWcwY1FXY2JnVG4yQ2ZQeTRVdUxKdVhFcDBDZnFzTmNNRUFIMWJPek80ZTNKS2VqWFAzTEVPXzREN1kzQnVzZkdvMG5qN1VOR2dVNFBnSzdEaGVUUmI5TGhBbGFwQUJIVno5bHc0YzdBck9SNjRBcnNwRndFTFN0dGFId01wVlU4bEhGOUNSRUN6aEIwNnByeGJnd3FiM2ZXMkQ4X0FnZ0xQeHJlRWd2UFphNFBIeDBDNlpVeWNOQQ?oc=5</t>
-  </si>
-  <si>
-    <t>Nvidia and Meta expand GPU team up with millions of additional AI chips - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Nvidia and Meta expand GPU team up with millions of additional AI chips  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNaEc1R3NCLTZRdDgwVWd6UDR5ZXB5SXd4Q0c2dlBUbVpnT1ZzRU8xMnh5bWNEa1BuS25zRHg3Qk45OW1QaVk3MlE1MEhta25icVhvYkw5UXd0MjU2U2gtVmljdFBrMzM1X1FKQzRPNG9uVllMb0lRSXFvQWx3TWFmaDAyaTNIMFhabl9maFdRek1jcVpBOEJaeFMzbUgxbF82dXRKTjVCZzRqZm9iNkUwbjNyQmZ6WkYw?oc=5</t>
-  </si>
-  <si>
-    <t>Chicago Atlantic Real Estate Finance Schedules Fourth Quarter 2025 Earnings Release and Conference Call Date - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Chicago Atlantic Real Estate Finance Schedules Fourth Quarter 2025 Earnings Release and Conference Call Date  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNazBfQm5fMm1UTGZMVF9JQm5FLXNnZHpwekp6R3lNQTk5aGYtd2J2eW9KemNpSHZWNzQtVVZ6NU92dTh6eEFSOTZ5NThjeV9yd0VXMU43djVCQTBLYUhJeks1b2xXX21HYXdVNjFOdzNwZDRrNmlRX1dFTGNyUjYtMHZPUUVaTWo5bWc?oc=5</t>
-  </si>
-  <si>
-    <t>Unlocking Finance for Nature-based Solutions in Indian Cities - Climate Policy Initiative</t>
-  </si>
-  <si>
-    <t>Unlocking Finance for Nature-based Solutions in Indian Cities  Climate Policy Initiative</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNbE9VZDZKVktsajJEVG0yM1ZfWEJ3Ums3RHRTM0FOZTFEZnFwa1NFSXBSbXpLMUpzNUktWGtqSzRVN052RllQUDNMY2x3TWlFSnNUS2VyNzF5X05ZWmx1MTlYSVlwOS05WDhjcmpCZTBacHc1Q29Ba2lZUkVuclMtaFJ6ejI3Z2lkMHVYdEFJREJIdXF2ZUVXT0VMMlFaLWRoeHFKY2xMS2syRTJWZDVQaVRraTQ?oc=5</t>
-  </si>
-  <si>
-    <t>Stock market today: Dow, S&amp;P 500, Nasdaq rise as AI worries recede, with Fed minutes ahead - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Stock market today: Dow, S&amp;P 500, Nasdaq rise as AI worries recede, with Fed minutes ahead  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQcEhkYkxjdlVSbDVfTk83VmVuZ2pVTmgzNjFsRFRjc0VqelNPX1c1RFZ4am1Ra3U5TUlVWnFNTVZkTlNTRGpzanNCcUVybTlGNHNMaXR4ajc4VVZqbW55cFp5ZWJlR3NGZmM1OFEyMmFqblBQVmNwdkdLRzRSMWdfVVpwZmYyRndHczgtOHYxWTNSQ3V1WmkzcTJod0d6X0pmY3B2d0ItTmx1OWpCenVtdzUtc09PeW1JWVgwcDQxYUJIZktZRHBGTC1idnc2cFFINVE?oc=5</t>
-  </si>
-  <si>
-    <t>Snap Finance Study Finds Majority of U.S. Households Delayed Essential Purchases in 2025 as Credit Pressures Persist Into 2026 - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Snap Finance Study Finds Majority of U.S. Households Delayed Essential Purchases in 2025 as Credit Pressures Persist Into 2026  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOTzNzdHpaNkF0TUlxNHJwdGtIRzQzdTBlNXpkUWRTbVdna1M0eE1IU1NvS1otYTAzVEFub2lvVWlKeHd6QkY3RmJ0T3NqSkVBX29Ya25DbkNydnZDRG55OGxDTksydXo4Y3JWSXNRd1U3UUY5Zm0zdlExbDVkZkxzVmxlU05Rdw?oc=5</t>
-  </si>
-  <si>
-    <t>Lightrock grabs an exit opportunity from Indian small business lender Aye Finance - ImpactAlpha</t>
-  </si>
-  <si>
-    <t>Lightrock grabs an exit opportunity from Indian small business lender Aye Finance  ImpactAlpha</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPbW5lcmJoSERuOFp0MGYzaHJXS2Q4c2FTNUgyODYybUlOZ2JKUlVLcTcwYlRoNmRxbC0tejNBZXFaSHhEaTR2Q1VDT1BEREtLWjhiM2JDSFFpM2JGMUYyazI4a2ZkTm9Ja2pCRmNtcGhqTlJzcFowVlNKWmxtOHpSR1g1X1hEaXZyVXB1Y0ZlYVlkV3N3VTVTT2U3Y1ZKMHE2VkNSeHpKNWYtUQ?oc=5</t>
-  </si>
-  <si>
-    <t>OPENLANE, Inc. Reports 2025 Financial Results - PR Newswire</t>
-  </si>
-  <si>
-    <t>OPENLANE, Inc. Reports 2025 Financial Results  PR Newswire</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNZ3FFQzNzUG81QkNjTDgycHBKSUh3NURtVi1WUkR0cGFoODg3LUFyX25YYjVYNFIzU0U2cW9YT2pkcUNxTnpWb2VoUFpGTGI2N2I0Y2tmZ1hwWVlQRzhNVU1LdnBzYkx6QUpKSlRLQmJiMHFuV0NSNkhpTEZpVTIxeTRwVmUxc2c3S01fYnVWZVJDR2Z3VzlvV2MweUw0bXJk?oc=5</t>
-  </si>
-  <si>
-    <t>Are Finance Stocks Lagging Barclays (BCS) This Year? - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Are Finance Stocks Lagging Barclays (BCS) This Year?  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPbkt4OTRYNGtDSjRKUTF5Y3hVZ242YzN0Nmlub0kzMl9KbnRRU00tMHdLVEl3aTY0V0Y5QWFzRDAtQ0M5WlVGV3ZxV1NzN3VpaWt2UVhVNWZVTDlScHA1bzg5TFlpN2p4Q0FGbHVhVVNuaWNzOTVQMTVoeklfR1hOT3h0R1ZlYmpQ?oc=5</t>
-  </si>
-  <si>
-    <t>West Virginia Senate Finance Committee approves appropriations bill for Hancock County Schools - News and Sentinel</t>
-  </si>
-  <si>
-    <t>West Virginia Senate Finance Committee approves appropriations bill for Hancock County Schools  News and Sentinel</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxORmNQWEtJSnc0OEQ2Yl92TldtMHJrVEdaZUdNdHNvb0pWdmpLcGdTV0xXZE5EcmJsWWFLSmxaOENUdUFqel92bTRjZ1g0TU9uLXVHTXNTY2x0VmVYV1Y4V1p4RTZKVDVNUGZHY0l3V3dWdmtuVGxMcmtOQVpralpLaDdGNXJ6OUt6dEpsMlNHQzNSOXpsclJBX1lOMXYzdkptaGlJRkRhNVdIaWowc2pFTTM5VlRFVlJsM0FCaU81TDl0by1fVVRCcUhYdThWYUdJbVRwUElna0hEVjQtM0NhYUlBcUtBUQ?oc=5</t>
+    <t>JPMorgan names Catherine O'Donnell head of North America Leveraged Finance - Reuters</t>
+  </si>
+  <si>
+    <t>JPMorgan names Catherine O'Donnell head of North America Leveraged Finance  Reuters</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOWEpseFJwUG1ZQno2N1VKRENxaUhBQjIyWDRwTHZSVXJmWGNndkF6dkxITFJkMENyb3NVMjRwaXRPOTd1TnU1LTNXdzdWTk55Tmk0b1ZzUG5RdzBEbGJWbXFOY2hfaHl2QldMdUF6RmhfdGVqMXhibk03cGNXVmVZaDVMUm92N0d5WWZkVHFuc254cGpMSG5SOXVBRnpNLVQyRWE3MjNxTlFvY1dkbkIzb2ZmSlk1eDZrb0VkRUpQcmQ?oc=5</t>
+  </si>
+  <si>
+    <t>Will investors buy the transition bond label? - Environmental Finance</t>
+  </si>
+  <si>
+    <t>Will investors buy the transition bond label?  Environmental Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOaFF0YzF2bWd3eHM4WHR5NHVzSlNRNTFUYk1QLWxCbjd6V2dzRkxHU2ttOGxsV1ZPVEtxTnBscVNLYjFYNGtEUGhIRzNaMUNUVGxaZkkwY2hOd1V2VVN0Y1RfM21SYXdnUlJtdktzWDkxN0JVTU41c0xuOTFrTFM2LU1jellYOTNaTGh6NGJhOWpXSFRxUnZZcG12Q3pVZV9sSHU0TnBGYw?oc=5</t>
+  </si>
+  <si>
+    <t>Gator Capital Management’s Investment Thesis for TFS Financial Corporation (TFSL) - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Gator Capital Management’s Investment Thesis for TFS Financial Corporation (TFSL)  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQQVpxUHI5eVNWd1FLVmJEdmtqbFd4Y2FfenVZbnNyVGdIWjJKM3VBUURxSVVRMi1tQjJPUWVaX2d2N051QVpqV2kzb05TdFRPcWpyejNKWDExUVRQUjFBX280MGRuM3BhZjNwYXR0N0pwOFlzN3RFRTQyM3dFRVdnVFdIMGZrMWFWSUY5YWs5dkJqdw?oc=5</t>
+  </si>
+  <si>
+    <t>Stock market today: Dow, S&amp;P 500, Nasdaq futures rise as AI worries recede, with Fed minutes ahead - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Stock market today: Dow, S&amp;P 500, Nasdaq futures rise as AI worries recede, with Fed minutes ahead  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQQWYwUXZORzFQZ1lfcUhPRnZVODdGLTdXbWRtVjVCVXRaV0dRQ2ktQmVYUXhDV0hULXFBclcyeDcyc0FuamRGdkI3SDRHYlFSa1JNa1NDSzM0engwclZWTnBqZmNYa0stRl9vcllHQ2E5cEZBc0hveVZ6M2MtLVBLTC0zaV9uWEVRYnpCemYwSUxuYlNiZ0VhRXl2c2RQblIyY0xFY2h6WElsbFJ5LXZaVUtpN09yRS1uTm9PTEFVQTRjSW5iNDNWMUVFRkhiNl9USXRyYV9BRVpiZ1ll?oc=5</t>
+  </si>
+  <si>
+    <t>Finance Chair Warns of Prediction Market Impact on Sports Gaming - State Affairs</t>
+  </si>
+  <si>
+    <t>Finance Chair Warns of Prediction Market Impact on Sports Gaming  State Affairs</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE04U3ZjVE9SNjRpN0hGSkEyNUNqdWMwclFieHV0UlpZNHdGRV9lSmdrdVlhcnVaSHJmQ3lpb3J6YnBnS2p2VEN4R0xwMjJ0d2NkNURTNFNpdzFOZ2xPTmppdGFxOFNJQTh2WHFFRTNxeGY1YkpXX01sWTJOUVBUNkE?oc=5</t>
+  </si>
+  <si>
+    <t>Medicare Advantage growth slows - Healthcare Finance News</t>
+  </si>
+  <si>
+    <t>Medicare Advantage growth slows  Healthcare Finance News</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5pQnk4Q0VjOEViR3Uyc29jUVota3pxNjFkOHVDOXJYX0RzNjA4TWxVVkd2NnRFU09oelViOGVjM2laRkFKRHREN2tId3lOWWM3TVVzeXd2Q0dBSTBvcnFua0JWYm9ibzY4aDVVTzgtQVBvVW9fWjh6cVVLWXhrWjg?oc=5</t>
+  </si>
+  <si>
+    <t>Morning Bid: Changing of Lagarde - Reuters</t>
+  </si>
+  <si>
+    <t>Morning Bid: Changing of Lagarde  Reuters</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPbExHYkdzZWlmeWtDWkJaVGtsV2ptaFRRT0tkT2l1cW9FMDN1NXNHdmoyWEFkN0JPakhxX2l1WFVWMlJ3M3NBNFplM2dwZC16OEl0MjdzYWVMcXlObGJMT2RsTExOaGNYUXZoVkVzcVZpUWR4V3VFYjFnb1NkSEFEUERB?oc=5</t>
   </si>
   <si>
     <t>Analog Devices Reports Fiscal First Quarter 2026 Financial Results - PR Newswire</t>
@@ -1961,40 +2042,49 @@
     <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPdk5GakFqU2s3RjN1N0VIb3RsZ0ZPQ1NqRVFXZXMtZ1QtV1AxWUxzWjVDemJrQmppMm9WTWZyMk5COVRDUF9WWk9zalhYamlIaUZOMlRVMTF6SUNJMnJRWEFZQ2hEeUVXb0dRNUpsdk9ydmxEVXlVcW9OdUhQX2VmNFpyZkJvQWdob0h4VzlWMGJKWTFUVTJySXZ0NGhJdmp1SWdVSGZLUkoxaFVfMEJoTG43QzZuYTlkTXRsNF9NWQ?oc=5</t>
   </si>
   <si>
-    <t>Financial scams are on the rise — but what’s being done about it? - The Hill</t>
-  </si>
-  <si>
-    <t>Financial scams are on the rise — but what’s being done about it?  The Hill</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQbFU0OFZxQ2tVdlpqamVrdldYbTE1N0NkOWw4RjlnQ3lDaFVIanpfTFNrbllSVWMySl9DS0FmZzlWSDRCTEloTEF2Vms5QmRPaFpJcjM0T3RTa3JtY3UtbW1tVlpHQkxYYWRlTTI4NWMwaXp2SVdYZDdZUlRYMHV4RmVXWdIBiAFBVV95cUxOZ1ZOWTllSWJKWEFaLTl4ZEk4LUx5dzl3M2tiMEhKZWhLb0dpaW16QnJ3RzRudExGS2NPeGZjYVVBbnItVGxfNE1pWUxyZG1SMmMxSEdxSVhIZndmM0FpRDdTbFFrNHluWVh6a2M5T3RRT2FsdkdJdlhJaGc1WXp1dVNFNXhlQ2hI?oc=5</t>
-  </si>
-  <si>
-    <t>JPMorgan names Catherine O'Donnell head of North America Leveraged Finance - Reuters</t>
-  </si>
-  <si>
-    <t>JPMorgan names Catherine O'Donnell head of North America Leveraged Finance  Reuters</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOWEpseFJwUG1ZQno2N1VKRENxaUhBQjIyWDRwTHZSVXJmWGNndkF6dkxITFJkMENyb3NVMjRwaXRPOTd1TnU1LTNXdzdWTk55Tmk0b1ZzUG5RdzBEbGJWbXFOY2hfaHl2QldMdUF6RmhfdGVqMXhibk03cGNXVmVZaDVMUm92N0d5WWZkVHFuc254cGpMSG5SOXVBRnpNLVQyRWE3MjNxTlFvY1dkbkIzb2ZmSlk1eDZrb0VkRUpQcmQ?oc=5</t>
-  </si>
-  <si>
-    <t>Will investors buy the transition bond label? - Environmental Finance</t>
-  </si>
-  <si>
-    <t>Will investors buy the transition bond label?  Environmental Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOaFF0YzF2bWd3eHM4WHR5NHVzSlNRNTFUYk1QLWxCbjd6V2dzRkxHU2ttOGxsV1ZPVEtxTnBscVNLYjFYNGtEUGhIRzNaMUNUVGxaZkkwY2hOd1V2VVN0Y1RfM21SYXdnUlJtdktzWDkxN0JVTU41c0xuOTFrTFM2LU1jellYOTNaTGh6NGJhOWpXSFRxUnZZcG12Q3pVZV9sSHU0TnBGYw?oc=5</t>
-  </si>
-  <si>
-    <t>Gator Capital Management’s Investment Thesis for TFS Financial Corporation (TFSL) - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Gator Capital Management’s Investment Thesis for TFS Financial Corporation (TFSL)  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQQVpxUHI5eVNWd1FLVmJEdmtqbFd4Y2FfenVZbnNyVGdIWjJKM3VBUURxSVVRMi1tQjJPUWVaX2d2N051QVpqV2kzb05TdFRPcWpyejNKWDExUVRQUjFBX280MGRuM3BhZjNwYXR0N0pwOFlzN3RFRTQyM3dFRVdnVFdIMGZrMWFWSUY5YWs5dkJqdw?oc=5</t>
+    <t>Gorilla Technology Acquires Shackleton Finance to Establish Regulated Capital Platform and Fund AI Infrastructure Growth - Investing News Network</t>
+  </si>
+  <si>
+    <t>Gorilla Technology Acquires Shackleton Finance to Establish Regulated Capital Platform and Fund AI Infrastructure Growth  Investing News Network</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPNmZQaXZmQVBnOURjeVFnZ2Y4U3U2MU1LVHRQUTdMLTUyWXFvM2htN3RJaVQwQmU2M203N2x1SkYwNVhtZnZ3QXNqNDZEVzU5N1pmTUhMX096M1ZhMUd2U2p6VXNrMWNnX092TEhMVUNQbWlua0JOc1hFYkNST1BzZ2E4cW95TVhCSDltX2xZeXJYUzY3Q0JZckxMUkQzUUhVX2tVc1YxbDg2WWhZWXd2YkctWEd1ME5qbGcyY1RTYl9tcWFSVHZUOWdtZTl3SkZoWU42WlRuTm9rWlRRZG8zaw?oc=5</t>
+  </si>
+  <si>
+    <t>Tuition, financial aid rates set for 2026–27 academic year - University of Rochester</t>
+  </si>
+  <si>
+    <t>Tuition, financial aid rates set for 2026–27 academic year  University of Rochester</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNclRRcDI0YUNSbzR1aWhpc29FZVBtT0ZZTlkxRXpkdjUyZXJfN0NBSTZjaFJLeDIxbHFNS2J0NWN6QURmZDI5OWg1NHdSYzVzTlhzbDM2R0gwVzNiXzJkWlpjcTlQNVBNOGpFc1BSbTRVQm81V0dfeDRQZzRJRzFNdmNKT3A5OC1qclB5dkxCaWNBOWpWZlBCOFFncw?oc=5</t>
+  </si>
+  <si>
+    <t>Sheffield Financial, Mercury Marine launch financing partnership for outboard engines and boat packages - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Sheffield Financial, Mercury Marine launch financing partnership for outboard engines and boat packages  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNRDdXZFRmVHVSYUxLME9OTWN2R0g0TDFDR2ptUl80UmZmNVlyVkZPTWkyTmotTXBja2NqLUVxdk1EWnFucU51d3F3UlZTWTlydy1TNVFRa0lfX1hnT3YwMXNyQldaVEphSHpYSFNBYjlPcmJCcGxVdDhKSUZBX0NVY0Z6UnFVMzhUcTJXNlVyNUM?oc=5</t>
+  </si>
+  <si>
+    <t>UK's YouGov appoints former ITV finance chief as chair - Reuters</t>
+  </si>
+  <si>
+    <t>UK's YouGov appoints former ITV finance chief as chair  Reuters</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNUldhNkVfU0otcmZKSGRkQU8waHdmWnpUQVIzTzQwOHBsejlIdEFjenVGWDh4YmZsMXcycTZNbTVLdzFkMF8xZlBrUE5UMHgzYURabUFtRHFQWHhTTXBHa3pYcjhGMzVoZUlyZVZ4WE9WU3o5TjdzTHhIME05S0JRR05DRjNuMFBZajlLSV9lbEZIbk5CZTBpaGVn?oc=5</t>
+  </si>
+  <si>
+    <t>Four health systems deploy AI to control spend - Healthcare Finance News</t>
+  </si>
+  <si>
+    <t>Four health systems deploy AI to control spend  Healthcare Finance News</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNc1kycHlPNTVqbVNZY0dFNjlfem0zamM5cDVhWjNmc3FSc0ZNcUVQMmlfODJnUVF2S3hsOUV6N1REUDYxMXZwY2diRkhlY0thSmFKZVpEeUZ0ZWE3cFU5dDJEZGhXQ2poc0VlU2RSbXFlM3Q0cW9WUnhfTmFKdzhZeHBOWGd0S3dUUHVVa09NYw?oc=5</t>
   </si>
   <si>
     <t>2026 Africa SABRE Awards: African Development Bank’s access-to-finance “AFAWA: Banking on Women” communications wins top global campaign honors - African Development Bank Group</t>
@@ -2006,60 +2096,6 @@
     <t>https://news.google.com/rss/articles/CBMingJBVV95cUxPNFVQU1NQV2VGeEtVMWFlUHRTa1ByUFUxV29fZ255Xzk3eUR2UUJpVWJuU2xGd09JYTlWaWM5ejZza00wM19QMWZSYjU3THlVSGoyU0ZXdGRpYktEeXJOMzZ2N2VkblZZQjd3emkxU2l6eVJ1amdabGlwelhlVE9fUUhhM1N0MEJaUXJsRVg5WGVpeHlDRGJyLWZiSXkzWk94OWxBRTdrYlJhdUdvT0dmalZka1FTT0FGb293dlo2M2kyZ0psR3NDbDM4SXRSZUFRb3c2NGJlbzhxMk1vckFnZlhwMjF1WkFMc0djc01kd2h4eFZ5dG5uZUx0ekFKR3FBbzJucHI5R0pMQjYySTJkUEVGNTR5cGplOVQ4WUJn?oc=5</t>
   </si>
   <si>
-    <t>Tuition, financial aid rates set for 2026–27 academic year - University of Rochester</t>
-  </si>
-  <si>
-    <t>Tuition, financial aid rates set for 2026–27 academic year  University of Rochester</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNclRRcDI0YUNSbzR1aWhpc29FZVBtT0ZZTlkxRXpkdjUyZXJfN0NBSTZjaFJLeDIxbHFNS2J0NWN6QURmZDI5OWg1NHdSYzVzTlhzbDM2R0gwVzNiXzJkWlpjcTlQNVBNOGpFc1BSbTRVQm81V0dfeDRQZzRJRzFNdmNKT3A5OC1qclB5dkxCaWNBOWpWZlBCOFFncw?oc=5</t>
-  </si>
-  <si>
-    <t>Gorilla Technology Acquires Shackleton Finance to Establish Regulated Capital Platform and Fund AI Infrastructure Growth - Investing News Network</t>
-  </si>
-  <si>
-    <t>Gorilla Technology Acquires Shackleton Finance to Establish Regulated Capital Platform and Fund AI Infrastructure Growth  Investing News Network</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPNmZQaXZmQVBnOURjeVFnZ2Y4U3U2MU1LVHRQUTdMLTUyWXFvM2htN3RJaVQwQmU2M203N2x1SkYwNVhtZnZ3QXNqNDZEVzU5N1pmTUhMX096M1ZhMUd2U2p6VXNrMWNnX092TEhMVUNQbWlua0JOc1hFYkNST1BzZ2E4cW95TVhCSDltX2xZeXJYUzY3Q0JZckxMUkQzUUhVX2tVc1YxbDg2WWhZWXd2YkctWEd1ME5qbGcyY1RTYl9tcWFSVHZUOWdtZTl3SkZoWU42WlRuTm9rWlRRZG8zaw?oc=5</t>
-  </si>
-  <si>
-    <t>Stock market today: Dow, S&amp;P 500, Nasdaq futures rise as AI worries recede, with Fed minutes ahead - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Stock market today: Dow, S&amp;P 500, Nasdaq futures rise as AI worries recede, with Fed minutes ahead  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQQWYwUXZORzFQZ1lfcUhPRnZVODdGLTdXbWRtVjVCVXRaV0dRQ2ktQmVYUXhDV0hULXFBclcyeDcyc0FuamRGdkI3SDRHYlFSa1JNa1NDSzM0engwclZWTnBqZmNYa0stRl9vcllHQ2E5cEZBc0hveVZ6M2MtLVBLTC0zaV9uWEVRYnpCemYwSUxuYlNiZ0VhRXl2c2RQblIyY0xFY2h6WElsbFJ5LXZaVUtpN09yRS1uTm9PTEFVQTRjSW5iNDNWMUVFRkhiNl9USXRyYV9BRVpiZ1ll?oc=5</t>
-  </si>
-  <si>
-    <t>Finance Chair Warns of Prediction Market Impact on Sports Gaming - State Affairs</t>
-  </si>
-  <si>
-    <t>Finance Chair Warns of Prediction Market Impact on Sports Gaming  State Affairs</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE04U3ZjVE9SNjRpN0hGSkEyNUNqdWMwclFieHV0UlpZNHdGRV9lSmdrdVlhcnVaSHJmQ3lpb3J6YnBnS2p2VEN4R0xwMjJ0d2NkNURTNFNpdzFOZ2xPTmppdGFxOFNJQTh2WHFFRTNxeGY1YkpXX01sWTJOUVBUNkE?oc=5</t>
-  </si>
-  <si>
-    <t>Morning Bid: Changing of Lagarde - Reuters</t>
-  </si>
-  <si>
-    <t>Morning Bid: Changing of Lagarde  Reuters</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPbExHYkdzZWlmeWtDWkJaVGtsV2ptaFRRT0tkT2l1cW9FMDN1NXNHdmoyWEFkN0JPakhxX2l1WFVWMlJ3M3NBNFplM2dwZC16OEl0MjdzYWVMcXlObGJMT2RsTExOaGNYUXZoVkVzcVZpUWR4V3VFYjFnb1NkSEFEUERB?oc=5</t>
-  </si>
-  <si>
-    <t>Medicare Advantage growth slows - Healthcare Finance News</t>
-  </si>
-  <si>
-    <t>Medicare Advantage growth slows  Healthcare Finance News</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5pQnk4Q0VjOEViR3Uyc29jUVota3pxNjFkOHVDOXJYX0RzNjA4TWxVVkd2NnRFU09oelViOGVjM2laRkFKRHREN2tId3lOWWM3TVVzeXd2Q0dBSTBvcnFua0JWYm9ibzY4aDVVTzgtQVBvVW9fWjh6cVVLWXhrWjg?oc=5</t>
-  </si>
-  <si>
     <t>Let Idaho fix campaign finance, get dark money out of politics | Opinion - Idaho Statesman</t>
   </si>
   <si>
@@ -2069,6 +2105,42 @@
     <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNWnMya0FLQWJQdFdvYVlfT3EzLXFsMFFoQU83OVdmMDI4ZlVmbTNjd0ZXeXBfWGN0VlZVdE9PZWVYZms3c3p6QUp6ZlZoOE9pdHFGaFZFN3lJazlxeWppOEpkN2ZiVUI2TDRadHhuc0dCRy1DekFmOEdRVnkySDdtcU5B0gGCAUFVX3lxTE42d2trUFl6Ql9PYjh6MFhsaU1KS1BQc2ZwWnZkTnRrX3pIbTJoc0czaHUweGVsVHRNSmNZX1ZMZ3hqeXpRdGJKb3RaUVAwRlB2VjZGVmJ0Wmh6LWMzQzdnOWFPbDV3cDhNX3pvV0tSVXZtRXNTOGVYbVYxbGRpbUxJZmc?oc=5</t>
   </si>
   <si>
+    <t>Senate bill decreasing campaign finance transparency passed - theintermountain.com</t>
+  </si>
+  <si>
+    <t>Senate bill decreasing campaign finance transparency passed  theintermountain.com</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNcVJRNTA1YVFuTldWNjFfNnV2bV9wYS1UNHR2UWszUEQ2NlNlRjRGaEFIS3NoQ3c3UExHVmF4UHFZeThYQUgtSURkN1ZPV1hBRUx5RndTV2VqT3JzQTVvc1NyOHpINnAxQS1zLWJHMlBLLXVSSGQ3TXd0ZHJoblhSWlFfMWFhaXhaRTRWR25vdkJhVURNaGtDX29MNjJfWFQtbXhWTFBkVXhUdnhYcENsZl9VNlFCaTIx?oc=5</t>
+  </si>
+  <si>
+    <t>Xerox partners with Texas PE firm, secures $450M in financing - Hartford Business Journal</t>
+  </si>
+  <si>
+    <t>Xerox partners with Texas PE firm, secures $450M in financing  Hartford Business Journal</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQSDFpZ0hmb213MU02blo3Rk9nU3phencxblN0YnBvTW5kZEtDN1gzdWtEaU5nc2pyNmFUYjNTM1VaRDVOSGNZMF9kUEQ0Z1F3cVVsczlkaEw2RkhFSnhLSXVwbHREcEZCUUFJbXpiT3dEN2plOU5tOTZBTVRMNmNoNXNzQ1VlOHEtdFpUMUNGZE9SN083cXFfaUk2Z3cwZw?oc=5</t>
+  </si>
+  <si>
+    <t>Embedded Finance Reshapes SME Cash-Flow Stability: Implications For Advisors - Wealth Briefing</t>
+  </si>
+  <si>
+    <t>Embedded Finance Reshapes SME Cash-Flow Stability: Implications For Advisors  Wealth Briefing</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOcFNnTkg3WGFKSWI3c2toU0RhTmJzdHNyVndiOW5sSDVyaWVqVkZkQ2FqMEREUWVsWFhWUXVZdGdBNEZXYUV5WmxtSE1YOVVEZTRaY2pEanFtczNXOTN2NFNmeWhkSlFSRGVfc2YxcGllVFFYaXgxVnA2cFctbGs3ei1USEFtM042eGZqeE0xS0dmY1ZaUkZKRy1fcmNUWkxyVFNhUlN6RTA0N3cwRW9FYUM2QXprMTUwd2tVRGJERnZrRng1VmJYYmJvX0h3dw?oc=5</t>
+  </si>
+  <si>
+    <t>Japan Election Supermajority Boosts Market Confidence In Economic Recovery - Global Finance Magazine</t>
+  </si>
+  <si>
+    <t>Japan Election Supermajority Boosts Market Confidence In Economic Recovery  Global Finance Magazine</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPenFOalRHdHhVR2dmNUR4SDhSeEVzLU1ZLUVYUk1UMXZwNGgtTWI4REJISU90TlhIeXRHaEtRY19RalVwSXNjUE9zUXBWNUFsbTZEQURudWE4WmpQOTdFNE9MUkZFMlFDcFg3NkVBQnk1a21UMF9tR0dXcV9DM0trOTZtSF96YTNHMm43U1VvUUlrNTE0cGN5UWwwZU15T1Q1TlZJQ3pyRTA3eHAxZ1NuWWZVX3VFcVM1UlJOY1VR?oc=5</t>
+  </si>
+  <si>
     <t>Symposium on International Investment Law &amp; Contemporary Crises: Divergent Approaches to the Nationality of Corporate Claimants in Banking and Finance Investor-State Arbitration - Opinio Juris</t>
   </si>
   <si>
@@ -2078,67 +2150,85 @@
     <t>https://news.google.com/rss/articles/CBMiswJBVV95cUxOVzVCTXM1OXlwdTg3WG1qR1poQW00WjBXeFhtNF9IMEhhWEZKbTBtV0lEUFNUWURScUFPVzFjOEQtMFQycnJmTmlUTFZaZm52X055djVCNDlxT1lEQXRuTnQ2Zk9iVEtLSHJiWEI2SkpsTmVCOUx3dlJkUERIcWNpMHF1WWpKeVJuMDI3bC1kZ0p1RnFuZzdoZlpqY2pVQkJTbGtqT2FpRkh4OGZqLUJJaDBCQzNTdmIxLS1mdnJ3T3pCOXZ0dGlwa0hRYTNDUXIyOFVsZjNycV9wT0tsTlhpTFRZWG5FazRaWVRzcjFaYXlYRUxEV1BnQi1jdDVqZzF1ZXQwdXdsS1pVRzQ5bnN5VTFyQVBKV05YYlFOUlZFV095TDJpOW9INEZQLXo0UXgzRnVN?oc=5</t>
   </si>
   <si>
-    <t>Sheffield Financial, Mercury Marine launch financing partnership for outboard engines and boat packages - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Sheffield Financial, Mercury Marine launch financing partnership for outboard engines and boat packages  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNRDdXZFRmVHVSYUxLME9OTWN2R0g0TDFDR2ptUl80UmZmNVlyVkZPTWkyTmotTXBja2NqLUVxdk1EWnFucU51d3F3UlZTWTlydy1TNVFRa0lfX1hnT3YwMXNyQldaVEphSHpYSFNBYjlPcmJCcGxVdDhKSUZBX0NVY0Z6UnFVMzhUcTJXNlVyNUM?oc=5</t>
-  </si>
-  <si>
-    <t>UK's YouGov appoints former ITV finance chief as chair - Reuters</t>
-  </si>
-  <si>
-    <t>UK's YouGov appoints former ITV finance chief as chair  Reuters</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNUldhNkVfU0otcmZKSGRkQU8waHdmWnpUQVIzTzQwOHBsejlIdEFjenVGWDh4YmZsMXcycTZNbTVLdzFkMF8xZlBrUE5UMHgzYURabUFtRHFQWHhTTXBHa3pYcjhGMzVoZUlyZVZ4WE9WU3o5TjdzTHhIME05S0JRR05DRjNuMFBZajlLSV9lbEZIbk5CZTBpaGVn?oc=5</t>
-  </si>
-  <si>
-    <t>Four health systems deploy AI to control spend - Healthcare Finance News</t>
-  </si>
-  <si>
-    <t>Four health systems deploy AI to control spend  Healthcare Finance News</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNc1kycHlPNTVqbVNZY0dFNjlfem0zamM5cDVhWjNmc3FSc0ZNcUVQMmlfODJnUVF2S3hsOUV6N1REUDYxMXZwY2diRkhlY0thSmFKZVpEeUZ0ZWE3cFU5dDJEZGhXQ2poc0VlU2RSbXFlM3Q0cW9WUnhfTmFKdzhZeHBOWGd0S3dUUHVVa09NYw?oc=5</t>
-  </si>
-  <si>
-    <t>Senate bill decreasing campaign finance transparency passed - theintermountain.com</t>
-  </si>
-  <si>
-    <t>Senate bill decreasing campaign finance transparency passed  theintermountain.com</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNcVJRNTA1YVFuTldWNjFfNnV2bV9wYS1UNHR2UWszUEQ2NlNlRjRGaEFIS3NoQ3c3UExHVmF4UHFZeThYQUgtSURkN1ZPV1hBRUx5RndTV2VqT3JzQTVvc1NyOHpINnAxQS1zLWJHMlBLLXVSSGQ3TXd0ZHJoblhSWlFfMWFhaXhaRTRWR25vdkJhVURNaGtDX29MNjJfWFQtbXhWTFBkVXhUdnhYcENsZl9VNlFCaTIx?oc=5</t>
-  </si>
-  <si>
-    <t>Xerox partners with Texas PE firm, secures $450M in financing - Hartford Business Journal</t>
-  </si>
-  <si>
-    <t>Xerox partners with Texas PE firm, secures $450M in financing  Hartford Business Journal</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQSDFpZ0hmb213MU02blo3Rk9nU3phencxblN0YnBvTW5kZEtDN1gzdWtEaU5nc2pyNmFUYjNTM1VaRDVOSGNZMF9kUEQ0Z1F3cVVsczlkaEw2RkhFSnhLSXVwbHREcEZCUUFJbXpiT3dEN2plOU5tOTZBTVRMNmNoNXNzQ1VlOHEtdFpUMUNGZE9SN083cXFfaUk2Z3cwZw?oc=5</t>
-  </si>
-  <si>
-    <t>Japan Election Supermajority Boosts Market Confidence In Economic Recovery - Global Finance Magazine</t>
-  </si>
-  <si>
-    <t>Japan Election Supermajority Boosts Market Confidence In Economic Recovery  Global Finance Magazine</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPenFOalRHdHhVR2dmNUR4SDhSeEVzLU1ZLUVYUk1UMXZwNGgtTWI4REJISU90TlhIeXRHaEtRY19RalVwSXNjUE9zUXBWNUFsbTZEQURudWE4WmpQOTdFNE9MUkZFMlFDcFg3NkVBQnk1a21UMF9tR0dXcV9DM0trOTZtSF96YTNHMm43U1VvUUlrNTE0cGN5UWwwZU15T1Q1TlZJQ3pyRTA3eHAxZ1NuWWZVX3VFcVM1UlJOY1VR?oc=5</t>
-  </si>
-  <si>
-    <t>Embedded Finance Reshapes SME Cash-Flow Stability: Implications For Advisors - Wealth Briefing</t>
-  </si>
-  <si>
-    <t>Embedded Finance Reshapes SME Cash-Flow Stability: Implications For Advisors  Wealth Briefing</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOcFNnTkg3WGFKSWI3c2toU0RhTmJzdHNyVndiOW5sSDVyaWVqVkZkQ2FqMEREUWVsWFhWUXVZdGdBNEZXYUV5WmxtSE1YOVVEZTRaY2pEanFtczNXOTN2NFNmeWhkSlFSRGVfc2YxcGllVFFYaXgxVnA2cFctbGs3ei1USEFtM042eGZqeE0xS0dmY1ZaUkZKRy1fcmNUWkxyVFNhUlN6RTA0N3cwRW9FYUM2QXprMTUwd2tVRGJERnZrRng1VmJYYmJvX0h3dw?oc=5</t>
+    <t>Stock market today: Dow, S&amp;P 500, Nasdaq futures climb with AI disruption in focus, Fed minutes ahead - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Stock market today: Dow, S&amp;P 500, Nasdaq futures climb with AI disruption in focus, Fed minutes ahead  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNM2lKWUJWMWdzZExXazVwM3M0Y0w5WnBKYUI1SHZWSDNnSkgxUVgxSUNVOEpneDh6NFNPdS1PZDJVWWhLbndnMWk4bFNUS3ZOWVJQVUpTTldhcUdEdmxDeTRDaS1hVURCUmgtR2RBb3d2TDBYbGVLUk5zZUl3cHQ5MmhiRkk0WTF6YXZZeXEtdG9EcF92Qlg3ang3TTFZMElfRWRQamFaRGdrcG5Ta3I0OHVPTGNMc3o3Q0F4Y1k0VVk4a2o5NEd1Y1lTQ0xkdVpNNlIyUU5uamZNZmJNREtLcA?oc=5</t>
+  </si>
+  <si>
+    <t>red violet to Announce Fourth Quarter and Full Year 2025 Financial Results on March 4, 2026 - Yahoo Finance UK</t>
+  </si>
+  <si>
+    <t>red violet to Announce Fourth Quarter and Full Year 2025 Financial Results on March 4, 2026  Yahoo Finance UK</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNUmpwMW1xVEFBUWZjcWRMRG1VVjRZTDFYT1pvQ3NqLVM0ZlQyX2pCc1ZyVHNQWGpaaTVUVVd2NHNMWHhXRmRQREVoWFJlZmg0Z25Yc29mNzFiU1AzR2U1N2swWWJ3S093Z21fV2d0VTlQTUtuUXlGMFJEa3VCNU5veWRTMmxxUkFRLU5N?oc=5</t>
+  </si>
+  <si>
+    <t>Commentary: Campaign finance reform suffers the risk of ‘a deal that has yet to be real - The Portland Tribune</t>
+  </si>
+  <si>
+    <t>Commentary: Campaign finance reform suffers the risk of ‘a deal that has yet to be real  The Portland Tribune</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNUWZMLXk4dms5VEh5YWJIMVZLSVdjOGExcXRQZEFhSDAzQ0d3WXRrYVhraXVDUXkyQjV4NnhQNUJxUlN0cTFRRGVORDNjOU9hS2NOZ2VMZ2NSY2w0YzRsMFQyZWJYQWJNZFNnakdvX0NZbTdjaFlSQ0dvc2dIZExUc0ctWHNGVU42QmpTcmVMblJLcE9KNlhCQTczUlJrU0JTWF93aF9OczVOcUhKSU0wVHd5bk1vSm1zS2l4S2VPMkI2OEE?oc=5</t>
+  </si>
+  <si>
+    <t>Top 10: AI Tools for Finance - AI Magazine</t>
+  </si>
+  <si>
+    <t>Top 10: AI Tools for Finance  AI Magazine</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBMangwQjkyOTJGb2d1SDI0U1N6M2o2cERWekxqbmlWT2FrZ3gtcU5ROElabGIxTjM5eEUwb2JpR09VS1UwQjAtYXFCUHEyTDU3VVdNNmtaUkxCdVdyaC1TUmVaVWNqNFU?oc=5</t>
+  </si>
+  <si>
+    <t>Pasinex Announces Q4 2025 Financial Results - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Pasinex Announces Q4 2025 Financial Results  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPVDJNaFBkZHlKN0g4QV9DRmRlZUdHSHVHbkdXYUxiYmJmRV96SFlJWEFoNEY4NFRMX2NxZ29peVh6dG9PSVpNN1cwa0xiSGVQYnp6cFdlbE1aMDhMc0lnckkwbUJCcGVJM3RQcEhHbFRpWlpGcllPU0Y2bHlFYmtaVWR3R2RiMWV5?oc=5</t>
+  </si>
+  <si>
+    <t>5 Financial Transaction Stocks to Watch Despite Elevated Expense Level - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>5 Financial Transaction Stocks to Watch Despite Elevated Expense Level  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPdThLN21OaFZvSC1IZ2ZyeEdoUVc0TnQxNUJjLXdGYkJ1UGMtSDBtSFVycXFOTktWOHlScU03YjVzc1ZiWnQwSnphYWpNSHdtVVJBQTUteHlSbWtwZ3ZJOWJkODl6NnBwd1JtaU0wdExoX0JQTjNKd3BLcHN4R1NtNC03VDBJTlpVcmc?oc=5</t>
+  </si>
+  <si>
+    <t>Financial &amp; Tax Information - Crescent Energy</t>
+  </si>
+  <si>
+    <t>Financial &amp; Tax Information  Crescent Energy</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOT2QzcEFjdlE0Ujd1TE1tUWtXZXhPajJkSkJBcUNaVHBaSTJSV0xZamFUd0UydjBPSC1waDAzNUd0dTQ0c2lHeEM5YTRoUGxFQ0JIUGFrTU51UUpTNzVoYXUyNDR0RzVGR202WHY5QkdRRjh0N0hVbFVqNjVpRVdTR3RScEJZRnZVVThyRk9YRW5GUmQxVXVaLXhudw?oc=5</t>
+  </si>
+  <si>
+    <t>Moderna stock surges as FDA reverses course, agrees to review new flu shot - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Moderna stock surges as FDA reverses course, agrees to review new flu shot  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQZ0t2N0F6U19YUjNIcE5WeGE0Ukt5VjZYSlRjWUNpd25HRnZpV0l0Mnd4N01OU3F6THRGY3FTWWREdFYzVXhVNUJyVDBxRWRVWm9Kc3VFOGl3OWhNZXYyaUs4LW9fSnBHajRSUXhvUUsxQ1gtelZiOXNnR0pnbnlOU3EwVHFvLWdNT2NUdnY3OWlzc2tiZU9mQTZZN0I2aW9RRExXVEhuTHZhSzFySnZsWTZPeDl0eWRTVE1n?oc=5</t>
+  </si>
+  <si>
+    <t>1 Financial Stock That Could Turn $250 Per Month Into $1.4 Million - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>1 Financial Stock That Could Turn $250 Per Month Into $1.4 Million  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9LV2tVdFpfN252eWtFWGtYaFhTM1pJbk5SOGtoVUdraE90YkRuNWtxRmw5VEJHS3NGT25lRkdyeENGNFc0a3ZFZHI3NldxbF85b3BoemZPdnRXeHZRT3BHQlZIUjRIa0xsYjVXV1VMTVR6NlcwODJ4UllMREFNSTQ?oc=5</t>
   </si>
   <si>
     <t>The capex crucible: What finance teams can learn from data center builds - McKinsey &amp; Company</t>
@@ -2150,69 +2240,6 @@
     <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNLUNwUVFROUdldVdjQ0ZwMnM5RmE5Y3BmTXo0bWhWd1Y2ZVdjbEJhSllULXRIdThRWV9rc2xURGk3V2NRcU0waWpNYXFjNGpXWlBqcm15R0RkYUdRVy1PWUFQNmVRUXVVOXJ4MXNxQlI3Yk8xZ0dvNFg2QjVKUl9PWHBLVDAzX1BicHA4dnUwazRjVE9ITkVLbWJiUjhzZGloVG0zQm1LM1ItRjlkQVVDYldCejR3Q0F3Q2RNU2x0S3dEbUJoR3N3eW5uVTZsX1RPLUVwOGExb0phbDJETG1femxFVmVpVlI3?oc=5</t>
   </si>
   <si>
-    <t>Financial &amp; Tax Information - Crescent Energy</t>
-  </si>
-  <si>
-    <t>Financial &amp; Tax Information  Crescent Energy</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOT2QzcEFjdlE0Ujd1TE1tUWtXZXhPajJkSkJBcUNaVHBaSTJSV0xZamFUd0UydjBPSC1waDAzNUd0dTQ0c2lHeEM5YTRoUGxFQ0JIUGFrTU51UUpTNzVoYXUyNDR0RzVGR202WHY5QkdRRjh0N0hVbFVqNjVpRVdTR3RScEJZRnZVVThyRk9YRW5GUmQxVXVaLXhudw?oc=5</t>
-  </si>
-  <si>
-    <t>Commentary: Campaign finance reform suffers the risk of ‘a deal that has yet to be real - The Portland Tribune</t>
-  </si>
-  <si>
-    <t>Commentary: Campaign finance reform suffers the risk of ‘a deal that has yet to be real  The Portland Tribune</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNUWZMLXk4dms5VEh5YWJIMVZLSVdjOGExcXRQZEFhSDAzQ0d3WXRrYVhraXVDUXkyQjV4NnhQNUJxUlN0cTFRRGVORDNjOU9hS2NOZ2VMZ2NSY2w0YzRsMFQyZWJYQWJNZFNnakdvX0NZbTdjaFlSQ0dvc2dIZExUc0ctWHNGVU42QmpTcmVMblJLcE9KNlhCQTczUlJrU0JTWF93aF9OczVOcUhKSU0wVHd5bk1vSm1zS2l4S2VPMkI2OEE?oc=5</t>
-  </si>
-  <si>
-    <t>Stock market today: Dow, S&amp;P 500, Nasdaq futures climb with AI disruption in focus, Fed minutes ahead - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Stock market today: Dow, S&amp;P 500, Nasdaq futures climb with AI disruption in focus, Fed minutes ahead  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNM2lKWUJWMWdzZExXazVwM3M0Y0w5WnBKYUI1SHZWSDNnSkgxUVgxSUNVOEpneDh6NFNPdS1PZDJVWWhLbndnMWk4bFNUS3ZOWVJQVUpTTldhcUdEdmxDeTRDaS1hVURCUmgtR2RBb3d2TDBYbGVLUk5zZUl3cHQ5MmhiRkk0WTF6YXZZeXEtdG9EcF92Qlg3ang3TTFZMElfRWRQamFaRGdrcG5Ta3I0OHVPTGNMc3o3Q0F4Y1k0VVk4a2o5NEd1Y1lTQ0xkdVpNNlIyUU5uamZNZmJNREtLcA?oc=5</t>
-  </si>
-  <si>
-    <t>red violet to Announce Fourth Quarter and Full Year 2025 Financial Results on March 4, 2026 - Yahoo Finance UK</t>
-  </si>
-  <si>
-    <t>red violet to Announce Fourth Quarter and Full Year 2025 Financial Results on March 4, 2026  Yahoo Finance UK</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNUmpwMW1xVEFBUWZjcWRMRG1VVjRZTDFYT1pvQ3NqLVM0ZlQyX2pCc1ZyVHNQWGpaaTVUVVd2NHNMWHhXRmRQREVoWFJlZmg0Z25Yc29mNzFiU1AzR2U1N2swWWJ3S093Z21fV2d0VTlQTUtuUXlGMFJEa3VCNU5veWRTMmxxUkFRLU5N?oc=5</t>
-  </si>
-  <si>
-    <t>Top 10: AI Tools for Finance - AI Magazine</t>
-  </si>
-  <si>
-    <t>Top 10: AI Tools for Finance  AI Magazine</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBMangwQjkyOTJGb2d1SDI0U1N6M2o2cERWekxqbmlWT2FrZ3gtcU5ROElabGIxTjM5eEUwb2JpR09VS1UwQjAtYXFCUHEyTDU3VVdNNmtaUkxCdVdyaC1TUmVaVWNqNFU?oc=5</t>
-  </si>
-  <si>
-    <t>Pasinex Announces Q4 2025 Financial Results - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Pasinex Announces Q4 2025 Financial Results  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPVDJNaFBkZHlKN0g4QV9DRmRlZUdHSHVHbkdXYUxiYmJmRV96SFlJWEFoNEY4NFRMX2NxZ29peVh6dG9PSVpNN1cwa0xiSGVQYnp6cFdlbE1aMDhMc0lnckkwbUJCcGVJM3RQcEhHbFRpWlpGcllPU0Y2bHlFYmtaVWR3R2RiMWV5?oc=5</t>
-  </si>
-  <si>
-    <t>5 Financial Transaction Stocks to Watch Despite Elevated Expense Level - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>5 Financial Transaction Stocks to Watch Despite Elevated Expense Level  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPdThLN21OaFZvSC1IZ2ZyeEdoUVc0TnQxNUJjLXdGYkJ1UGMtSDBtSFVycXFOTktWOHlScU03YjVzc1ZiWnQwSnphYWpNSHdtVVJBQTUteHlSbWtwZ3ZJOWJkODl6NnBwd1JtaU0wdExoX0JQTjNKd3BLcHN4R1NtNC03VDBJTlpVcmc?oc=5</t>
-  </si>
-  <si>
     <t>Papua New Guinea: 29 financial institutions decline to finance TotalEnergies liquefied natural gas project - Business and Human Rights Centre</t>
   </si>
   <si>
@@ -2222,22 +2249,58 @@
     <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxQZE11X3dpa0xGRFVUUl9XbUFULXpyc1R2N21NTTdNUlNIb0ZBSGdaVVA5YW1QbE8wMG9zd3JTakJvNDhfSkc3RXR4Z1Zkd2FfcHRDUXlwTThhLXpVV3JRaTFfSEl1alRkQ3NjeWtwakhSd2hKUlRHSjlYaWlBSUNueXJBbWV0amxycC1GOTM0aXEzMlM3M0VxNlFBZVRSRDJPdlJybDZGU1k0Tk5SbTR3VGlFN1lfOV9xSXQ1NzBzTDVNWHE4bzNXdHlvQjg2TWxaMzl5TTN2RWFmVjZrRUcyMm5KcGJNMlo3MzVfdVM3MA?oc=5</t>
   </si>
   <si>
-    <t>1 Financial Stock That Could Turn $250 Per Month Into $1.4 Million - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>1 Financial Stock That Could Turn $250 Per Month Into $1.4 Million  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9LV2tVdFpfN252eWtFWGtYaFhTM1pJbk5SOGtoVUdraE90YkRuNWtxRmw5VEJHS3NGT25lRkdyeENGNFc0a3ZFZHI3NldxbF85b3BoemZPdnRXeHZRT3BHQlZIUjRIa0xsYjVXV1VMTVR6NlcwODJ4UllMREFNSTQ?oc=5</t>
-  </si>
-  <si>
-    <t>Moderna stock surges as FDA reverses course, agrees to review new flu shot - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Moderna stock surges as FDA reverses course, agrees to review new flu shot  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQZ0t2N0F6U19YUjNIcE5WeGE0Ukt5VjZYSlRjWUNpd25HRnZpV0l0Mnd4N01OU3F6THRGY3FTWWREdFYzVXhVNUJyVDBxRWRVWm9Kc3VFOGl3OWhNZXYyaUs4LW9fSnBHajRSUXhvUUsxQ1gtelZiOXNnR0pnbnlOU3EwVHFvLWdNT2NUdnY3OWlzc2tiZU9mQTZZN0I2aW9RRExXVEhuTHZhSzFySnZsWTZPeDl0eWRTVE1n?oc=5</t>
+    <t>Gold price below $5,000 as investors wait on Fed guidance for clues - Yahoo Finance UK</t>
+  </si>
+  <si>
+    <t>Gold price below $5,000 as investors wait on Fed guidance for clues  Yahoo Finance UK</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNMUUxWklvNENGNjNoaF9ER2hvVEp0ZjNEb3hWUHdqY0lzQW9VZWd3VGtRQ1VmcWMyT2wzOUh0X0pqbXNGLWduMGFlajhPZUlaTlpfREhfdXRWbDFUem1tRnlkRVNrSXUtaWhVRERwRUNlTTFHcVYxMFFwNWN0dzVwVXdja09wa0U1SmxlTFZYdWRZa01MdWJtOGI1R1J3RTdZSFdaOU51dkFRRVBrb181UnhQWUNhS2g3YjVfV1JKODNfWjJvQzlxVFVxMGRIZw?oc=5</t>
+  </si>
+  <si>
+    <t>ADMA Biologics to Report Fourth Quarter and Full Year 2025 Financial Results on February 25, 2026 - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>ADMA Biologics to Report Fourth Quarter and Full Year 2025 Financial Results on February 25, 2026  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOelJTNnhWN2JPN1hGaXYwX200Y1ZYcUJLdkh1bUpNUGk4NGVfSlZqWTl3eGwyWUd4QjBFeXYtTW5mQzliSnVtOUk3X0NObTZDTW1jMGl0SDk0VUtMWjFGdS1EVTlHdzN1Y1B5M1VDWEJEaTRCbkhpdFNFbkxsQ0JHWkNrVWUyQTN5Mnc?oc=5</t>
+  </si>
+  <si>
+    <t>Apple decouples from Nasdaq, offering alternative to AI-fueled volatility - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Apple decouples from Nasdaq, offering alternative to AI-fueled volatility  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQc3ZPY2hTcHBmTk1zRXI2czJhSnEwaDRONDl3SmhXbEVOZWdEd3FJdkNBVDc2Q0lPalVFY0FZbGNLNkRla1BoNHFybTF0ZGkydVNkTmRRbjNMMjkyYlhwTTJnVER3TjdzUTVsd3N2QWtCWDdDZ0xGNjNpQ0dnaVpRcThjRQ?oc=5</t>
+  </si>
+  <si>
+    <t>Kyndryl (KD) Soars 11% on Financial Statement Compliance - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Kyndryl (KD) Soars 11% on Financial Statement Compliance  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPS09EMmQ0Z3BLd3VyWVFYZU9PUG8wMkFnNkxnQUYwTE9tdHQ5dXM3djhDQkJQN3pOcGsyRHdNUFBoZFY2VmxLdWQ5Qm1tUjE0RHhnTjRjM2V1LUtDSGtWdkx1X2g4VHU1NXFpbTRxRTJjcUpFaXZOSVR4bElxTkNYaQ?oc=5</t>
+  </si>
+  <si>
+    <t>Luotea plc will publish Financial Statements Release for 2025 on 27 February 2026 - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Luotea plc will publish Financial Statements Release for 2025 on 27 February 2026  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOV2t0cklVS29jTS1qa1Z3eDhNQms4bWVLUmV3MW94QTVMZnFJVXltbENYZmlPdmRneDM2RWJZbkxtT2o1WU1kdUVNSklKLXJfWU5VMWhMRmJuTzhkaW1jSGtnaFpmREk5Y2liRWVJb1FULWVubEdmTEtQX1ZUSmxRcXdveWJtdWsxODZuc2NR?oc=5</t>
+  </si>
+  <si>
+    <t>Wingstop Inc. Reports Fourth Quarter and Fiscal Year 2025 Financial Results - PR Newswire</t>
+  </si>
+  <si>
+    <t>Wingstop Inc. Reports Fourth Quarter and Fiscal Year 2025 Financial Results  PR Newswire</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxObjkzcjdQNW03cmVjV01GdWxoV2VjT2pZWEN6amlMSWw0UUotbk42TEt6cDVXZmp5Mnd1aG9QUk9Zb2owOC1BYXZjTW53RmoyWlFqNzV1ZmhSOTd0dFNJXzF5YUJsempmSDEwbVRXRk9CWmVOaXVNNG1lX2E2R3FhTFhrZDE2eDdGZVhDWnJDY1NzdF96M2VyQUVaNjIxbkVDdGhabnB3TkZPT2RzNlVmRk1iTnhzTnhDSnM0QmpVbnM5YkZ0M19aOFZ3?oc=5</t>
   </si>
   <si>
     <t>‘He’s jumping in all the way’: A Trump financial regulator backs prediction markets in their clash against states - Politico</t>
@@ -2249,13 +2312,40 @@
     <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNX3hNc0hjMW1FVW5WaVZOSnhIcmlMQjYxc1gycEdZWkczSXFPeUF0ZVh6SWg0RERvbVE1eXoyN2FyY0J0R2VQbmt0ZjZDY3BNRFpxMk5hZm4tNDl3eDdyM2tnSGFxN19udmV0LVlJbmpwbzI2cUh5WU5YZVdvYWVHRi04U2hlUnNVMm5tdE5n?oc=5</t>
   </si>
   <si>
-    <t>Gold price below $5,000 as investors wait on Fed guidance for clues - Yahoo Finance UK</t>
-  </si>
-  <si>
-    <t>Gold price below $5,000 as investors wait on Fed guidance for clues  Yahoo Finance UK</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNMUUxWklvNENGNjNoaF9ER2hvVEp0ZjNEb3hWUHdqY0lzQW9VZWd3VGtRQ1VmcWMyT2wzOUh0X0pqbXNGLWduMGFlajhPZUlaTlpfREhfdXRWbDFUem1tRnlkRVNrSXUtaWhVRERwRUNlTTFHcVYxMFFwNWN0dzVwVXdja09wa0U1SmxlTFZYdWRZa01MdWJtOGI1R1J3RTdZSFdaOU51dkFRRVBrb181UnhQWUNhS2g3YjVfV1JKODNfWjJvQzlxVFVxMGRIZw?oc=5</t>
+    <t>MFA Financial, Inc. Announces Fourth Quarter and Full Year 2025 Financial Results - Yahoo Finance Singapore</t>
+  </si>
+  <si>
+    <t>MFA Financial, Inc. Announces Fourth Quarter and Full Year 2025 Financial Results  Yahoo Finance Singapore</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPWXRuWEJ5bFhBN1VnUngzblhLVDkzMDJkaTFWSmI4NnhzSkh1NTZpX2FWeEJIM0lNLURPU3o3bU1Uc3BpLU9CeW1Sek5OSDRPYnhNY3l6bDJNdEpsdXk3UjFLVU85OGZsVVkxeFN4QjdPQXVDdHlES0tteDZ3eS1aM1dTRnp5Y3FhdHRN?oc=5</t>
+  </si>
+  <si>
+    <t>Will Chen joins Westfield Specialty as U.S. Chief Financial Officer - PR Newswire</t>
+  </si>
+  <si>
+    <t>Will Chen joins Westfield Specialty as U.S. Chief Financial Officer  PR Newswire</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPVVpzWURrVFNsVXlfeHJ5VlE0MWpPNHJnYV9FRFhyR1lzU29iOWRmTURzUW4yVDlGUFFndUl4VzBKSGlxOWV1bVlIS1BCTmlscy1OQzk2Y1FUNnhEN2ZjV2JORmtKOWZvaDdxeGhZdGxGVlVaQThlSjBBYXJfeS10VkNMMXVQaTllMGh4V0VJc0JaVVRURHZSTWVrenJyRkJXUHc0TWk4ZzR0V3R4UFpfVldfNEppUEhrX2ZVTUl3?oc=5</t>
+  </si>
+  <si>
+    <t>FOX23 Investigates: Tulsa families question credit union they used to finance pools - fox23.com</t>
+  </si>
+  <si>
+    <t>FOX23 Investigates: Tulsa families question credit union they used to finance pools  fox23.com</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxOSXF3Qlc4SzVaLUtQS1lRT0RGS3BQVUN2aEtPQjVBcThGV2c2M2gzaTBSVFVTOUhkb0VGSlF2d3JMenA2eGdmU1FQODI1NlB6Y2ZKckV3ZTY4LWx3NnlnYlFFLUNlTzdfWXpCLUs0QjZjWG9PUmxQWE9XLTNmYlZ4VDBtLTREWFMyWkpLazlDN1J1aEJCX25qYU9OSUlkSzBaaTBrQXJTU3JQRk1JZHJOX2k2TnJyN0ZMdkJPQ29meUFJOVBDQ3FhY2lULWpOR3ROTml5VW5Ma0ZYZnR3LTNkdkNhY1FNbWxtdlZJX2hZaWE?oc=5</t>
+  </si>
+  <si>
+    <t>Scottish Water taps Oracle to support agile transformation - Oracle</t>
+  </si>
+  <si>
+    <t>Scottish Water taps Oracle to support agile transformation  Oracle</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE04cnh1aG1Vcnp6bzI0R2ozajBGckJLcy10RG9JdTFlbDVacWRXSzA2V0hZa3d3bHVNY1NiVGRNVDNIM0pHVVM4SEozUG5zOFRmTmU3NVl4X2FyVDVq?oc=5</t>
   </si>
   <si>
     <t>OFS Financial Services Provides Insurance So You Don’t Have to Choose Between Care and Cost - ThurstonTalk</t>
@@ -2267,40 +2357,94 @@
     <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNcEdHdTZEVDAxNFQyT3pxNGhSdlpSU2FkdG5FYVZEY2lNU1R4YWRzV2lfalhzS005OUdDNzlpd1VuSkZhN3hTMGVqNTdZMVF6a1NRNU9lWjlLYlZaNklGTWcwVDVrYllxTFRVbXF3Umk3dzBoNkpLVlVnWjRQMXgxbThDZkZYb1puRDROU0tldHlaeXduV05qaUxBS240SGZ5UVdQbDlCZ0x4bUQxQ0NrVVJRTnZNVi1TcWE4eFJtZU9SSUVoc1haakg0Zw?oc=5</t>
   </si>
   <si>
-    <t>ADMA Biologics to Report Fourth Quarter and Full Year 2025 Financial Results on February 25, 2026 - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>ADMA Biologics to Report Fourth Quarter and Full Year 2025 Financial Results on February 25, 2026  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOelJTNnhWN2JPN1hGaXYwX200Y1ZYcUJLdkh1bUpNUGk4NGVfSlZqWTl3eGwyWUd4QjBFeXYtTW5mQzliSnVtOUk3X0NObTZDTW1jMGl0SDk0VUtMWjFGdS1EVTlHdzN1Y1B5M1VDWEJEaTRCbkhpdFNFbkxsQ0JHWkNrVWUyQTN5Mnc?oc=5</t>
-  </si>
-  <si>
-    <t>Apple decouples from Nasdaq, offering alternative to AI-fueled volatility - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Apple decouples from Nasdaq, offering alternative to AI-fueled volatility  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQc3ZPY2hTcHBmTk1zRXI2czJhSnEwaDRONDl3SmhXbEVOZWdEd3FJdkNBVDc2Q0lPalVFY0FZbGNLNkRla1BoNHFybTF0ZGkydVNkTmRRbjNMMjkyYlhwTTJnVER3TjdzUTVsd3N2QWtCWDdDZ0xGNjNpQ0dnaVpRcThjRQ?oc=5</t>
-  </si>
-  <si>
-    <t>Kyndryl (KD) Soars 11% on Financial Statement Compliance - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Kyndryl (KD) Soars 11% on Financial Statement Compliance  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPS09EMmQ0Z3BLd3VyWVFYZU9PUG8wMkFnNkxnQUYwTE9tdHQ5dXM3djhDQkJQN3pOcGsyRHdNUFBoZFY2VmxLdWQ5Qm1tUjE0RHhnTjRjM2V1LUtDSGtWdkx1X2g4VHU1NXFpbTRxRTJjcUpFaXZOSVR4bElxTkNYaQ?oc=5</t>
-  </si>
-  <si>
-    <t>Video: FOX23 Investigates: Tulsa families question credit union they used to finance pools - fox23.com</t>
-  </si>
-  <si>
-    <t>Video: FOX23 Investigates: Tulsa families question credit union they used to finance pools  fox23.com</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxNYlB5bmZWdHFBeVJWWGhxNmY5bmRZU1Azd25LNnZHLWpYVkwxWmlnTDF2QXlKb2JZcEJlbGVTT1lScHkxeU1od1N4TVotZkJvT3lRYV9sejB2QXNvWDRhTzljZTVjV2g4NUdTenN0LWpHdHhZQjBxRlRBOFpkSzBKZmVYVHhXS1RHZWRyM1FJa01UVDhqZXh5VVV5dUJPMUNVdHluRXlUN2Nyby1CalB3NkFMYW1UZ1Z5b2F2NkVtVVV3UGFjU2FwdTVjdjhzU0Z0N2hjb0Q1Z09YUmFYN0d2ZmJONFlVYzlOclMzYnhwWDZURWRHUUE?oc=5</t>
+    <t>Nvidia in focus: Meta partnership expanded, Arm stake sold - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Nvidia in focus: Meta partnership expanded, Arm stake sold  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOSFdMSEFMSDJ5Mk1nTk5xdkhTTHdDQzlJS3NZY2xKTnloYy1Nb2FQYk9QdHBoR3hqZlNOQkxzVHFTbEI5NGJ2OFA0Ulc2clhVR09nYTc3OU5jdVhMTFRDV0w2dERzWVVVQmJJWURFWUh3OEh0OTYwM2lHMkN2em9qcXotNE1sa1dzZjNaU1pn?oc=5</t>
+  </si>
+  <si>
+    <t>Verastem Oncology to Report Fourth Quarter and Full Year 2025 Financial Results on March 4, 2026 - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Verastem Oncology to Report Fourth Quarter and Full Year 2025 Financial Results on March 4, 2026  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOeHVlU1QyOWNaQnd4MlQ3dkF0RXdPczhfc0NJRDZpd2c1bDNQQThrblhraWQ2S0xhdk1kVGtDTkRrVktTZFE4c0hkcGlYS1hRdVYya0JnUlNrcEFQY09tcHBSNlhQS2pkdVByS3pFc0gydl9NOGRoQW5zX2ZLT0NZMzNkem9pRjBtQnhTZ3lB?oc=5</t>
+  </si>
+  <si>
+    <t>Charleston launches Financial Empowerment Center for residents - Live 5 News</t>
+  </si>
+  <si>
+    <t>Charleston launches Financial Empowerment Center for residents  Live 5 News</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOQXhWZFN3ek1UV3F2UjBhVXhKZlpva3pXUFRBdnJtYk5LYUc0aHdYLVlTbEw2MDRyd3hjZlNSdmUtVHEzb0FPT1RQRWtMbWN4LXdzS3c0bWZ1bEU5UDJ1V2J0OFJGemNmSEg5RE5zandQTXJPYjNIUzVucGdIcVBORTFPdldCY3Q1SjMtQjA2NS1BMmdoTkM0RXhwdXbSAbABQVVfeXFMTVFLTldMZmRxZnBLS3ltT2JQaDJFcEJWR2tMZXlVOWtNSWxDbVRMNDJUSlk1WkJVYndMSmMxTlNkT3VpclJtak1DcGtKSDR5eTIzeGtGWk9hVzBtOEZUcndOeDFtQXJLbGgxRl9mWTRzQVpydC1MX2RXZVc5VWN6cDQyc1RqRnVkeklSRUV1SU9tcHZheFRHbTFkcTFjQkI1OW9FdTF6LV9lT3FNSXNKWjY?oc=5</t>
+  </si>
+  <si>
+    <t>Palantir upgraded, Workday downgraded: Wall Street's top analyst calls - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Palantir upgraded, Workday downgraded: Wall Street's top analyst calls  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPQXBvZnBsVHRXNUF0NWpMRkFBbFJHeV9kQmFXMUxDbTRPcmszOW1TRmVDQXVROEpiLUpmQURXS2x0cnRncWZLYTRiYktrNW5PNGhfdXJrU1J5SEMzZHRMdEJ6TmxGOWt5eXRIelcyR3pPY2M2XzdrbldtazhyVGhxWXdxem9Ecm45VDVTT29kdTE?oc=5</t>
+  </si>
+  <si>
+    <t>Brian Armstrong Reveals Retail Users 'Buying The Dip' In Bitcoin, Ethereum: Coinbase CEO Says, 'They Have Diamond Hands' - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Brian Armstrong Reveals Retail Users 'Buying The Dip' In Bitcoin, Ethereum: Coinbase CEO Says, 'They Have Diamond Hands'  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPRGRKMXhSa2ZDZGZVbXRVZGpiYXNrOHpWc2FxWVpnSUMwVmtObExFdTlrSktGd0p1WlZaX1g4b3JacW9rRnVtMnpPM0tpSFIxRmJGS1cyX2ljLV9zLWxHc05qeXc3UUNBOU9PSDY4aTFMT040b3REODFGem9ULXM5SWtrSDROTzdZd0E?oc=5</t>
+  </si>
+  <si>
+    <t>Ericsson and Mastercard enhance global digital money movement and accelerate digital financial inclusion - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Ericsson and Mastercard enhance global digital money movement and accelerate digital financial inclusion  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNWk9Ha2ZHM3NrNmNMMjh2ZFlaX0dxdXdiYnBucXpHNTZZcTE1RGl6SGRCUzdMSW9yYzNqTGxRckhYT0NwUzhHVkxYSGcydVlrbTl6NzdyeG9SOW1aRmpUZ041T1V2OVNRdmRlaHVQVHRsWGpPUUlIc3I1a2dwWWJoTDFIQU90TmhxR2NQanZ1YmNkZw?oc=5</t>
+  </si>
+  <si>
+    <t>Swift Current Energy Secures Project Financing and Tax Equity for 122 MW Energy Facility in Maine - PR Newswire</t>
+  </si>
+  <si>
+    <t>Swift Current Energy Secures Project Financing and Tax Equity for 122 MW Energy Facility in Maine  PR Newswire</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOa2ZNV3VUc3ZrNktDSF9Hc1BaeGh4aFJaQWg1Uk5oSDFsdy1qQkRKSDVtWjVUV3pnVzloNHFWZ1BnUld1UGJpcnJLLUJsV2V2SVJMcW9QX0RXNDVvLXVhcUpiLXVWSWU0bWdsa3k4SnQ5OXFJeFFwQS13Wk00eGQ1RFc4WkxBcGk0azBXc1hYT3NFenk4R1hHYmFqTDZicXJvdVpiYWtXUFVjT3VBenZuMkx1UFJqSDhIVFczVUlTdl94QmVVWGJsSXd1TTRSWUx5NmVvR2ZxelBSOEtFNkZEU1laNzdOUDY3?oc=5</t>
+  </si>
+  <si>
+    <t>Harrow To Report Fourth Quarter and Year-End 2025 Financial Results After Market Close on March 2, 2026 - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Harrow To Report Fourth Quarter and Year-End 2025 Financial Results After Market Close on March 2, 2026  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxOVVB3alBRUWdJS0kxb3BYclo1VS1PclRzLVUwTmluRFFQX1JnZUVNUVEwR1JvcW94cWhnYWtuSTZ5QlA4TjBMTXNyUm0wZUt3YzhGdFpYbDBiQjBEaUpmVkFjZFNiYXY2bUZaOXJlelFaZzdSVjRmS3lsN2JEbmtxT2JJV2s?oc=5</t>
+  </si>
+  <si>
+    <t>Meta CEO Mark Zuckerberg set to testify in teen social media addiction suit - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Meta CEO Mark Zuckerberg set to testify in teen social media addiction suit  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOTDJaZUVoeXJuVjBuTUNrMU5GbEhncFgwVTZ5X0Q3bGFXNEhYakxDM3Q1VnQ1eS1rMzRDcERUSWZKX2xRcTVPNjFXbWJNTHV6SXVlcTBZd0tpTlZ2ZlZVb3JIMjZaSm1iM0UwR3h3LXdkU09MM2tmNDVFOXZmQldqQVkzV1hFRTFaSG1mQXF0OGNMY3hQbXZZa2dodjZJbkhVc1RwU0IwdGtIN2FuaURjeG11bGYxcVo5eHFsZXdn?oc=5</t>
+  </si>
+  <si>
+    <t>Recursion to Report Fourth Quarter and Full Year 2025 Business Updates and Financial Results on February 25 - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Recursion to Report Fourth Quarter and Full Year 2025 Business Updates and Financial Results on February 25  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNUktiOHpfaDBaekR6MmlpQVVTOXZ6TUZKYWxzblF4eE1acE54eXlNYWwtOVdYbmxadjhKNk5Vc1ZXVFFlNzQ1Zkt1Y0hfbDBlQ2VPOEM1Q3lEQ0FNam9SWkh2ZWFmZXE0azdWalotcFZmVzJTWGhVdWp3ZlJWRnk0VUlTRFFQNGtaRWc?oc=5</t>
   </si>
   <si>
     <t>Hawaiʻi Was Once A National Leader In Long-Term Care Financing - Honolulu Civil Beat</t>
@@ -2312,15 +2456,6 @@
     <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQNkJBUVJVMUd1Mld5MlFVSkZVYXNnUFV1MF9EeEVKX1dSSWxpcGpUbjBGR1BTdTBEem05UmlYdW1HdXlISHhhakVjYndQQUpRU3QxY1R0MFdiSFpNd0xOdE9La0Z2NFlUUkZhUWxHMC1SQ1gzZ1BDYXVVN1NZUElid0dLdmUwMVRyay04VmpnR2dkTVU4M1QtcU5PSlhyaF9kV1hyQQ?oc=5</t>
   </si>
   <si>
-    <t>Scottish Water taps Oracle to support agile transformation - Oracle</t>
-  </si>
-  <si>
-    <t>Scottish Water taps Oracle to support agile transformation  Oracle</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE04cnh1aG1Vcnp6bzI0R2ozajBGckJLcy10RG9JdTFlbDVacWRXSzA2V0hZa3d3bHVNY1NiVGRNVDNIM0pHVVM4SEozUG5zOFRmTmU3NVl4X2FyVDVq?oc=5</t>
-  </si>
-  <si>
     <t>The adoption and efficacy of large language models in US consumer financial complaints - Nature</t>
   </si>
   <si>
@@ -2339,139 +2474,13 @@
     <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9YZXY5aVdtbFpHdk1mQVZvaDgtWEdyaHpYd3N0a0dWZ3NQYlpfaEtwY3c1c2ZDQ0lfX05jdzBGaGZZZGR2UjhiZnZHMFJVa1FmVDFDSVIzbTBCMl9SNG9JVVMwTHl2MnVheEFfbXFWamQ?oc=5</t>
   </si>
   <si>
-    <t>Luotea plc will publish Financial Statements Release for 2025 on 27 February 2026 - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Luotea plc will publish Financial Statements Release for 2025 on 27 February 2026  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOV2t0cklVS29jTS1qa1Z3eDhNQms4bWVLUmV3MW94QTVMZnFJVXltbENYZmlPdmRneDM2RWJZbkxtT2o1WU1kdUVNSklKLXJfWU5VMWhMRmJuTzhkaW1jSGtnaFpmREk5Y2liRWVJb1FULWVubEdmTEtQX1ZUSmxRcXdveWJtdWsxODZuc2NR?oc=5</t>
-  </si>
-  <si>
-    <t>Swift Current Energy Secures Project Financing and Tax Equity for 122 MW Energy Facility in Maine - PR Newswire</t>
-  </si>
-  <si>
-    <t>Swift Current Energy Secures Project Financing and Tax Equity for 122 MW Energy Facility in Maine  PR Newswire</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOa2ZNV3VUc3ZrNktDSF9Hc1BaeGh4aFJaQWg1Uk5oSDFsdy1qQkRKSDVtWjVUV3pnVzloNHFWZ1BnUld1UGJpcnJLLUJsV2V2SVJMcW9QX0RXNDVvLXVhcUpiLXVWSWU0bWdsa3k4SnQ5OXFJeFFwQS13Wk00eGQ1RFc4WkxBcGk0azBXc1hYT3NFenk4R1hHYmFqTDZicXJvdVpiYWtXUFVjT3VBenZuMkx1UFJqSDhIVFczVUlTdl94QmVVWGJsSXd1TTRSWUx5NmVvR2ZxelBSOEtFNkZEU1laNzdOUDY3?oc=5</t>
-  </si>
-  <si>
-    <t>Wingstop Inc. Reports Fourth Quarter and Fiscal Year 2025 Financial Results - PR Newswire</t>
-  </si>
-  <si>
-    <t>Wingstop Inc. Reports Fourth Quarter and Fiscal Year 2025 Financial Results  PR Newswire</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxObjkzcjdQNW03cmVjV01GdWxoV2VjT2pZWEN6amlMSWw0UUotbk42TEt6cDVXZmp5Mnd1aG9QUk9Zb2owOC1BYXZjTW53RmoyWlFqNzV1ZmhSOTd0dFNJXzF5YUJsempmSDEwbVRXRk9CWmVOaXVNNG1lX2E2R3FhTFhrZDE2eDdGZVhDWnJDY1NzdF96M2VyQUVaNjIxbkVDdGhabnB3TkZPT2RzNlVmRk1iTnhzTnhDSnM0QmpVbnM5YkZ0M19aOFZ3?oc=5</t>
-  </si>
-  <si>
-    <t>MFA Financial, Inc. Announces Fourth Quarter and Full Year 2025 Financial Results - Yahoo Finance Singapore</t>
-  </si>
-  <si>
-    <t>MFA Financial, Inc. Announces Fourth Quarter and Full Year 2025 Financial Results  Yahoo Finance Singapore</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPWXRuWEJ5bFhBN1VnUngzblhLVDkzMDJkaTFWSmI4NnhzSkh1NTZpX2FWeEJIM0lNLURPU3o3bU1Uc3BpLU9CeW1Sek5OSDRPYnhNY3l6bDJNdEpsdXk3UjFLVU85OGZsVVkxeFN4QjdPQXVDdHlES0tteDZ3eS1aM1dTRnp5Y3FhdHRN?oc=5</t>
-  </si>
-  <si>
-    <t>Will Chen joins Westfield Specialty as U.S. Chief Financial Officer - PR Newswire</t>
-  </si>
-  <si>
-    <t>Will Chen joins Westfield Specialty as U.S. Chief Financial Officer  PR Newswire</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPVVpzWURrVFNsVXlfeHJ5VlE0MWpPNHJnYV9FRFhyR1lzU29iOWRmTURzUW4yVDlGUFFndUl4VzBKSGlxOWV1bVlIS1BCTmlscy1OQzk2Y1FUNnhEN2ZjV2JORmtKOWZvaDdxeGhZdGxGVlVaQThlSjBBYXJfeS10VkNMMXVQaTllMGh4V0VJc0JaVVRURHZSTWVrenJyRkJXUHc0TWk4ZzR0V3R4UFpfVldfNEppUEhrX2ZVTUl3?oc=5</t>
-  </si>
-  <si>
-    <t>FOX23 Investigates: Tulsa families question credit union they used to finance pools - fox23.com</t>
-  </si>
-  <si>
-    <t>FOX23 Investigates: Tulsa families question credit union they used to finance pools  fox23.com</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxOSXF3Qlc4SzVaLUtQS1lRT0RGS3BQVUN2aEtPQjVBcThGV2c2M2gzaTBSVFVTOUhkb0VGSlF2d3JMenA2eGdmU1FQODI1NlB6Y2ZKckV3ZTY4LWx3NnlnYlFFLUNlTzdfWXpCLUs0QjZjWG9PUmxQWE9XLTNmYlZ4VDBtLTREWFMyWkpLazlDN1J1aEJCX25qYU9OSUlkSzBaaTBrQXJTU3JQRk1JZHJOX2k2TnJyN0ZMdkJPQ29meUFJOVBDQ3FhY2lULWpOR3ROTml5VW5Ma0ZYZnR3LTNkdkNhY1FNbWxtdlZJX2hZaWE?oc=5</t>
-  </si>
-  <si>
-    <t>SME finance: the geographic gap in equity financing - Centre for Cities</t>
-  </si>
-  <si>
-    <t>SME finance: the geographic gap in equity financing  Centre for Cities</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQMnB0NmlfT2UxUFBXcTN3Um9NOU03UzVYNTdwNmMweC0tbVVDVk1hWVEyQ2hjUVhfblpfY0doUGhpckdHMm9vUDJPXzI3LVpQNG1aR09PbUlpeGVMTzBCTi1QYmhvRjJyR1hiUlBMcWFWVjVpZER2SkxiSUhKeXVrQU5TeEFxY1VIMmF5SjBRWGdLb3c?oc=5</t>
-  </si>
-  <si>
-    <t>Nvidia in focus: Meta partnership expanded, Arm stake sold - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Nvidia in focus: Meta partnership expanded, Arm stake sold  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOSFdMSEFMSDJ5Mk1nTk5xdkhTTHdDQzlJS3NZY2xKTnloYy1Nb2FQYk9QdHBoR3hqZlNOQkxzVHFTbEI5NGJ2OFA0Ulc2clhVR09nYTc3OU5jdVhMTFRDV0w2dERzWVVVQmJJWURFWUh3OEh0OTYwM2lHMkN2em9qcXotNE1sa1dzZjNaU1pn?oc=5</t>
-  </si>
-  <si>
-    <t>Verastem Oncology to Report Fourth Quarter and Full Year 2025 Financial Results on March 4, 2026 - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Verastem Oncology to Report Fourth Quarter and Full Year 2025 Financial Results on March 4, 2026  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOeHVlU1QyOWNaQnd4MlQ3dkF0RXdPczhfc0NJRDZpd2c1bDNQQThrblhraWQ2S0xhdk1kVGtDTkRrVktTZFE4c0hkcGlYS1hRdVYya0JnUlNrcEFQY09tcHBSNlhQS2pkdVByS3pFc0gydl9NOGRoQW5zX2ZLT0NZMzNkem9pRjBtQnhTZ3lB?oc=5</t>
-  </si>
-  <si>
-    <t>Palantir upgraded, Workday downgraded: Wall Street's top analyst calls - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Palantir upgraded, Workday downgraded: Wall Street's top analyst calls  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPQXBvZnBsVHRXNUF0NWpMRkFBbFJHeV9kQmFXMUxDbTRPcmszOW1TRmVDQXVROEpiLUpmQURXS2x0cnRncWZLYTRiYktrNW5PNGhfdXJrU1J5SEMzZHRMdEJ6TmxGOWt5eXRIelcyR3pPY2M2XzdrbldtazhyVGhxWXdxem9Ecm45VDVTT29kdTE?oc=5</t>
-  </si>
-  <si>
-    <t>Brian Armstrong Reveals Retail Users 'Buying The Dip' In Bitcoin, Ethereum: Coinbase CEO Says, 'They Have Diamond Hands' - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Brian Armstrong Reveals Retail Users 'Buying The Dip' In Bitcoin, Ethereum: Coinbase CEO Says, 'They Have Diamond Hands'  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPRGRKMXhSa2ZDZGZVbXRVZGpiYXNrOHpWc2FxWVpnSUMwVmtObExFdTlrSktGd0p1WlZaX1g4b3JacW9rRnVtMnpPM0tpSFIxRmJGS1cyX2ljLV9zLWxHc05qeXc3UUNBOU9PSDY4aTFMT040b3REODFGem9ULXM5SWtrSDROTzdZd0E?oc=5</t>
-  </si>
-  <si>
-    <t>Ericsson and Mastercard enhance global digital money movement and accelerate digital financial inclusion - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Ericsson and Mastercard enhance global digital money movement and accelerate digital financial inclusion  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNWk9Ha2ZHM3NrNmNMMjh2ZFlaX0dxdXdiYnBucXpHNTZZcTE1RGl6SGRCUzdMSW9yYzNqTGxRckhYT0NwUzhHVkxYSGcydVlrbTl6NzdyeG9SOW1aRmpUZ041T1V2OVNRdmRlaHVQVHRsWGpPUUlIc3I1a2dwWWJoTDFIQU90TmhxR2NQanZ1YmNkZw?oc=5</t>
-  </si>
-  <si>
-    <t>Harrow To Report Fourth Quarter and Year-End 2025 Financial Results After Market Close on March 2, 2026 - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Harrow To Report Fourth Quarter and Year-End 2025 Financial Results After Market Close on March 2, 2026  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxOVVB3alBRUWdJS0kxb3BYclo1VS1PclRzLVUwTmluRFFQX1JnZUVNUVEwR1JvcW94cWhnYWtuSTZ5QlA4TjBMTXNyUm0wZUt3YzhGdFpYbDBiQjBEaUpmVkFjZFNiYXY2bUZaOXJlelFaZzdSVjRmS3lsN2JEbmtxT2JJV2s?oc=5</t>
-  </si>
-  <si>
-    <t>Meta CEO Mark Zuckerberg set to testify in teen social media addiction suit - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Meta CEO Mark Zuckerberg set to testify in teen social media addiction suit  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOTDJaZUVoeXJuVjBuTUNrMU5GbEhncFgwVTZ5X0Q3bGFXNEhYakxDM3Q1VnQ1eS1rMzRDcERUSWZKX2xRcTVPNjFXbWJNTHV6SXVlcTBZd0tpTlZ2ZlZVb3JIMjZaSm1iM0UwR3h3LXdkU09MM2tmNDVFOXZmQldqQVkzV1hFRTFaSG1mQXF0OGNMY3hQbXZZa2dodjZJbkhVc1RwU0IwdGtIN2FuaURjeG11bGYxcVo5eHFsZXdn?oc=5</t>
-  </si>
-  <si>
-    <t>Recursion to Report Fourth Quarter and Full Year 2025 Business Updates and Financial Results on February 25 - Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Recursion to Report Fourth Quarter and Full Year 2025 Business Updates and Financial Results on February 25  Yahoo Finance</t>
-  </si>
-  <si>
-    <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNUktiOHpfaDBaekR6MmlpQVVTOXZ6TUZKYWxzblF4eE1acE54eXlNYWwtOVdYbmxadjhKNk5Vc1ZXVFFlNzQ1Zkt1Y0hfbDBlQ2VPOEM1Q3lEQ0FNam9SWkh2ZWFmZXE0azdWalotcFZmVzJTWGhVdWp3ZlJWRnk0VUlTRFFQNGtaRWc?oc=5</t>
+    <t>NewAmsterdam Pharma Reports Full Year 2025 Financial Results and Provides Corporate Update - Yahoo Finance</t>
+  </si>
+  <si>
+    <t>NewAmsterdam Pharma Reports Full Year 2025 Financial Results and Provides Corporate Update  Yahoo Finance</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPM0xkQ2h2UEN6cXdCRUprYkdxM3dSWV9mbG40R0tLcGtxY1BUaUJaU3hTaDM5dlcwRDVwcVU2eFZEbnczRnliY2ZncmxGbzNMa3lxSUM2dklkeW5Tc19GS2F1TnI2UTVVbkRsNlhndi1VWG5hX2tFOTBnYk9KNjdJa1lTbXJaQW82dUVz?oc=5</t>
   </si>
   <si>
     <t>Mortgage Rates Today, Wednesday, February 18: Rates Remain Low</t>
@@ -2573,6 +2582,15 @@
     <t>https://stockmarketwatch.com/stock-market-news/exxonmobil-expands-guyana-gas-strategy-jj-commits-1-billion-to-pennsylvania-expansion/58720/</t>
   </si>
   <si>
+    <t>Why Nvidia’s deal with Meta is an ‘Intel killer,’ according to this analyst</t>
+  </si>
+  <si>
+    <t>The use of Nvidia CPUs could signal a significant shift toward Arm-based chips in the data center.</t>
+  </si>
+  <si>
+    <t>https://www.marketwatch.com/story/why-nvidias-deal-with-meta-is-an-intel-killer-according-to-this-analyst-a531f80d?mod=mw_rss_topstories</t>
+  </si>
+  <si>
     <t>How Amazon’s ‘underappreciated’ AI potential could drive the stock 50% higher</t>
   </si>
   <si>
@@ -2654,13 +2672,22 @@
     <t>https://www.marketwatch.com/story/moderna-got-the-fda-to-change-its-mind-and-review-its-flu-vaccine-after-some-concessions-04c3f38e?mod=mw_rss_topstories</t>
   </si>
   <si>
-    <t>Why a 40-year Wall Street veteran is telling clients to sell everything American</t>
-  </si>
-  <si>
-    <t>Andy Constan says the rest of the world now offers more opportunities.</t>
-  </si>
-  <si>
-    <t>https://www.marketwatch.com/story/why-a-40-year-wall-street-veteran-is-telling-clients-to-sell-everything-american-77e50ae5?mod=mw_rss_topstories</t>
+    <t>Laureate Education Q4 2025 Earnings Preview</t>
+  </si>
+  <si>
+    <t>https://seekingalpha.com/news/4553468-laureate-education-q4-2025-earnings-preview?utm_source=feed_news_all&amp;utm_medium=referral&amp;feed_item_type=news</t>
+  </si>
+  <si>
+    <t>Sprott Q4 2025 Earnings Preview</t>
+  </si>
+  <si>
+    <t>https://seekingalpha.com/news/4553467-sprott-q4-2025-earnings-preview?utm_source=feed_news_all&amp;utm_medium=referral&amp;feed_item_type=news</t>
+  </si>
+  <si>
+    <t>Talkspace Q4 2025 Earnings Preview</t>
+  </si>
+  <si>
+    <t>https://seekingalpha.com/news/4553466-talkspace-q4-2025-earnings-preview?utm_source=feed_news_all&amp;utm_medium=referral&amp;feed_item_type=news</t>
   </si>
   <si>
     <t>ICON rises as Cowen upgrades after recent selloff</t>
@@ -2687,24 +2714,6 @@
     <t>https://seekingalpha.com/news/4553453-quad-projects-net-sales-decline-of-1-percent-to-5-percent-in-2026-as-targeted-print-and?utm_source=feed_news_all&amp;utm_medium=referral&amp;feed_item_type=news</t>
   </si>
   <si>
-    <t>Most and least shorted energy stocks with over $2B market cap as of mid-Feb</t>
-  </si>
-  <si>
-    <t>https://seekingalpha.com/news/4553446-most-and-least-shorted-large-cap-energy-stocks-as-of-mid-feb?utm_source=feed_news_all&amp;utm_medium=referral&amp;feed_item_type=news</t>
-  </si>
-  <si>
-    <t>Pediatrix Medical Group Q4 2025 Earnings Preview</t>
-  </si>
-  <si>
-    <t>https://seekingalpha.com/news/4553445-pediatrix-medical-group-q4-2025-earnings-preview?utm_source=feed_news_all&amp;utm_medium=referral&amp;feed_item_type=news</t>
-  </si>
-  <si>
-    <t>Visteon Q4 2025 Earnings Preview</t>
-  </si>
-  <si>
-    <t>https://seekingalpha.com/news/4553444-visteon-q4-2025-earnings-preview?utm_source=feed_news_all&amp;utm_medium=referral&amp;feed_item_type=news</t>
-  </si>
-  <si>
     <t>SharonAI debuts on Nasdaq slightly above IPO price</t>
   </si>
   <si>
@@ -2765,12 +2774,6 @@
     <t>https://www.investing.com/news/stock-market-news/moodys-forecasts-upbeat-2026-profit-on-strong-demand-for-credit-ratings-4510892</t>
   </si>
   <si>
-    <t>LIVE: White House briefing with Karoline Leavitt</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=f0LW2vYWuag</t>
-  </si>
-  <si>
     <t>LIVE: House's Hakeem Jeffries holds a briefing in Washington</t>
   </si>
   <si>
@@ -2853,6 +2856,12 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=osMjcYVxqEg</t>
+  </si>
+  <si>
+    <t>BAE Systems sees years of growth in ‘new era’ of defense spending</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=eBgrSqQEDX4</t>
   </si>
   <si>
     <t>Candidaturas de empresas a linha de crédito à tesouraria devido ao mau tempo somam 905 milhões</t>
@@ -4039,7 +4048,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D431"/>
+  <dimension ref="A1:D432"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -8098,8 +8107,11 @@
       <c r="A290" t="s">
         <v>864</v>
       </c>
+      <c r="B290" t="s">
+        <v>865</v>
+      </c>
       <c r="C290" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D290" t="s">
         <v>7</v>
@@ -8107,10 +8119,10 @@
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C291" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="D291" t="s">
         <v>7</v>
@@ -8118,10 +8130,10 @@
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C292" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D292" t="s">
         <v>7</v>
@@ -8129,10 +8141,10 @@
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C293" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="D293" t="s">
         <v>7</v>
@@ -8140,10 +8152,10 @@
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C294" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D294" t="s">
         <v>7</v>
@@ -8151,10 +8163,10 @@
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C295" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D295" t="s">
         <v>7</v>
@@ -8162,10 +8174,10 @@
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C296" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="D296" t="s">
         <v>7</v>
@@ -8173,10 +8185,10 @@
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C297" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D297" t="s">
         <v>7</v>
@@ -8184,10 +8196,10 @@
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C298" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="D298" t="s">
         <v>7</v>
@@ -8195,10 +8207,10 @@
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C299" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="D299" t="s">
         <v>7</v>
@@ -8206,10 +8218,10 @@
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C300" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="D300" t="s">
         <v>7</v>
@@ -8217,10 +8229,10 @@
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C301" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D301" t="s">
         <v>7</v>
@@ -8228,10 +8240,10 @@
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C302" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D302" t="s">
         <v>7</v>
@@ -8239,10 +8251,10 @@
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C303" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D303" t="s">
         <v>7</v>
@@ -8250,10 +8262,10 @@
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C304" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D304" t="s">
         <v>7</v>
@@ -8261,10 +8273,10 @@
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C305" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D305" t="s">
         <v>7</v>
@@ -8272,10 +8284,10 @@
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C306" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="D306" t="s">
         <v>7</v>
@@ -8283,10 +8295,10 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C307" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="D307" t="s">
         <v>7</v>
@@ -8294,10 +8306,10 @@
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C308" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D308" t="s">
         <v>7</v>
@@ -8305,10 +8317,10 @@
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C309" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D309" t="s">
         <v>7</v>
@@ -8316,10 +8328,10 @@
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C310" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D310" t="s">
         <v>7</v>
@@ -8327,10 +8339,10 @@
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C311" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D311" t="s">
         <v>7</v>
@@ -8338,10 +8350,10 @@
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C312" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D312" t="s">
         <v>7</v>
@@ -8349,10 +8361,10 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C313" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="D313" t="s">
         <v>7</v>
@@ -8360,10 +8372,10 @@
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C314" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D314" t="s">
         <v>7</v>
@@ -8371,10 +8383,10 @@
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C315" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D315" t="s">
         <v>7</v>
@@ -8382,10 +8394,10 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C316" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D316" t="s">
         <v>7</v>
@@ -8393,10 +8405,10 @@
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C317" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D317" t="s">
         <v>7</v>
@@ -8404,10 +8416,10 @@
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C318" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D318" t="s">
         <v>7</v>
@@ -8415,10 +8427,10 @@
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C319" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D319" t="s">
         <v>7</v>
@@ -8426,10 +8438,10 @@
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C320" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="D320" t="s">
         <v>7</v>
@@ -8437,10 +8449,10 @@
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="C321" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D321" t="s">
         <v>7</v>
@@ -8448,9 +8460,6 @@
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>928</v>
-      </c>
-      <c r="B322" t="s">
         <v>929</v>
       </c>
       <c r="C322" t="s">
@@ -8590,8 +8599,11 @@
       <c r="A332" t="s">
         <v>958</v>
       </c>
+      <c r="B332" t="s">
+        <v>959</v>
+      </c>
       <c r="C332" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="D332" t="s">
         <v>7</v>
@@ -8599,10 +8611,10 @@
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C333" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="D333" t="s">
         <v>7</v>
@@ -8610,10 +8622,10 @@
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C334" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="D334" t="s">
         <v>7</v>
@@ -8621,10 +8633,10 @@
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="C335" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D335" t="s">
         <v>7</v>
@@ -8632,10 +8644,10 @@
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C336" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="D336" t="s">
         <v>7</v>
@@ -8643,10 +8655,10 @@
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C337" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D337" t="s">
         <v>7</v>
@@ -8654,10 +8666,10 @@
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="C338" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="D338" t="s">
         <v>7</v>
@@ -8665,10 +8677,10 @@
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>878</v>
+        <v>973</v>
       </c>
       <c r="C339" t="s">
-        <v>879</v>
+        <v>974</v>
       </c>
       <c r="D339" t="s">
         <v>7</v>
@@ -8676,10 +8688,10 @@
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>972</v>
+        <v>881</v>
       </c>
       <c r="C340" t="s">
-        <v>973</v>
+        <v>882</v>
       </c>
       <c r="D340" t="s">
         <v>7</v>
@@ -8687,10 +8699,10 @@
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>880</v>
+        <v>975</v>
       </c>
       <c r="C341" t="s">
-        <v>881</v>
+        <v>976</v>
       </c>
       <c r="D341" t="s">
         <v>7</v>
@@ -8698,10 +8710,10 @@
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C342" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="D342" t="s">
         <v>7</v>
@@ -8709,13 +8721,10 @@
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>974</v>
-      </c>
-      <c r="B343" t="s">
-        <v>975</v>
+        <v>885</v>
       </c>
       <c r="C343" t="s">
-        <v>976</v>
+        <v>886</v>
       </c>
       <c r="D343" t="s">
         <v>7</v>
@@ -9045,13 +9054,13 @@
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>111</v>
+        <v>1046</v>
       </c>
       <c r="B367" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="C367" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="D367" t="s">
         <v>7</v>
@@ -9059,7 +9068,7 @@
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>1048</v>
+        <v>111</v>
       </c>
       <c r="B368" t="s">
         <v>1049</v>
@@ -9591,13 +9600,13 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>237</v>
+        <v>1162</v>
       </c>
       <c r="B406" t="s">
-        <v>238</v>
+        <v>1163</v>
       </c>
       <c r="C406" t="s">
-        <v>239</v>
+        <v>1164</v>
       </c>
       <c r="D406" t="s">
         <v>7</v>
@@ -9605,13 +9614,13 @@
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B407" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C407" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D407" t="s">
         <v>7</v>
@@ -9619,13 +9628,13 @@
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>1162</v>
+        <v>240</v>
       </c>
       <c r="B408" t="s">
-        <v>1163</v>
+        <v>241</v>
       </c>
       <c r="C408" t="s">
-        <v>1164</v>
+        <v>242</v>
       </c>
       <c r="D408" t="s">
         <v>7</v>
@@ -9731,13 +9740,13 @@
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>243</v>
+        <v>1186</v>
       </c>
       <c r="B416" t="s">
-        <v>244</v>
+        <v>1187</v>
       </c>
       <c r="C416" t="s">
-        <v>245</v>
+        <v>1188</v>
       </c>
       <c r="D416" t="s">
         <v>7</v>
@@ -9745,13 +9754,13 @@
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B417" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C417" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D417" t="s">
         <v>7</v>
@@ -9759,13 +9768,13 @@
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B418" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C418" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D418" t="s">
         <v>7</v>
@@ -9773,13 +9782,13 @@
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B419" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C419" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D419" t="s">
         <v>7</v>
@@ -9787,13 +9796,13 @@
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B420" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C420" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D420" t="s">
         <v>7</v>
@@ -9801,13 +9810,13 @@
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B421" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C421" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D421" t="s">
         <v>7</v>
@@ -9815,13 +9824,13 @@
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B422" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C422" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D422" t="s">
         <v>7</v>
@@ -9829,13 +9838,13 @@
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B423" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C423" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D423" t="s">
         <v>7</v>
@@ -9843,13 +9852,13 @@
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B424" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C424" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D424" t="s">
         <v>7</v>
@@ -9857,13 +9866,13 @@
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B425" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C425" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D425" t="s">
         <v>7</v>
@@ -9871,13 +9880,13 @@
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B426" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C426" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D426" t="s">
         <v>7</v>
@@ -9885,13 +9894,13 @@
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B427" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C427" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D427" t="s">
         <v>7</v>
@@ -9899,13 +9908,13 @@
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B428" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C428" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D428" t="s">
         <v>7</v>
@@ -9913,13 +9922,13 @@
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B429" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C429" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D429" t="s">
         <v>7</v>
@@ -9927,13 +9936,13 @@
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B430" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C430" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D430" t="s">
         <v>7</v>
@@ -9941,15 +9950,29 @@
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
+        <v>285</v>
+      </c>
+      <c r="B431" t="s">
+        <v>286</v>
+      </c>
+      <c r="C431" t="s">
+        <v>287</v>
+      </c>
+      <c r="D431" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
         <v>288</v>
       </c>
-      <c r="B431" t="s">
+      <c r="B432" t="s">
         <v>289</v>
       </c>
-      <c r="C431" t="s">
+      <c r="C432" t="s">
         <v>290</v>
       </c>
-      <c r="D431" t="s">
+      <c r="D432" t="s">
         <v>7</v>
       </c>
     </row>
